--- a/results/job_matches_2026-05-30.xlsx
+++ b/results/job_matches_2026-05-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G196"/>
+  <dimension ref="A1:G261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote in CA)</t>
+          <t>Associate Data Solutions Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>22.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Google Cloud Platform, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=096ec33d45508f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c665018c2e31d8</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88c69f0d47a40e9</t>
+          <t>https://www.indeed.com/viewjob?jk=096ec33d45508f2d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AXIAN</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,17 +556,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67aa72efa5b04e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=b88c69f0d47a40e9</t>
         </is>
       </c>
     </row>
@@ -678,95 +678,95 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Data Modeler</t>
+          <t>Full Stack Developer / AI Focused</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Republic Services</t>
+          <t>CarParts.com</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, RDS, Medallion Architecture, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633c48c04bec794a</t>
+          <t>https://www.indeed.com/viewjob?jk=c61c6b86bc3293d8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Sr. Data Modeler</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>Republic Services</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Splunk</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, RDS, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d54cb6fb55273d2</t>
+          <t>https://www.indeed.com/viewjob?jk=633c48c04bec794a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Databricks Administrator</t>
+          <t>Cloud &amp; Digital Platform DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Avnet</t>
+          <t>Diality</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4012204380caba1</t>
+          <t>https://www.indeed.com/viewjob?jk=905414e7ceb13800</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Solutions Architect - Platform, Cloud Infrastructure and Security</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SunnyData</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Splunk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47aa02c81d1c7a60</t>
+          <t>https://www.indeed.com/viewjob?jk=7d54cb6fb55273d2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data</t>
+          <t>Databricks Administrator</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sightview Software</t>
+          <t>Avnet</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102fc288fbb9abdd</t>
+          <t>https://www.indeed.com/viewjob?jk=e4012204380caba1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud Engineer - DevOps</t>
+          <t>Solutions Architect - Platform, Cloud Infrastructure and Security</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Innovative Solutions</t>
+          <t>SunnyData</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521ed8a47e56a014</t>
+          <t>https://www.indeed.com/viewjob?jk=47aa02c81d1c7a60</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - IGEN</t>
+          <t>Software Engineer III - Big Data</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>Sightview Software</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0ca36351ff88fb</t>
+          <t>https://www.indeed.com/viewjob?jk=102fc288fbb9abdd</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Cloud Engineer - DevOps</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>Innovative Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Spark, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0761c7021676d118</t>
+          <t>https://www.indeed.com/viewjob?jk=521ed8a47e56a014</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Snowflake)</t>
+          <t>Senior Data Engineer - IGEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>VSP Vision</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Appleton, WI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Cloud Storage, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d06419a6d15ac391</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0ca36351ff88fb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47fb9412169ca299</t>
+          <t>https://www.indeed.com/viewjob?jk=330bf279fb8cd838</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Spark, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cd40cf715d1757e</t>
+          <t>https://www.indeed.com/viewjob?jk=0761c7021676d118</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3efe7a4e50700ee</t>
+          <t>https://www.indeed.com/viewjob?jk=1cd40cf715d1757e</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alachua, FL, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3185efffc8151880</t>
+          <t>https://www.indeed.com/viewjob?jk=c3efe7a4e50700ee</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bar Harbor, ME, US USA</t>
+          <t>Alachua, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b53f7ddb0026dea4</t>
+          <t>https://www.indeed.com/viewjob?jk=3185efffc8151880</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Bar Harbor, ME, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf3b9815a50b381</t>
+          <t>https://www.indeed.com/viewjob?jk=b53f7ddb0026dea4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer (Contract)</t>
+          <t>Informatica Product Owner - Remote</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AXIAN</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91333a1bd534aa31</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf3b9815a50b381</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,69 +1256,69 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, ECS, RDS, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f59e2bfb4a8152</t>
+          <t>https://www.indeed.com/viewjob?jk=6bc40683645d5866</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bc40683645d5866</t>
+          <t>https://www.indeed.com/viewjob?jk=d0769674b72ae58f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Solutions Architect</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd4faeed9a50a59</t>
+          <t>https://www.indeed.com/viewjob?jk=aef1c5cf0ee00174</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Data Solutions Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0769674b72ae58f</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd4faeed9a50a59</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Architect - Remote</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aef1c5cf0ee00174</t>
+          <t>https://www.indeed.com/viewjob?jk=4c32603ea351f9bf</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Architect - Remote</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Kafka, PostgreSQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c32603ea351f9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=17cb9776bd0e7f4a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Kafka, PostgreSQL, MongoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cb9776bd0e7f4a</t>
+          <t>https://www.indeed.com/viewjob?jk=1bcc3fe3fd715833</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Infrastructure</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bcc3fe3fd715833</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd2d99f50f24a3c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,104 +1536,104 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd2d99f50f24a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=1558bff9d1119b05</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Digital Customer Experience</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e4adfa75de057b</t>
+          <t>https://www.indeed.com/viewjob?jk=c250c7540d478f32</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1558bff9d1119b05</t>
+          <t>https://www.indeed.com/viewjob?jk=a88dfb056c5c3b9b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>Data Platform Engineer- 6 Month Assignment</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a88dfb056c5c3b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5d273dd8b89dfc</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Platform Engineer- 6 Month Assignment</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>Aptean</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5d273dd8b89dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=13c44a8aef4fd0a0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Aptean</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, NoSQL</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aa9a1ae247379c0</t>
+          <t>https://www.indeed.com/viewjob?jk=ef802648dc8c758d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site AI Engineer - Boston, MA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Aptean</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13c44a8aef4fd0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf91e3de3b3cfaa</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site AI Engineer - Temple, TX</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Aptean</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,24 +1781,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef802648dc8c758d</t>
+          <t>https://www.indeed.com/viewjob?jk=02502cf23954a80e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Boston, MA</t>
+          <t>Site AI Engineer - Las Vegas, NV</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf91e3de3b3cfaa</t>
+          <t>https://www.indeed.com/viewjob?jk=71a6429c12809608</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Temple, TX</t>
+          <t>Site AI Engineer - Dallas, TX</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1856,19 +1856,19 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02502cf23954a80e</t>
+          <t>https://www.indeed.com/viewjob?jk=94942178e7603ad0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Las Vegas, NV</t>
+          <t>Site AI Engineer - Fort Meyers, FL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Fort Myers, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1891,19 +1891,19 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71a6429c12809608</t>
+          <t>https://www.indeed.com/viewjob?jk=1119ddab775a5553</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Dallas, TX</t>
+          <t>Site AI Engineer - USVI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte Amalie, VI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1926,99 +1926,99 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94942178e7603ad0</t>
+          <t>https://www.indeed.com/viewjob?jk=d2dcedc535de31f7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Fort Meyers, FL</t>
+          <t>Senior Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Decagon</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Fort Myers, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1119ddab775a5553</t>
+          <t>https://www.indeed.com/viewjob?jk=d3d218109f5a2e7c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Site AI Engineer - USVI</t>
+          <t>Senior Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Decagon</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte Amalie, VI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2dcedc535de31f7</t>
+          <t>https://www.indeed.com/viewjob?jk=cb96afd07bcd39f3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Infrastructure</t>
+          <t>Platform Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Decagon</t>
+          <t>Happy Returns, Inc.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3d218109f5a2e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa757e1e92cc3c3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Infrastructure</t>
+          <t>Sr. DevOps Engineer- Snowflake &amp; Azure</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Decagon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb96afd07bcd39f3</t>
+          <t>https://www.indeed.com/viewjob?jk=763fd8f53ea47c3f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Platform Software Engineer (Remote)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Happy Returns, Inc.</t>
+          <t>Echo Global Logistics</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Data Modeling</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa757e1e92cc3c3</t>
+          <t>https://www.indeed.com/viewjob?jk=eae8bcb49c9597d5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer- Snowflake &amp; Azure</t>
+          <t>Data Engineer (Agent Systems)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Faraday Future</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>S3, RDS, BigQuery, Spark, Kafka, Snowflake, PostgreSQL, MySQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763fd8f53ea47c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=3701c804c9b0b189</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Cloud &amp; Digital Platform Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Echo Global Logistics</t>
+          <t>Diality</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, GCP, Scala, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae8bcb49c9597d5</t>
+          <t>https://www.indeed.com/viewjob?jk=7fe3f1dbc64665df</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer (Agent Systems)</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Faraday Future</t>
+          <t>Frontwave Credit Union</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>S3, RDS, BigQuery, Spark, Kafka, Snowflake, PostgreSQL, MySQL, dbt, CI/CD</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3701c804c9b0b189</t>
+          <t>https://www.indeed.com/viewjob?jk=ddd8dc23d0848aec</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer (Agent Systems)</t>
+          <t>Sr. Solutions Architect - Emerging</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Faraday Future</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>S3, RDS, BigQuery, Spark, Kafka, Snowflake, PostgreSQL, MySQL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,14 +2246,14 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5592fc9e666f0b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=7afdce6cf8faaddf</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Emerging</t>
+          <t>Sr. Solutions Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7afdce6cf8faaddf</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ce1a2957006a72</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,42 +2306,42 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ce1a2957006a72</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f0a0dc2930f694</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>MAGNETO &amp; DIESEL INJECTOR SERVICE</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Humble, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Scala, MySQL, MongoDB, NoSQL, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hive, Sqoop, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,102 +2351,102 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecf9ebddadf41837</t>
+          <t>https://www.indeed.com/viewjob?jk=d19cafe12d10dcef</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Sr. Systems Engineer- Cloud Infrastructure Engineering</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Frontwave Credit Union</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddd8dc23d0848aec</t>
+          <t>https://www.indeed.com/viewjob?jk=4de6e8c6244caa58</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f0a0dc2930f694</t>
+          <t>https://www.indeed.com/viewjob?jk=3be471e01eea2f2a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Database Administrator (Automation, Cloud &amp; Data Analytics)</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brooklyn, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfec1ad6856f8bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=bb8f91201caafc33</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MAGNETO &amp; DIESEL INJECTOR SERVICE</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Humble, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hive, Sqoop, Spark, Scala, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d19cafe12d10dcef</t>
+          <t>https://www.indeed.com/viewjob?jk=29a68b9b44071451</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be471e01eea2f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=34d8a92dff07ca15</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Azure Full Stack Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Hiro Talent Solutions</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>RDS, Azure, Blob Storage, Scala, Power BI, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb8f91201caafc33</t>
+          <t>https://www.indeed.com/viewjob?jk=c770b1c4f512c431</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Senior Software Engineer - Infrastructure and Tools</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a68b9b44071451</t>
+          <t>https://www.indeed.com/viewjob?jk=92d9bf233ed60118</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>AI Engineer/Solution Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>andrew morgan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d8a92dff07ca15</t>
+          <t>https://www.indeed.com/viewjob?jk=f828ea2a58e520b1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Azure Full Stack Engineer</t>
+          <t>Software Engineer II - Full Stack Java</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Hiro Talent Solutions</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Scala, Power BI, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c770b1c4f512c431</t>
+          <t>https://www.indeed.com/viewjob?jk=2c274b0f05e69603</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Infrastructure and Tools</t>
+          <t>Cloud Data Architect (Full-time Remote, NC Based)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Alliance Health Plan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow</t>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92d9bf233ed60118</t>
+          <t>https://www.indeed.com/viewjob?jk=8cb114578f5bf1e9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform</t>
+          <t>AI Engineer/Solution Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>andrew morgan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee0bc73a9e9547ac</t>
+          <t>https://www.indeed.com/viewjob?jk=7604b89af99ba406</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer II - Full Stack Java</t>
+          <t>Senior Software Engineer, Product Foundations</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, SQS, IAM, RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c274b0f05e69603</t>
+          <t>https://www.indeed.com/viewjob?jk=dd2bfc17d54981e1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI Engineer/Solution Architect</t>
+          <t>Senior Software Engineer, Product Foundations</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>andrew morgan</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, NoSQL</t>
+          <t>AWS, SQS, IAM, RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7604b89af99ba406</t>
+          <t>https://www.indeed.com/viewjob?jk=0277abc185dfb7c6</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Product Foundations</t>
+          <t>Software Engineer 4</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Castlight</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd2bfc17d54981e1</t>
+          <t>https://www.indeed.com/viewjob?jk=3ce519e36124f5ab</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Product Foundations</t>
+          <t>Full Stack Developer -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0277abc185dfb7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=adcfd5cf564b5b00</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ce519e36124f5ab</t>
+          <t>https://www.indeed.com/viewjob?jk=b5023cf7cd4ba777</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full Stack Developer -In office, Alpharetta, GA</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd5cf564b5b00</t>
+          <t>https://www.indeed.com/viewjob?jk=8f9b9650d1bc3a54</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cloud Data Architect (Full-time Remote, NC Based)</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Alliance Health Plan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cb114578f5bf1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=efb82b07adb9feba</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer 4</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Castlight</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5023cf7cd4ba777</t>
+          <t>https://www.indeed.com/viewjob?jk=65195644bb1b9e0b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer Expert</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1f104bd0b18db7</t>
+          <t>https://www.indeed.com/viewjob?jk=75e8ade515a41a57</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Irvington, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a189ac16e1f72f61</t>
+          <t>https://www.indeed.com/viewjob?jk=859e82cabfb17666</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer Expert</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc3130fd4a42b451</t>
+          <t>https://www.indeed.com/viewjob?jk=f143b13efb8ce9b6</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Distributed Data Systems</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f494d2abfb9b3a</t>
+          <t>https://www.indeed.com/viewjob?jk=5a031b4964c2a255</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Distributed Data Systems</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35301f7890450ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=c4349cc4f94a5d87</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Distributed Data Systems</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,67 +3226,67 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f178ac0bdca2782a</t>
+          <t>https://www.indeed.com/viewjob?jk=e66448573f4489d1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hive, Spark, Scala, ELT, MLOps, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d531875d9bfd27</t>
+          <t>https://www.indeed.com/viewjob?jk=ddbf7440ad773888</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Fabletics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac7bdb141d55008</t>
+          <t>https://www.indeed.com/viewjob?jk=b72f3a18139b7e54</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DevOps Engineer, II</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NRCCUA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e257db597eccae8d</t>
+          <t>https://www.indeed.com/viewjob?jk=7467917f2474b2e9</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DevOps Engineer, II</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Encoura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22172251f6a1ea83</t>
+          <t>https://www.indeed.com/viewjob?jk=741f313dfe0a4767</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - GSI's and FinTech Data</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44ec35e1f7566eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=fb549dda19deb4df</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Solutions Architect - Emerging Enterprise (Startups)</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f72901b7b29fed1</t>
+          <t>https://www.indeed.com/viewjob?jk=ad53455736c94aa1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Financial Services (Insurance)</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df17d8e1960c7150</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf96d3e5672d2dd</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Solutions Architect - Emerging Enterprise</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e7797d12dd5834</t>
+          <t>https://www.indeed.com/viewjob?jk=a2abd6bece93c89e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Financial Services (Wealth and Asset Management)</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b25a6a580453b9d6</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7b4a6316115547</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7a9b5d614307098</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef2a2c6485dc8ce</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Solutions Architect - MFG</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aad818a2ea4d82e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8777195f0640326</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Integration Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,67 +3646,67 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606aeb761182bb83</t>
+          <t>https://www.indeed.com/viewjob?jk=8b251c80469648dc</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AI Automation Developer II</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Yale New Haven Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Stratford, CT, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b4f3e15b0e54b1c</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad5e6a6c6033f66</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Fullstack</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,137 +3716,137 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e1d5edd7f6cfacc</t>
+          <t>https://www.indeed.com/viewjob?jk=4439501b54b34a7a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (React, JavaScript, .net)</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Hagerstown, MD, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, Data Modeling, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc464898e64c2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=1151c815185cd79e</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior AI Full Stack Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=825e221841f6b0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=d6614c39234b9da2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Engineering Specialist</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35e60c72e365c000</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7e23c7f438f8c8</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae7ce0b79b127907</t>
+          <t>https://www.indeed.com/viewjob?jk=e8663ead75611c2e</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc99c4d09fcc8c74</t>
+          <t>https://www.indeed.com/viewjob?jk=51de78e580811e18</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2644095339b05a5</t>
+          <t>https://www.indeed.com/viewjob?jk=548feeaa37b8c916</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Mimecast</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca736f22eed6fef2</t>
+          <t>https://www.indeed.com/viewjob?jk=9cf7d70224611ecc</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Cost Engineer – Data Analytics</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69730719f6ab06e5</t>
+          <t>https://www.indeed.com/viewjob?jk=08e283453e85139f</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer / Database Management Specialist for Fish Data</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,67 +4031,67 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ce35760bca7d80</t>
+          <t>https://www.indeed.com/viewjob?jk=ecaa2a1fd433f4a4</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ATI Physical Therapy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f9e3e8db4c59f0</t>
+          <t>https://www.indeed.com/viewjob?jk=dd01c10e73409cc8</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Public Sector (Hunter)</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e07e9f86b285212</t>
+          <t>https://www.indeed.com/viewjob?jk=3166241cc8c62f5d</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Public Sector (Federal Civilian)</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3046d735729808a</t>
+          <t>https://www.indeed.com/viewjob?jk=1572589542133e74</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Digital Native Business</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=604425795ad5683a</t>
+          <t>https://www.indeed.com/viewjob?jk=a2ec3f9f81325aa0</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Solutions Architect - Public Sector (SLED)</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff1bc3eed7d9ae60</t>
+          <t>https://www.indeed.com/viewjob?jk=492f0c5d5b1026f4</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Public Sector (SLED)</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7b19a38637eb42</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5a1bf124fcc939</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Public Sector (SLED)</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37498a6699ecacb</t>
+          <t>https://www.indeed.com/viewjob?jk=e7780a9fb7958201</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>BI Engineer - Data Analytics</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca97d35c293c8ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=fd18a128a4672b91</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4edb47917f0e6215</t>
+          <t>https://www.indeed.com/viewjob?jk=ea676aaaba70e2d7</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e84f993a048191bd</t>
+          <t>https://www.indeed.com/viewjob?jk=cab3ba747ce4a550</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aad1cd4d5b8e2</t>
+          <t>https://www.indeed.com/viewjob?jk=d65e39a595440fab</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer, IT Software</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fda6cb70fb70e09</t>
+          <t>https://www.indeed.com/viewjob?jk=55cb9c48e2f72a54</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd22b9c4b47341c</t>
+          <t>https://www.indeed.com/viewjob?jk=b3a01b8449781d9b</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Everbridge</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43479a5e279bea94</t>
+          <t>https://www.indeed.com/viewjob?jk=5fa7561c868d2097</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Everbridge</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c9dce1dbceabf77</t>
+          <t>https://www.indeed.com/viewjob?jk=3a729d7eaa711e20</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Fullstack</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d41030c2a031bc3</t>
+          <t>https://www.indeed.com/viewjob?jk=1f022796cfb8fbcc</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Fullstack</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,67 +4626,67 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e37bcb174213c7a</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c33b5572cf45fa</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Enlyte</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24937a6185650d43</t>
+          <t>https://www.indeed.com/viewjob?jk=8762f88f61ad7223</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior BI Analyst - IGEN</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, dbt, Power BI, Tableau, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,67 +4696,67 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd6baf60c6afe77</t>
+          <t>https://www.indeed.com/viewjob?jk=efdfb03d10f7ec00</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Forward Deployed Data Engineer Expert</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Thousand Oaks, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Oracle, MySQL, CI/CD, Jenkins, AKS, Jenkins</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95ab2514764a8e05</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1f104bd0b18db7</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SmartAsset</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvington, NY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f326fc2210a7954</t>
+          <t>https://www.indeed.com/viewjob?jk=a189ac16e1f72f61</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend</t>
+          <t>Forward Deployed Data Engineer Expert</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,14 +4801,14 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9446abbf0a9e21d5</t>
+          <t>https://www.indeed.com/viewjob?jk=fc3130fd4a42b451</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend</t>
+          <t>Senior Software Engineer - Distributed Data Systems</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4818,15 +4818,15 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,102 +4836,102 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cf9f394fc466cab</t>
+          <t>https://www.indeed.com/viewjob?jk=68f494d2abfb9b3a</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Distributed Data Systems</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d95d0b3cc2017278</t>
+          <t>https://www.indeed.com/viewjob?jk=35301f7890450ed0</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer - Distributed Data Systems</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=392c5b4963d57266</t>
+          <t>https://www.indeed.com/viewjob?jk=f178ac0bdca2782a</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Associate, Data Analytics Engineering</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Insight Software</t>
+          <t>Options Clearing Corporation</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f17a3a493c5baa0</t>
+          <t>https://www.indeed.com/viewjob?jk=1ad61eb5cd2a5633</t>
         </is>
       </c>
     </row>
@@ -4953,20 +4953,20 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>Fabletics</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spokane Valley, WA, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,32 +4976,32 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b11f37b58c06df</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac7bdb141d55008</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>DevOps Engineer, II</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>NRCCUA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,32 +5011,32 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e166dda8b8fb2c2</t>
+          <t>https://www.indeed.com/viewjob?jk=e257db597eccae8d</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>DevOps Engineer, II</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>Encoura</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Richland, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,32 +5046,32 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38d66edddd66e10c</t>
+          <t>https://www.indeed.com/viewjob?jk=22172251f6a1ea83</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
+          <t>Senior Software Engineer - Fullstack</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,154 +5081,154 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89dd9964d8bd40d3</t>
+          <t>https://www.indeed.com/viewjob?jk=6e1d5edd7f6cfacc</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer (React, JavaScript, .net)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Youth Villages</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Chesterfield, VA, US USA</t>
+          <t>Hagerstown, MD, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, Data Modeling, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db40921aad59c33b</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc464898e64c2d7</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09edda39b98ef300</t>
+          <t>https://www.indeed.com/viewjob?jk=825e221841f6b0ce</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI Automation Developer II</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Yale New Haven Health</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Stratford, CT, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b96821caf0970503</t>
+          <t>https://www.indeed.com/viewjob?jk=7b4f3e15b0e54b1c</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Solutions Architect, Hunter - Digital Native Business</t>
+          <t>Engineering Specialist</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f73730c651c668</t>
+          <t>https://www.indeed.com/viewjob?jk=35e60c72e365c000</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Solutions Engineer - GSI's and FinTech Data</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5238,15 +5238,15 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,14 +5256,14 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5573ef7a1b12bff2</t>
+          <t>https://www.indeed.com/viewjob?jk=44ec35e1f7566eb4</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Healthcare &amp; Life Sciences</t>
+          <t>Sr. Solutions Engineer - Financial Services (Insurance)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5273,15 +5273,15 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,32 +5291,32 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=321bfa09857de51b</t>
+          <t>https://www.indeed.com/viewjob?jk=df17d8e1960c7150</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,32 +5326,32 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d65210acef7f3cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ae7ce0b79b127907</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Financial Services</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,32 +5361,32 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8079788dc4b57b</t>
+          <t>https://www.indeed.com/viewjob?jk=dc99c4d09fcc8c74</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Financial Services</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,32 +5396,32 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=178e68526af56a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=a2644095339b05a5</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Financial Services</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Mimecast</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, S3, SQS, RDS, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,32 +5431,32 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=548c7479d4abc718</t>
+          <t>https://www.indeed.com/viewjob?jk=ca736f22eed6fef2</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Healthcare &amp; Life Sciences</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,19 +5466,19 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c99b1563d5b2a5e4</t>
+          <t>https://www.indeed.com/viewjob?jk=b7994c3eb46bae42</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Ai Architect</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5487,11 +5487,11 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,32 +5501,32 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b842ee858dea9c</t>
+          <t>https://www.indeed.com/viewjob?jk=649242ee28a33ae5</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,32 +5536,32 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85ead362a062186e</t>
+          <t>https://www.indeed.com/viewjob?jk=4b46b87f1359f8f5</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Manufacturing</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,32 +5571,32 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a09c3cec51934e4</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a7b9a70e68cf9f</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Solutions Architect - Digital Native Business, Strategic</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,32 +5606,32 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e61be032685e36</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a148e3a41849d9</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,32 +5641,32 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38625ef404e5c4f3</t>
+          <t>https://www.indeed.com/viewjob?jk=fa4b4fcc410a503a</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,32 +5676,32 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7e1163fe26a7f0c</t>
+          <t>https://www.indeed.com/viewjob?jk=6147a561d729a0dd</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Healthcare &amp; Life Sciences</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,32 +5711,32 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=300acc8c1eb7c502</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab5bc5f32a7b9a0</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,32 +5746,32 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f223dfd349f07c12</t>
+          <t>https://www.indeed.com/viewjob?jk=29f309b16d064eae</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Financial Services</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,32 +5781,32 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91a31dc96a52eccd</t>
+          <t>https://www.indeed.com/viewjob?jk=f0b6e4cc0b843bf8</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,32 +5816,32 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7db4000add37c391</t>
+          <t>https://www.indeed.com/viewjob?jk=9d739c3bc7cf38d1</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Strategic AI Native</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,32 +5851,32 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e74525fcfa96e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=70aa889c4c9efda8</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Healthcare &amp; Life Sciences</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,32 +5886,32 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7770787ca90c8b1</t>
+          <t>https://www.indeed.com/viewjob?jk=97557fcc3403a036</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Manufacturing</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,32 +5921,32 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bab1eb82e51a467</t>
+          <t>https://www.indeed.com/viewjob?jk=01009226e788120d</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - AI Natives Business</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,32 +5956,32 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d884fcaeec353d16</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b0eb4fb08e6514</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Financial Services</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,32 +5991,32 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=427fc18bf3e71e29</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7b1778e389048a</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Manufacturing</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,32 +6026,32 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a54c94417b741d3</t>
+          <t>https://www.indeed.com/viewjob?jk=a5c63e693a3dd615</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Financial Services</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,32 +6061,32 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9586c99c5eb6653</t>
+          <t>https://www.indeed.com/viewjob?jk=91abed51133c7c23</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,32 +6096,32 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37f9f241665f8f25</t>
+          <t>https://www.indeed.com/viewjob?jk=432b655803995623</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,32 +6131,32 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd06f296c307d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=04006a1fe4e66850</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,32 +6166,32 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4297244e8d171dc</t>
+          <t>https://www.indeed.com/viewjob?jk=4786e7810dfbd42c</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Financial Services</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6201,32 +6201,32 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6fbdbfa7f478c1e</t>
+          <t>https://www.indeed.com/viewjob?jk=a73d9c78e32edfcb</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,32 +6236,32 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0759cd4fbd6bdac8</t>
+          <t>https://www.indeed.com/viewjob?jk=f6e14d6ec4b8aeb0</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Financial Services</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,32 +6271,32 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94317beda0e6b715</t>
+          <t>https://www.indeed.com/viewjob?jk=f49fd486a1470d4a</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,32 +6306,32 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b8ceabdc300636a</t>
+          <t>https://www.indeed.com/viewjob?jk=bb0d75494367b7de</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,32 +6341,32 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=822d767e26112ada</t>
+          <t>https://www.indeed.com/viewjob?jk=3194fbbe9c9c6915</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Healthcare &amp; Life Sciences</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,32 +6376,32 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81b64f7562795fab</t>
+          <t>https://www.indeed.com/viewjob?jk=28e73925baaee988</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - AI Natives Business</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,32 +6411,32 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b6a8557301e33c</t>
+          <t>https://www.indeed.com/viewjob?jk=fd07d9e8d85d17ee</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Healthcare &amp; Life Sciences</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6446,32 +6446,32 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d113953416ca6dbb</t>
+          <t>https://www.indeed.com/viewjob?jk=518960648e6b46f0</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Manufacturing</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6481,32 +6481,32 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc84e05f0d0c4f9</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5b4030fed54c3d</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Financial Services</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6516,32 +6516,32 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ed17e2895f23aa</t>
+          <t>https://www.indeed.com/viewjob?jk=25174fd8817164ea</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Healthcare &amp; Life Sciences</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,32 +6551,32 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9519050e585036f9</t>
+          <t>https://www.indeed.com/viewjob?jk=69b7427915d34288</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,32 +6586,32 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22686cead31117d5</t>
+          <t>https://www.indeed.com/viewjob?jk=4964a3b46fec8c52</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Sr. Resident Solutions Architect</t>
+          <t>Cost Engineer – Data Analytics</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,32 +6621,32 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75153db402f3d420</t>
+          <t>https://www.indeed.com/viewjob?jk=69730719f6ab06e5</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
+          <t>Data Engineer / Database Management Specialist for Fish Data</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6656,67 +6656,67 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e46c18319f67321a</t>
+          <t>https://www.indeed.com/viewjob?jk=47ce35760bca7d80</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>ATI Physical Therapy</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=687bf527e281aa97</t>
+          <t>https://www.indeed.com/viewjob?jk=15f9e3e8db4c59f0</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,32 +6726,32 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64c482ee7d2fd8be</t>
+          <t>https://www.indeed.com/viewjob?jk=308aad1cd4d5b8e2</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>BI Engineer - Data Analytics</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, MongoDB, Splunk, Jenkins, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6761,32 +6761,32 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80790f8d8ef27b8d</t>
+          <t>https://www.indeed.com/viewjob?jk=ca97d35c293c8ce6</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Application Traffic team</t>
+          <t>Sr Associate Engineer, IT Software</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6796,42 +6796,42 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc893f4e11c92275</t>
+          <t>https://www.indeed.com/viewjob?jk=8fda6cb70fb70e09</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3ac436669ece2e5</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd22b9c4b47341c</t>
         </is>
       </c>
     </row>
@@ -6843,20 +6843,20 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Everbridge</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6866,32 +6866,32 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6b981d8b3e30244</t>
+          <t>https://www.indeed.com/viewjob?jk=43479a5e279bea94</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Teza Technologies</t>
+          <t>Everbridge</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6901,32 +6901,32 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8521b827213a9dde</t>
+          <t>https://www.indeed.com/viewjob?jk=9c9dce1dbceabf77</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer</t>
+          <t>Senior Software Engineer - Fullstack</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6936,32 +6936,32 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b971d4cbb76a50f0</t>
+          <t>https://www.indeed.com/viewjob?jk=3d41030c2a031bc3</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Applications New</t>
+          <t>Senior Software Engineer - Fullstack</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Temporal Technologies</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6971,164 +6971,164 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b0c42ad13150702</t>
+          <t>https://www.indeed.com/viewjob?jk=9e37bcb174213c7a</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, SharePoint</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Enlyte</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8916dfa1faff9d0</t>
+          <t>https://www.indeed.com/viewjob?jk=24937a6185650d43</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df1553e436d1437f</t>
+          <t>https://www.indeed.com/viewjob?jk=4edb47917f0e6215</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect (Databricks)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Zions Bancorporation</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Google Cloud Platform, GCP, Spark, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6b21cb550cfb29</t>
+          <t>https://www.indeed.com/viewjob?jk=e84f993a048191bd</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior BI Analyst - IGEN</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Appleton, WI, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
+          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, dbt, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22b7d0d557e5c8f6</t>
+          <t>https://www.indeed.com/viewjob?jk=acd6baf60c6afe77</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>HealthEdge</t>
+          <t>SmartAsset</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7136,34 +7136,34 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, ECS, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f2d4cc8d5ebe0f</t>
+          <t>https://www.indeed.com/viewjob?jk=4f326fc2210a7954</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Digital Enterprise DevSecOps Engineer</t>
+          <t>Senior Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Arnold AFB, TN, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7171,34 +7171,34 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9f43023d7db0b07</t>
+          <t>https://www.indeed.com/viewjob?jk=9446abbf0a9e21d5</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Senior - MLOps/LLMOps Engineer, Development</t>
+          <t>Senior Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7206,34 +7206,34 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=796c1b2eafcb17e6</t>
+          <t>https://www.indeed.com/viewjob?jk=4cf9f394fc466cab</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Thousand Oaks, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, ETL, CI/CD, Docker, Kubernetes, AKS, Git</t>
+          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -7251,24 +7251,24 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394f5e1ae2551595</t>
+          <t>https://www.indeed.com/viewjob?jk=d95d0b3cc2017278</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>AI Systems Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7276,15 +7276,2290 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=392c5b4963d57266</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Associate Data Engineer</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Insight Software</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f17a3a493c5baa0</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Gesa Credit Union</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Spokane Valley, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05b11f37b58c06df</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Gesa Credit Union</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Renton, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e166dda8b8fb2c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Gesa Credit Union</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Richland, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38d66edddd66e10c</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89dd9964d8bd40d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Youth Villages</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Chesterfield, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db40921aad59c33b</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09edda39b98ef300</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b96821caf0970503</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc42c2a4e5140f69</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66e65258ac69fefd</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7b8c309e1dd4b82</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f98038822e26dd8</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a55ba7ce9c7c4713</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85557e4da3ee4405</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4c9edfc26a261dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc933305859d57b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18e6b1969d6c7210</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d7e1d701408b5626</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=288dfb7ead95495d</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6fa85911435d672d</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9b1c071eb4265fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16f343db215cfb2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c44c288bccc8a6a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=211ece43a6639e15</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=117b69fc0cf106cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a31df839c27886a</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2e202fe647fc8c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c1275067df0fefc</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b046a816c53c475</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d0dcc0f31186adf</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26a73c1c18e4feb1</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c162c04d00001e41</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d72aa3d302823165</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=437542252a94a7bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1db9b5fd4ad91c79</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c338c18f5cc8b343</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b85cee4884732fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87011ec9083a8b23</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1d4cefa45bd4112</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66e3413d7b223f3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f780ced93a3bc16</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a4ad2ff105c8b83</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=430e2adbc8757712</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43daf093c3246e39</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90d2c0b1b77db71f</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db8c787399aa7569</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afd791e19de5a0fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e23b8b93066067d</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa821c9250f94164</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f15f76b6c67bbdd</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Cloud Security Engineer, Sr</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Old National Bank</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Lake Elmo, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, DynamoDB, CI/CD, Terraform, AKS</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3c3aa33c043a7bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Senior Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3ac436669ece2e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Application Traffic team</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc893f4e11c92275</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Database Architect</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>McKesson</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Event Hubs, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64c482ee7d2fd8be</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Zoom Communications</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6b981d8b3e30244</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Teza Technologies</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8521b827213a9dde</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Alight Solutions</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b971d4cbb76a50f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Cloud Applications New</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Temporal Technologies</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b0c42ad13150702</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, SharePoint</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Suffolk Construction</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8916dfa1faff9d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>BlackLine</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22b7d0d557e5c8f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>HealthEdge</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80f2d4cc8d5ebe0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Digital Enterprise DevSecOps Engineer</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>BNH</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Arnold AFB, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, Python</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9f43023d7db0b07</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Ai Architect</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Five Below</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45b842ee858dea9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Sr. Solutions Engineer - AI Natives Business</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d884fcaeec353d16</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>AI Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Suffolk Construction</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
           <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr">
+      <c r="F261" t="inlineStr">
         <is>
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr">
+      <c r="G261" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=16c48102f3cbafa7</t>
         </is>

--- a/results/job_matches_2026-05-30.xlsx
+++ b/results/job_matches_2026-05-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G261"/>
+  <dimension ref="A1:G237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,130 +573,130 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer - Archimedes</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, clustering keys, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3ddd82b2a383f38</t>
+          <t>https://www.indeed.com/viewjob?jk=100ea499e9e2ee80</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer - Archimedes</t>
+          <t>Full Stack Developer / AI Focused</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>CarParts.com</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=197d18130a300324</t>
+          <t>https://www.indeed.com/viewjob?jk=c61c6b86bc3293d8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Sr. Data Modeler</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Republic Services</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, clustering keys, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, RDS, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100ea499e9e2ee80</t>
+          <t>https://www.indeed.com/viewjob?jk=633c48c04bec794a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full Stack Developer / AI Focused</t>
+          <t>Cloud &amp; Digital Platform DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CarParts.com</t>
+          <t>Diality</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61c6b86bc3293d8</t>
+          <t>https://www.indeed.com/viewjob?jk=905414e7ceb13800</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Data Modeler</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Republic Services</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, RDS, Medallion Architecture, Spark</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Splunk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633c48c04bec794a</t>
+          <t>https://www.indeed.com/viewjob?jk=7d54cb6fb55273d2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud &amp; Digital Platform DevSecOps Engineer</t>
+          <t>Solutions Architect - Platform, Cloud Infrastructure and Security</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Diality</t>
+          <t>SunnyData</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905414e7ceb13800</t>
+          <t>https://www.indeed.com/viewjob?jk=47aa02c81d1c7a60</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer III - Big Data</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>Sightview Software</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Splunk</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d54cb6fb55273d2</t>
+          <t>https://www.indeed.com/viewjob?jk=102fc288fbb9abdd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Databricks Administrator</t>
+          <t>Cloud Engineer - DevOps</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Avnet</t>
+          <t>Innovative Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4012204380caba1</t>
+          <t>https://www.indeed.com/viewjob?jk=521ed8a47e56a014</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Solutions Architect - Platform, Cloud Infrastructure and Security</t>
+          <t>Senior Data Engineer - IGEN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SunnyData</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Appleton, WI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47aa02c81d1c7a60</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0ca36351ff88fb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sightview Software</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
+          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102fc288fbb9abdd</t>
+          <t>https://www.indeed.com/viewjob?jk=330bf279fb8cd838</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cloud Engineer - DevOps</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Innovative Solutions</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Spark, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521ed8a47e56a014</t>
+          <t>https://www.indeed.com/viewjob?jk=0761c7021676d118</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - IGEN</t>
+          <t>Informatica Product Owner - Remote</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0ca36351ff88fb</t>
+          <t>https://www.indeed.com/viewjob?jk=1cd40cf715d1757e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Informatica Product Owner - Remote</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330bf279fb8cd838</t>
+          <t>https://www.indeed.com/viewjob?jk=c3efe7a4e50700ee</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Informatica Product Owner - Remote</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Alachua, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Spark, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0761c7021676d118</t>
+          <t>https://www.indeed.com/viewjob?jk=3185efffc8151880</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bar Harbor, ME, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cd40cf715d1757e</t>
+          <t>https://www.indeed.com/viewjob?jk=b53f7ddb0026dea4</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3efe7a4e50700ee</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf3b9815a50b381</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alachua, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3185efffc8151880</t>
+          <t>https://www.indeed.com/viewjob?jk=d0769674b72ae58f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bar Harbor, ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b53f7ddb0026dea4</t>
+          <t>https://www.indeed.com/viewjob?jk=aef1c5cf0ee00174</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Data Architect - Remote</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,67 +1231,67 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf3b9815a50b381</t>
+          <t>https://www.indeed.com/viewjob?jk=4c32603ea351f9bf</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Solutions Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bc40683645d5866</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd4faeed9a50a59</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Kafka, PostgreSQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0769674b72ae58f</t>
+          <t>https://www.indeed.com/viewjob?jk=17cb9776bd0e7f4a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Sr Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aef1c5cf0ee00174</t>
+          <t>https://www.indeed.com/viewjob?jk=1bcc3fe3fd715833</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Solutions Architect</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd4faeed9a50a59</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd2d99f50f24a3c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Architect - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c32603ea351f9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=c250c7540d478f32</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Kafka, PostgreSQL, MongoDB, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cb9776bd0e7f4a</t>
+          <t>https://www.indeed.com/viewjob?jk=a88dfb056c5c3b9b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Infrastructure</t>
+          <t>Data Platform Engineer- 6 Month Assignment</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT, MLflow</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bcc3fe3fd715833</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5d273dd8b89dfc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>Aptean</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd2d99f50f24a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=13c44a8aef4fd0a0</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Aptean</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1558bff9d1119b05</t>
+          <t>https://www.indeed.com/viewjob?jk=ef802648dc8c758d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Decagon</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c250c7540d478f32</t>
+          <t>https://www.indeed.com/viewjob?jk=d3d218109f5a2e7c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>Senior Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>Decagon</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a88dfb056c5c3b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=cb96afd07bcd39f3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Platform Engineer- 6 Month Assignment</t>
+          <t>Platform Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>Happy Returns, Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5d273dd8b89dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa757e1e92cc3c3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. DevOps Engineer- Snowflake &amp; Azure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Aptean</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13c44a8aef4fd0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=763fd8f53ea47c3f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Aptean</t>
+          <t>Echo Global Logistics</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,242 +1721,242 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef802648dc8c758d</t>
+          <t>https://www.indeed.com/viewjob?jk=eae8bcb49c9597d5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Boston, MA</t>
+          <t>Data Engineer (Agent Systems)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Faraday Future</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>S3, RDS, BigQuery, Spark, Kafka, Snowflake, PostgreSQL, MySQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf91e3de3b3cfaa</t>
+          <t>https://www.indeed.com/viewjob?jk=3701c804c9b0b189</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Temple, TX</t>
+          <t>Cloud &amp; Digital Platform Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Diality</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02502cf23954a80e</t>
+          <t>https://www.indeed.com/viewjob?jk=7fe3f1dbc64665df</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Las Vegas, NV</t>
+          <t>Sr. Solutions Architect - Emerging</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71a6429c12809608</t>
+          <t>https://www.indeed.com/viewjob?jk=7afdce6cf8faaddf</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Dallas, TX</t>
+          <t>Sr. Solutions Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94942178e7603ad0</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ce1a2957006a72</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Fort Meyers, FL</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>MAGNETO &amp; DIESEL INJECTOR SERVICE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fort Myers, FL, US USA</t>
+          <t>Humble, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hive, Sqoop, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1119ddab775a5553</t>
+          <t>https://www.indeed.com/viewjob?jk=d19cafe12d10dcef</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Site AI Engineer - USVI</t>
+          <t>Sr. Systems Engineer- Cloud Infrastructure Engineering</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte Amalie, VI, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2dcedc535de31f7</t>
+          <t>https://www.indeed.com/viewjob?jk=4de6e8c6244caa58</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Infrastructure</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Decagon</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3d218109f5a2e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=3be471e01eea2f2a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Infrastructure</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Decagon</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb96afd07bcd39f3</t>
+          <t>https://www.indeed.com/viewjob?jk=bb8f91201caafc33</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Platform Software Engineer (Remote)</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Happy Returns, Inc.</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Data Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa757e1e92cc3c3</t>
+          <t>https://www.indeed.com/viewjob?jk=29a68b9b44071451</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer- Snowflake &amp; Azure</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763fd8f53ea47c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=34d8a92dff07ca15</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Azure Full Stack Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Echo Global Logistics</t>
+          <t>Hiro Talent Solutions</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, GCP, Scala, NoSQL</t>
+          <t>RDS, Azure, Blob Storage, Scala, Power BI, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae8bcb49c9597d5</t>
+          <t>https://www.indeed.com/viewjob?jk=c770b1c4f512c431</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer (Agent Systems)</t>
+          <t>Senior Software Engineer - Infrastructure and Tools</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Faraday Future</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>S3, RDS, BigQuery, Spark, Kafka, Snowflake, PostgreSQL, MySQL, dbt, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,102 +2141,102 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3701c804c9b0b189</t>
+          <t>https://www.indeed.com/viewjob?jk=92d9bf233ed60118</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cloud &amp; Digital Platform Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Diality</t>
+          <t>First Command Financial Services</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS</t>
+          <t>RDS, Data Factory, Scala, Oracle, SQL Server, NoSQL, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fe3f1dbc64665df</t>
+          <t>https://www.indeed.com/viewjob?jk=5a2bba3746f32469</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>AI Engineer/Solution Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Frontwave Credit Union</t>
+          <t>andrew morgan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddd8dc23d0848aec</t>
+          <t>https://www.indeed.com/viewjob?jk=7604b89af99ba406</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Emerging</t>
+          <t>Software Engineer II - Full Stack Java</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7afdce6cf8faaddf</t>
+          <t>https://www.indeed.com/viewjob?jk=2c274b0f05e69603</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer</t>
+          <t>Cloud Data Architect (Full-time Remote, NC Based)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Alliance Health Plan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,59 +2281,59 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ce1a2957006a72</t>
+          <t>https://www.indeed.com/viewjob?jk=8cb114578f5bf1e9</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Software Engineer, Product Foundations</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
+          <t>AWS, SQS, IAM, RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f0a0dc2930f694</t>
+          <t>https://www.indeed.com/viewjob?jk=dd2bfc17d54981e1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Product Foundations</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MAGNETO &amp; DIESEL INJECTOR SERVICE</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Humble, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hive, Sqoop, Spark, Scala, ETL, ELT</t>
+          <t>AWS, SQS, IAM, RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d19cafe12d10dcef</t>
+          <t>https://www.indeed.com/viewjob?jk=0277abc185dfb7c6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer- Cloud Infrastructure Engineering</t>
+          <t>Software Engineer 4</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Castlight</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de6e8c6244caa58</t>
+          <t>https://www.indeed.com/viewjob?jk=3ce519e36124f5ab</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Full Stack Developer -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be471e01eea2f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=adcfd5cf564b5b00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb8f91201caafc33</t>
+          <t>https://www.indeed.com/viewjob?jk=8f9b9650d1bc3a54</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a68b9b44071451</t>
+          <t>https://www.indeed.com/viewjob?jk=efb82b07adb9feba</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d8a92dff07ca15</t>
+          <t>https://www.indeed.com/viewjob?jk=65195644bb1b9e0b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Azure Full Stack Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Hiro Talent Solutions</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Scala, Power BI, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c770b1c4f512c431</t>
+          <t>https://www.indeed.com/viewjob?jk=75e8ade515a41a57</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Infrastructure and Tools</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92d9bf233ed60118</t>
+          <t>https://www.indeed.com/viewjob?jk=859e82cabfb17666</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Engineer/Solution Architect</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>andrew morgan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, NoSQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f828ea2a58e520b1</t>
+          <t>https://www.indeed.com/viewjob?jk=f143b13efb8ce9b6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer II - Full Stack Java</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c274b0f05e69603</t>
+          <t>https://www.indeed.com/viewjob?jk=5a031b4964c2a255</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cloud Data Architect (Full-time Remote, NC Based)</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Alliance Health Plan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cb114578f5bf1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=c4349cc4f94a5d87</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI Engineer/Solution Architect</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>andrew morgan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, NoSQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7604b89af99ba406</t>
+          <t>https://www.indeed.com/viewjob?jk=e66448573f4489d1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Product Foundations</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd2bfc17d54981e1</t>
+          <t>https://www.indeed.com/viewjob?jk=ddbf7440ad773888</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Product Foundations</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0277abc185dfb7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=b72f3a18139b7e54</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer 4</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Castlight</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ce519e36124f5ab</t>
+          <t>https://www.indeed.com/viewjob?jk=7467917f2474b2e9</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full Stack Developer -In office, Alpharetta, GA</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd5cf564b5b00</t>
+          <t>https://www.indeed.com/viewjob?jk=741f313dfe0a4767</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer 4</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Castlight</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5023cf7cd4ba777</t>
+          <t>https://www.indeed.com/viewjob?jk=fb549dda19deb4df</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f9b9650d1bc3a54</t>
+          <t>https://www.indeed.com/viewjob?jk=ad53455736c94aa1</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb82b07adb9feba</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf96d3e5672d2dd</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65195644bb1b9e0b</t>
+          <t>https://www.indeed.com/viewjob?jk=a2abd6bece93c89e</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e8ade515a41a57</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7b4a6316115547</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859e82cabfb17666</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef2a2c6485dc8ce</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f143b13efb8ce9b6</t>
+          <t>https://www.indeed.com/viewjob?jk=f8777195f0640326</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a031b4964c2a255</t>
+          <t>https://www.indeed.com/viewjob?jk=8b251c80469648dc</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4349cc4f94a5d87</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad5e6a6c6033f66</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66448573f4489d1</t>
+          <t>https://www.indeed.com/viewjob?jk=4439501b54b34a7a</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddbf7440ad773888</t>
+          <t>https://www.indeed.com/viewjob?jk=1151c815185cd79e</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b72f3a18139b7e54</t>
+          <t>https://www.indeed.com/viewjob?jk=d6614c39234b9da2</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7467917f2474b2e9</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7e23c7f438f8c8</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=741f313dfe0a4767</t>
+          <t>https://www.indeed.com/viewjob?jk=e8663ead75611c2e</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb549dda19deb4df</t>
+          <t>https://www.indeed.com/viewjob?jk=51de78e580811e18</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad53455736c94aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=548feeaa37b8c916</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf96d3e5672d2dd</t>
+          <t>https://www.indeed.com/viewjob?jk=9cf7d70224611ecc</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2abd6bece93c89e</t>
+          <t>https://www.indeed.com/viewjob?jk=08e283453e85139f</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7b4a6316115547</t>
+          <t>https://www.indeed.com/viewjob?jk=ecaa2a1fd433f4a4</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef2a2c6485dc8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=dd01c10e73409cc8</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8777195f0640326</t>
+          <t>https://www.indeed.com/viewjob?jk=3166241cc8c62f5d</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b251c80469648dc</t>
+          <t>https://www.indeed.com/viewjob?jk=1572589542133e74</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad5e6a6c6033f66</t>
+          <t>https://www.indeed.com/viewjob?jk=a2ec3f9f81325aa0</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4439501b54b34a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=492f0c5d5b1026f4</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1151c815185cd79e</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5a1bf124fcc939</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6614c39234b9da2</t>
+          <t>https://www.indeed.com/viewjob?jk=e7780a9fb7958201</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7e23c7f438f8c8</t>
+          <t>https://www.indeed.com/viewjob?jk=fd18a128a4672b91</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8663ead75611c2e</t>
+          <t>https://www.indeed.com/viewjob?jk=ea676aaaba70e2d7</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51de78e580811e18</t>
+          <t>https://www.indeed.com/viewjob?jk=cab3ba747ce4a550</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=548feeaa37b8c916</t>
+          <t>https://www.indeed.com/viewjob?jk=d65e39a595440fab</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cf7d70224611ecc</t>
+          <t>https://www.indeed.com/viewjob?jk=55cb9c48e2f72a54</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e283453e85139f</t>
+          <t>https://www.indeed.com/viewjob?jk=b3a01b8449781d9b</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecaa2a1fd433f4a4</t>
+          <t>https://www.indeed.com/viewjob?jk=5fa7561c868d2097</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd01c10e73409cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=3a729d7eaa711e20</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3166241cc8c62f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=1f022796cfb8fbcc</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1572589542133e74</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c33b5572cf45fa</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2ec3f9f81325aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=8762f88f61ad7223</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=492f0c5d5b1026f4</t>
+          <t>https://www.indeed.com/viewjob?jk=efdfb03d10f7ec00</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Forward Deployed Data Engineer Expert</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5a1bf124fcc939</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1f104bd0b18db7</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Irvington, NY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7780a9fb7958201</t>
+          <t>https://www.indeed.com/viewjob?jk=a189ac16e1f72f61</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Senior Software Engineer - Distributed Data Systems</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd18a128a4672b91</t>
+          <t>https://www.indeed.com/viewjob?jk=68f494d2abfb9b3a</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Senior Software Engineer - Distributed Data Systems</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea676aaaba70e2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=35301f7890450ed0</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Senior Software Engineer - Distributed Data Systems</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab3ba747ce4a550</t>
+          <t>https://www.indeed.com/viewjob?jk=f178ac0bdca2782a</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Senior Associate, Data Analytics Engineering</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Options Clearing Corporation</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65e39a595440fab</t>
+          <t>https://www.indeed.com/viewjob?jk=1ad61eb5cd2a5633</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Fabletics</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55cb9c48e2f72a54</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac7bdb141d55008</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>DevOps Engineer, II</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NRCCUA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3a01b8449781d9b</t>
+          <t>https://www.indeed.com/viewjob?jk=e257db597eccae8d</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>DevOps Engineer, II</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Encoura</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,67 +4521,67 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fa7561c868d2097</t>
+          <t>https://www.indeed.com/viewjob?jk=22172251f6a1ea83</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Uber Freight</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Scala, Kafka, Oracle, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a729d7eaa711e20</t>
+          <t>https://www.indeed.com/viewjob?jk=1b1465e42f01feff</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Senior Software Engineer - Fullstack</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f022796cfb8fbcc</t>
+          <t>https://www.indeed.com/viewjob?jk=6e1d5edd7f6cfacc</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Sr. Solutions Engineer - GSI's and FinTech Data</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c33b5572cf45fa</t>
+          <t>https://www.indeed.com/viewjob?jk=44ec35e1f7566eb4</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Sr. Solutions Engineer - Financial Services (Insurance)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8762f88f61ad7223</t>
+          <t>https://www.indeed.com/viewjob?jk=df17d8e1960c7150</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Sr. Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdfb03d10f7ec00</t>
+          <t>https://www.indeed.com/viewjob?jk=ae7ce0b79b127907</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer Expert</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1f104bd0b18db7</t>
+          <t>https://www.indeed.com/viewjob?jk=dc99c4d09fcc8c74</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Irvington, NY, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a189ac16e1f72f61</t>
+          <t>https://www.indeed.com/viewjob?jk=a2644095339b05a5</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer Expert</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Mimecast</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, S3, SQS, RDS, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc3130fd4a42b451</t>
+          <t>https://www.indeed.com/viewjob?jk=ca736f22eed6fef2</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Distributed Data Systems</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f494d2abfb9b3a</t>
+          <t>https://www.indeed.com/viewjob?jk=b7994c3eb46bae42</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Distributed Data Systems</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35301f7890450ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=649242ee28a33ae5</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Distributed Data Systems</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,32 +4906,32 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f178ac0bdca2782a</t>
+          <t>https://www.indeed.com/viewjob?jk=4b46b87f1359f8f5</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Analytics Engineering</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Options Clearing Corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, dbt, Tableau, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,32 +4941,32 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ad61eb5cd2a5633</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a7b9a70e68cf9f</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Fabletics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,32 +4976,32 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac7bdb141d55008</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a148e3a41849d9</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>DevOps Engineer, II</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>NRCCUA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,32 +5011,32 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e257db597eccae8d</t>
+          <t>https://www.indeed.com/viewjob?jk=fa4b4fcc410a503a</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>DevOps Engineer, II</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Encoura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,32 +5046,32 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22172251f6a1ea83</t>
+          <t>https://www.indeed.com/viewjob?jk=6147a561d729a0dd</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Fullstack</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,172 +5081,172 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e1d5edd7f6cfacc</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab5bc5f32a7b9a0</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (React, JavaScript, .net)</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Hagerstown, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, Data Modeling, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc464898e64c2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=29f309b16d064eae</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior AI Full Stack Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=825e221841f6b0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=f0b6e4cc0b843bf8</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AI Automation Developer II</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Yale New Haven Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Stratford, CT, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b4f3e15b0e54b1c</t>
+          <t>https://www.indeed.com/viewjob?jk=9d739c3bc7cf38d1</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Engineering Specialist</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35e60c72e365c000</t>
+          <t>https://www.indeed.com/viewjob?jk=70aa889c4c9efda8</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - GSI's and FinTech Data</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,32 +5256,32 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44ec35e1f7566eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=97557fcc3403a036</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Financial Services (Insurance)</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df17d8e1960c7150</t>
+          <t>https://www.indeed.com/viewjob?jk=01009226e788120d</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae7ce0b79b127907</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b0eb4fb08e6514</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc99c4d09fcc8c74</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7b1778e389048a</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2644095339b05a5</t>
+          <t>https://www.indeed.com/viewjob?jk=a5c63e693a3dd615</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Mimecast</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca736f22eed6fef2</t>
+          <t>https://www.indeed.com/viewjob?jk=91abed51133c7c23</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7994c3eb46bae42</t>
+          <t>https://www.indeed.com/viewjob?jk=432b655803995623</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=649242ee28a33ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=04006a1fe4e66850</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b46b87f1359f8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=4786e7810dfbd42c</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a7b9a70e68cf9f</t>
+          <t>https://www.indeed.com/viewjob?jk=a73d9c78e32edfcb</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a148e3a41849d9</t>
+          <t>https://www.indeed.com/viewjob?jk=f6e14d6ec4b8aeb0</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa4b4fcc410a503a</t>
+          <t>https://www.indeed.com/viewjob?jk=f49fd486a1470d4a</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6147a561d729a0dd</t>
+          <t>https://www.indeed.com/viewjob?jk=bb0d75494367b7de</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab5bc5f32a7b9a0</t>
+          <t>https://www.indeed.com/viewjob?jk=3194fbbe9c9c6915</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29f309b16d064eae</t>
+          <t>https://www.indeed.com/viewjob?jk=28e73925baaee988</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0b6e4cc0b843bf8</t>
+          <t>https://www.indeed.com/viewjob?jk=fd07d9e8d85d17ee</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d739c3bc7cf38d1</t>
+          <t>https://www.indeed.com/viewjob?jk=518960648e6b46f0</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70aa889c4c9efda8</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5b4030fed54c3d</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97557fcc3403a036</t>
+          <t>https://www.indeed.com/viewjob?jk=25174fd8817164ea</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01009226e788120d</t>
+          <t>https://www.indeed.com/viewjob?jk=69b7427915d34288</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b0eb4fb08e6514</t>
+          <t>https://www.indeed.com/viewjob?jk=4964a3b46fec8c52</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Cost Engineer – Data Analytics</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7b1778e389048a</t>
+          <t>https://www.indeed.com/viewjob?jk=69730719f6ab06e5</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Data Engineer / Database Management Specialist for Fish Data</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5c63e693a3dd615</t>
+          <t>https://www.indeed.com/viewjob?jk=47ce35760bca7d80</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ATI Physical Therapy</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,34 +6051,34 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91abed51133c7c23</t>
+          <t>https://www.indeed.com/viewjob?jk=15f9e3e8db4c59f0</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432b655803995623</t>
+          <t>https://www.indeed.com/viewjob?jk=308aad1cd4d5b8e2</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Sr Associate Engineer, IT Software</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,24 +6131,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04006a1fe4e66850</t>
+          <t>https://www.indeed.com/viewjob?jk=8fda6cb70fb70e09</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,24 +6166,24 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4786e7810dfbd42c</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd22b9c4b47341c</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Software Engineer - Fullstack</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6201,24 +6201,24 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a73d9c78e32edfcb</t>
+          <t>https://www.indeed.com/viewjob?jk=3d41030c2a031bc3</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Software Engineer - Fullstack</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,24 +6236,24 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6e14d6ec4b8aeb0</t>
+          <t>https://www.indeed.com/viewjob?jk=9e37bcb174213c7a</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f49fd486a1470d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=4edb47917f0e6215</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb0d75494367b7de</t>
+          <t>https://www.indeed.com/viewjob?jk=e84f993a048191bd</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior BI Analyst - IGEN</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Appleton, WI, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, dbt, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,24 +6341,24 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3194fbbe9c9c6915</t>
+          <t>https://www.indeed.com/viewjob?jk=acd6baf60c6afe77</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>BI Engineer - Data Analytics</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,32 +6376,32 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e73925baaee988</t>
+          <t>https://www.indeed.com/viewjob?jk=ca97d35c293c8ce6</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SmartAsset</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, ECS, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,32 +6411,32 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd07d9e8d85d17ee</t>
+          <t>https://www.indeed.com/viewjob?jk=4f326fc2210a7954</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6446,32 +6446,32 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518960648e6b46f0</t>
+          <t>https://www.indeed.com/viewjob?jk=9446abbf0a9e21d5</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6481,102 +6481,102 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5b4030fed54c3d</t>
+          <t>https://www.indeed.com/viewjob?jk=4cf9f394fc466cab</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25174fd8817164ea</t>
+          <t>https://www.indeed.com/viewjob?jk=53279f54b14e6849</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b7427915d34288</t>
+          <t>https://www.indeed.com/viewjob?jk=0a92d266fe841f72</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,32 +6586,32 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4964a3b46fec8c52</t>
+          <t>https://www.indeed.com/viewjob?jk=0fb0b209468363aa</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Cost Engineer – Data Analytics</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Insight Software</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,32 +6621,32 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69730719f6ab06e5</t>
+          <t>https://www.indeed.com/viewjob?jk=4f17a3a493c5baa0</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Data Engineer / Database Management Specialist for Fish Data</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
+          <t>Gesa Credit Union</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Spokane Valley, WA, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6656,67 +6656,67 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ce35760bca7d80</t>
+          <t>https://www.indeed.com/viewjob?jk=05b11f37b58c06df</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ATI Physical Therapy</t>
+          <t>Gesa Credit Union</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f9e3e8db4c59f0</t>
+          <t>https://www.indeed.com/viewjob?jk=9e166dda8b8fb2c2</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Gesa Credit Union</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Richland, WA, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,32 +6726,32 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aad1cd4d5b8e2</t>
+          <t>https://www.indeed.com/viewjob?jk=38d66edddd66e10c</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>BI Engineer - Data Analytics</t>
+          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6761,32 +6761,32 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca97d35c293c8ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=89dd9964d8bd40d3</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Youth Villages</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chesterfield, VA, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6796,32 +6796,32 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fda6cb70fb70e09</t>
+          <t>https://www.indeed.com/viewjob?jk=db40921aad59c33b</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6831,32 +6831,32 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd22b9c4b47341c</t>
+          <t>https://www.indeed.com/viewjob?jk=b96821caf0970503</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Software Engineer - Shared Services</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Everbridge</t>
+          <t>HeroDevs</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6866,32 +6866,32 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43479a5e279bea94</t>
+          <t>https://www.indeed.com/viewjob?jk=6847e3d78dab687e</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Everbridge</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6901,32 +6901,32 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c9dce1dbceabf77</t>
+          <t>https://www.indeed.com/viewjob?jk=cc42c2a4e5140f69</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Fullstack</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6936,32 +6936,32 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d41030c2a031bc3</t>
+          <t>https://www.indeed.com/viewjob?jk=66e65258ac69fefd</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Fullstack</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6971,67 +6971,67 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e37bcb174213c7a</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b8c309e1dd4b82</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Enlyte</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24937a6185650d43</t>
+          <t>https://www.indeed.com/viewjob?jk=3f98038822e26dd8</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7041,19 +7041,19 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4edb47917f0e6215</t>
+          <t>https://www.indeed.com/viewjob?jk=a55ba7ce9c7c4713</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7062,11 +7062,11 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e84f993a048191bd</t>
+          <t>https://www.indeed.com/viewjob?jk=85557e4da3ee4405</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Senior BI Analyst - IGEN</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, dbt, Power BI, Tableau, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -7111,24 +7111,24 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd6baf60c6afe77</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c9edfc26a261dd</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>SmartAsset</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -7146,24 +7146,24 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f326fc2210a7954</t>
+          <t>https://www.indeed.com/viewjob?jk=bc933305859d57b2</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -7181,24 +7181,24 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9446abbf0a9e21d5</t>
+          <t>https://www.indeed.com/viewjob?jk=18e6b1969d6c7210</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -7216,24 +7216,24 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cf9f394fc466cab</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e1d701408b5626</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7241,34 +7241,34 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d95d0b3cc2017278</t>
+          <t>https://www.indeed.com/viewjob?jk=288dfb7ead95495d</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7276,34 +7276,34 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=392c5b4963d57266</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa85911435d672d</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Insight Software</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -7321,24 +7321,24 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f17a3a493c5baa0</t>
+          <t>https://www.indeed.com/viewjob?jk=d9b1c071eb4265fc</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spokane Valley, WA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -7356,24 +7356,24 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b11f37b58c06df</t>
+          <t>https://www.indeed.com/viewjob?jk=16f343db215cfb2f</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -7391,24 +7391,24 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e166dda8b8fb2c2</t>
+          <t>https://www.indeed.com/viewjob?jk=c44c288bccc8a6a7</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Richland, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -7426,24 +7426,24 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38d66edddd66e10c</t>
+          <t>https://www.indeed.com/viewjob?jk=211ece43a6639e15</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -7461,24 +7461,24 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89dd9964d8bd40d3</t>
+          <t>https://www.indeed.com/viewjob?jk=117b69fc0cf106cd</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Youth Villages</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Chesterfield, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -7496,24 +7496,24 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db40921aad59c33b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a31df839c27886a</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -7531,24 +7531,24 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09edda39b98ef300</t>
+          <t>https://www.indeed.com/viewjob?jk=c2e202fe647fc8c9</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b96821caf0970503</t>
+          <t>https://www.indeed.com/viewjob?jk=7c1275067df0fefc</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc42c2a4e5140f69</t>
+          <t>https://www.indeed.com/viewjob?jk=0b046a816c53c475</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66e65258ac69fefd</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0dcc0f31186adf</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b8c309e1dd4b82</t>
+          <t>https://www.indeed.com/viewjob?jk=26a73c1c18e4feb1</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f98038822e26dd8</t>
+          <t>https://www.indeed.com/viewjob?jk=c162c04d00001e41</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a55ba7ce9c7c4713</t>
+          <t>https://www.indeed.com/viewjob?jk=d72aa3d302823165</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85557e4da3ee4405</t>
+          <t>https://www.indeed.com/viewjob?jk=437542252a94a7bd</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c9edfc26a261dd</t>
+          <t>https://www.indeed.com/viewjob?jk=1db9b5fd4ad91c79</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc933305859d57b2</t>
+          <t>https://www.indeed.com/viewjob?jk=c338c18f5cc8b343</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18e6b1969d6c7210</t>
+          <t>https://www.indeed.com/viewjob?jk=9b85cee4884732fd</t>
         </is>
       </c>
     </row>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e1d701408b5626</t>
+          <t>https://www.indeed.com/viewjob?jk=87011ec9083a8b23</t>
         </is>
       </c>
     </row>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=288dfb7ead95495d</t>
+          <t>https://www.indeed.com/viewjob?jk=c1d4cefa45bd4112</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fa85911435d672d</t>
+          <t>https://www.indeed.com/viewjob?jk=66e3413d7b223f3a</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9b1c071eb4265fc</t>
+          <t>https://www.indeed.com/viewjob?jk=5f780ced93a3bc16</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f343db215cfb2f</t>
+          <t>https://www.indeed.com/viewjob?jk=5a4ad2ff105c8b83</t>
         </is>
       </c>
     </row>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44c288bccc8a6a7</t>
+          <t>https://www.indeed.com/viewjob?jk=430e2adbc8757712</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211ece43a6639e15</t>
+          <t>https://www.indeed.com/viewjob?jk=43daf093c3246e39</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117b69fc0cf106cd</t>
+          <t>https://www.indeed.com/viewjob?jk=90d2c0b1b77db71f</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a31df839c27886a</t>
+          <t>https://www.indeed.com/viewjob?jk=db8c787399aa7569</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2e202fe647fc8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=afd791e19de5a0fe</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c1275067df0fefc</t>
+          <t>https://www.indeed.com/viewjob?jk=1e23b8b93066067d</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8283,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b046a816c53c475</t>
+          <t>https://www.indeed.com/viewjob?jk=aa821c9250f94164</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -8336,24 +8336,24 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0dcc0f31186adf</t>
+          <t>https://www.indeed.com/viewjob?jk=8f15f76b6c67bbdd</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>DevOps Engineer - Mid</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nalley Consulting</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -8371,24 +8371,24 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26a73c1c18e4feb1</t>
+          <t>https://www.indeed.com/viewjob?jk=35023775c057de52</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -8396,34 +8396,34 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c162c04d00001e41</t>
+          <t>https://www.indeed.com/viewjob?jk=c3ac436669ece2e5</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Senior Software Engineer - Application Traffic team</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -8441,24 +8441,24 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72aa3d302823165</t>
+          <t>https://www.indeed.com/viewjob?jk=dc893f4e11c92275</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Event Hubs, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -8476,24 +8476,24 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=437542252a94a7bd</t>
+          <t>https://www.indeed.com/viewjob?jk=64c482ee7d2fd8be</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -8511,24 +8511,24 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1db9b5fd4ad91c79</t>
+          <t>https://www.indeed.com/viewjob?jk=a6b981d8b3e30244</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Teza Technologies</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -8546,24 +8546,24 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c338c18f5cc8b343</t>
+          <t>https://www.indeed.com/viewjob?jk=8521b827213a9dde</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -8581,24 +8581,24 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b85cee4884732fd</t>
+          <t>https://www.indeed.com/viewjob?jk=b971d4cbb76a50f0</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Senior Software Engineer, Cloud Applications New</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Temporal Technologies</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -8616,24 +8616,24 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87011ec9083a8b23</t>
+          <t>https://www.indeed.com/viewjob?jk=6b0c42ad13150702</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Digital Enterprise DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Arnold AFB, TN, US USA</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -8641,34 +8641,34 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1d4cefa45bd4112</t>
+          <t>https://www.indeed.com/viewjob?jk=a9f43023d7db0b07</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Ai Architect</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -8686,24 +8686,24 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66e3413d7b223f3a</t>
+          <t>https://www.indeed.com/viewjob?jk=45b842ee858dea9c</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Sr. Solutions Engineer - AI Natives Business</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -8721,847 +8721,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f780ced93a3bc16</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D238" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a4ad2ff105c8b83</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D239" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=430e2adbc8757712</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D240" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=43daf093c3246e39</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D241" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90d2c0b1b77db71f</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D242" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db8c787399aa7569</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D243" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=afd791e19de5a0fe</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>Costa Mesa, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D244" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1e23b8b93066067d</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>New Orleans, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D245" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa821c9250f94164</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D246" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f15f76b6c67bbdd</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>Cloud Security Engineer, Sr</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>Old National Bank</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>Lake Elmo, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D247" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, DynamoDB, CI/CD, Terraform, AKS</t>
-        </is>
-      </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c3aa33c043a7bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>Senior Applied AI Engineer</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D248" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c3ac436669ece2e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Application Traffic team</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>Mountain View, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D249" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow</t>
-        </is>
-      </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc893f4e11c92275</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>Database Architect</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>McKesson</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D250" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Event Hubs, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=64c482ee7d2fd8be</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>Zoom Communications</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D251" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a6b981d8b3e30244</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>Teza Technologies</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D252" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8521b827213a9dde</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>Alight Solutions</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D253" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b971d4cbb76a50f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Cloud Applications New</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>Temporal Technologies</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D254" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Kafka, PostgreSQL</t>
-        </is>
-      </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6b0c42ad13150702</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, SharePoint</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>Suffolk Construction</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D255" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e8916dfa1faff9d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>BlackLine</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>Pleasanton, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D256" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
-        </is>
-      </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=22b7d0d557e5c8f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>HealthEdge</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D257" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80f2d4cc8d5ebe0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>Digital Enterprise DevSecOps Engineer</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>BNH</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>Arnold AFB, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D258" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a9f43023d7db0b07</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>Ai Architect</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Five Below</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D259" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=45b842ee858dea9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>Sr. Solutions Engineer - AI Natives Business</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D260" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
-        </is>
-      </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=d884fcaeec353d16</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>AI Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>Suffolk Construction</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D261" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
-        </is>
-      </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16c48102f3cbafa7</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-30.xlsx
+++ b/results/job_matches_2026-05-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G237"/>
+  <dimension ref="A1:G234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Architect - Remote</t>
+          <t>Senior Data Solutions Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c32603ea351f9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd4faeed9a50a59</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Solutions Architect</t>
+          <t>Data Architect - Remote</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd4faeed9a50a59</t>
+          <t>https://www.indeed.com/viewjob?jk=4c32603ea351f9bf</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Engineer/Solution Architect</t>
+          <t>Software Engineer II - Full Stack Java</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>andrew morgan</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7604b89af99ba406</t>
+          <t>https://www.indeed.com/viewjob?jk=2c274b0f05e69603</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer II - Full Stack Java</t>
+          <t>Cloud Data Architect (Full-time Remote, NC Based)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Alliance Health Plan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c274b0f05e69603</t>
+          <t>https://www.indeed.com/viewjob?jk=8cb114578f5bf1e9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud Data Architect (Full-time Remote, NC Based)</t>
+          <t>AI Engineer/Solution Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Alliance Health Plan</t>
+          <t>andrew morgan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cb114578f5bf1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=7604b89af99ba406</t>
         </is>
       </c>
     </row>
@@ -6033,17 +6033,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ATI Physical Therapy</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,34 +6051,34 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f9e3e8db4c59f0</t>
+          <t>https://www.indeed.com/viewjob?jk=308aad1cd4d5b8e2</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Sr Associate Engineer, IT Software</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,14 +6096,14 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aad1cd4d5b8e2</t>
+          <t>https://www.indeed.com/viewjob?jk=8fda6cb70fb70e09</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer, IT Software</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,24 +6131,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fda6cb70fb70e09</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd22b9c4b47341c</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Software Engineer - Fullstack</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd22b9c4b47341c</t>
+          <t>https://www.indeed.com/viewjob?jk=3d41030c2a031bc3</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,24 +6201,24 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d41030c2a031bc3</t>
+          <t>https://www.indeed.com/viewjob?jk=9e37bcb174213c7a</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Fullstack</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e37bcb174213c7a</t>
+          <t>https://www.indeed.com/viewjob?jk=4edb47917f0e6215</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4edb47917f0e6215</t>
+          <t>https://www.indeed.com/viewjob?jk=e84f993a048191bd</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior BI Analyst - IGEN</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Appleton, WI, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, dbt, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e84f993a048191bd</t>
+          <t>https://www.indeed.com/viewjob?jk=acd6baf60c6afe77</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Senior BI Analyst - IGEN</t>
+          <t>BI Engineer - Data Analytics</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, dbt, Power BI, Tableau, Git</t>
+          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,32 +6341,32 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd6baf60c6afe77</t>
+          <t>https://www.indeed.com/viewjob?jk=ca97d35c293c8ce6</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>BI Engineer - Data Analytics</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>SmartAsset</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
+          <t>AWS, ECS, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,24 +6376,24 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca97d35c293c8ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=4f326fc2210a7954</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Senior Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>SmartAsset</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f326fc2210a7954</t>
+          <t>https://www.indeed.com/viewjob?jk=9446abbf0a9e21d5</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,24 +6446,24 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9446abbf0a9e21d5</t>
+          <t>https://www.indeed.com/viewjob?jk=4cf9f394fc466cab</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,17 +6471,17 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cf9f394fc466cab</t>
+          <t>https://www.indeed.com/viewjob?jk=53279f54b14e6849</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,24 +6516,24 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53279f54b14e6849</t>
+          <t>https://www.indeed.com/viewjob?jk=0a92d266fe841f72</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Insight Software</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,34 +6541,34 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a92d266fe841f72</t>
+          <t>https://www.indeed.com/viewjob?jk=4f17a3a493c5baa0</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Gesa Credit Union</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Spokane Valley, WA, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,24 +6586,24 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fb0b209468363aa</t>
+          <t>https://www.indeed.com/viewjob?jk=05b11f37b58c06df</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Insight Software</t>
+          <t>Gesa Credit Union</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f17a3a493c5baa0</t>
+          <t>https://www.indeed.com/viewjob?jk=9e166dda8b8fb2c2</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spokane Valley, WA, US USA</t>
+          <t>Richland, WA, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,24 +6656,24 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b11f37b58c06df</t>
+          <t>https://www.indeed.com/viewjob?jk=38d66edddd66e10c</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6691,24 +6691,24 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e166dda8b8fb2c2</t>
+          <t>https://www.indeed.com/viewjob?jk=89dd9964d8bd40d3</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>Youth Villages</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Richland, WA, US USA</t>
+          <t>Chesterfield, VA, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,24 +6726,24 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38d66edddd66e10c</t>
+          <t>https://www.indeed.com/viewjob?jk=db40921aad59c33b</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6761,24 +6761,24 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89dd9964d8bd40d3</t>
+          <t>https://www.indeed.com/viewjob?jk=b96821caf0970503</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer - Shared Services</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Youth Villages</t>
+          <t>HeroDevs</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Chesterfield, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6796,24 +6796,24 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db40921aad59c33b</t>
+          <t>https://www.indeed.com/viewjob?jk=6847e3d78dab687e</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6831,24 +6831,24 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b96821caf0970503</t>
+          <t>https://www.indeed.com/viewjob?jk=cc42c2a4e5140f69</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Shared Services</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>HeroDevs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6847e3d78dab687e</t>
+          <t>https://www.indeed.com/viewjob?jk=66e65258ac69fefd</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc42c2a4e5140f69</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b8c309e1dd4b82</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66e65258ac69fefd</t>
+          <t>https://www.indeed.com/viewjob?jk=3f98038822e26dd8</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b8c309e1dd4b82</t>
+          <t>https://www.indeed.com/viewjob?jk=a55ba7ce9c7c4713</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f98038822e26dd8</t>
+          <t>https://www.indeed.com/viewjob?jk=85557e4da3ee4405</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a55ba7ce9c7c4713</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c9edfc26a261dd</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85557e4da3ee4405</t>
+          <t>https://www.indeed.com/viewjob?jk=bc933305859d57b2</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c9edfc26a261dd</t>
+          <t>https://www.indeed.com/viewjob?jk=18e6b1969d6c7210</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc933305859d57b2</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e1d701408b5626</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18e6b1969d6c7210</t>
+          <t>https://www.indeed.com/viewjob?jk=288dfb7ead95495d</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e1d701408b5626</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa85911435d672d</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=288dfb7ead95495d</t>
+          <t>https://www.indeed.com/viewjob?jk=d9b1c071eb4265fc</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fa85911435d672d</t>
+          <t>https://www.indeed.com/viewjob?jk=16f343db215cfb2f</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9b1c071eb4265fc</t>
+          <t>https://www.indeed.com/viewjob?jk=c44c288bccc8a6a7</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f343db215cfb2f</t>
+          <t>https://www.indeed.com/viewjob?jk=211ece43a6639e15</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44c288bccc8a6a7</t>
+          <t>https://www.indeed.com/viewjob?jk=117b69fc0cf106cd</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211ece43a6639e15</t>
+          <t>https://www.indeed.com/viewjob?jk=3a31df839c27886a</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117b69fc0cf106cd</t>
+          <t>https://www.indeed.com/viewjob?jk=c2e202fe647fc8c9</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a31df839c27886a</t>
+          <t>https://www.indeed.com/viewjob?jk=7c1275067df0fefc</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2e202fe647fc8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=0b046a816c53c475</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c1275067df0fefc</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0dcc0f31186adf</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b046a816c53c475</t>
+          <t>https://www.indeed.com/viewjob?jk=26a73c1c18e4feb1</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0dcc0f31186adf</t>
+          <t>https://www.indeed.com/viewjob?jk=c162c04d00001e41</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26a73c1c18e4feb1</t>
+          <t>https://www.indeed.com/viewjob?jk=d72aa3d302823165</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c162c04d00001e41</t>
+          <t>https://www.indeed.com/viewjob?jk=437542252a94a7bd</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72aa3d302823165</t>
+          <t>https://www.indeed.com/viewjob?jk=1db9b5fd4ad91c79</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=437542252a94a7bd</t>
+          <t>https://www.indeed.com/viewjob?jk=c338c18f5cc8b343</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1db9b5fd4ad91c79</t>
+          <t>https://www.indeed.com/viewjob?jk=9b85cee4884732fd</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c338c18f5cc8b343</t>
+          <t>https://www.indeed.com/viewjob?jk=87011ec9083a8b23</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b85cee4884732fd</t>
+          <t>https://www.indeed.com/viewjob?jk=c1d4cefa45bd4112</t>
         </is>
       </c>
     </row>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87011ec9083a8b23</t>
+          <t>https://www.indeed.com/viewjob?jk=66e3413d7b223f3a</t>
         </is>
       </c>
     </row>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1d4cefa45bd4112</t>
+          <t>https://www.indeed.com/viewjob?jk=5f780ced93a3bc16</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66e3413d7b223f3a</t>
+          <t>https://www.indeed.com/viewjob?jk=5a4ad2ff105c8b83</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f780ced93a3bc16</t>
+          <t>https://www.indeed.com/viewjob?jk=430e2adbc8757712</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a4ad2ff105c8b83</t>
+          <t>https://www.indeed.com/viewjob?jk=43daf093c3246e39</t>
         </is>
       </c>
     </row>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=430e2adbc8757712</t>
+          <t>https://www.indeed.com/viewjob?jk=90d2c0b1b77db71f</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43daf093c3246e39</t>
+          <t>https://www.indeed.com/viewjob?jk=db8c787399aa7569</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d2c0b1b77db71f</t>
+          <t>https://www.indeed.com/viewjob?jk=afd791e19de5a0fe</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db8c787399aa7569</t>
+          <t>https://www.indeed.com/viewjob?jk=1e23b8b93066067d</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd791e19de5a0fe</t>
+          <t>https://www.indeed.com/viewjob?jk=aa821c9250f94164</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -8266,24 +8266,24 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e23b8b93066067d</t>
+          <t>https://www.indeed.com/viewjob?jk=8f15f76b6c67bbdd</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>DevOps Engineer - Mid</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nalley Consulting</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -8301,24 +8301,24 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa821c9250f94164</t>
+          <t>https://www.indeed.com/viewjob?jk=35023775c057de52</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -8326,34 +8326,34 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f15f76b6c67bbdd</t>
+          <t>https://www.indeed.com/viewjob?jk=c3ac436669ece2e5</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Mid</t>
+          <t>Senior Software Engineer - Application Traffic team</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Nalley Consulting</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -8371,24 +8371,24 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35023775c057de52</t>
+          <t>https://www.indeed.com/viewjob?jk=dc893f4e11c92275</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -8396,34 +8396,34 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Event Hubs, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3ac436669ece2e5</t>
+          <t>https://www.indeed.com/viewjob?jk=64c482ee7d2fd8be</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Application Traffic team</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -8441,24 +8441,24 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc893f4e11c92275</t>
+          <t>https://www.indeed.com/viewjob?jk=a6b981d8b3e30244</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Teza Technologies</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -8476,24 +8476,24 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64c482ee7d2fd8be</t>
+          <t>https://www.indeed.com/viewjob?jk=8521b827213a9dde</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -8511,24 +8511,24 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6b981d8b3e30244</t>
+          <t>https://www.indeed.com/viewjob?jk=b971d4cbb76a50f0</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer, Cloud Applications New</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Teza Technologies</t>
+          <t>Temporal Technologies</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -8546,24 +8546,24 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8521b827213a9dde</t>
+          <t>https://www.indeed.com/viewjob?jk=6b0c42ad13150702</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer</t>
+          <t>Ai Architect</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -8581,24 +8581,24 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b971d4cbb76a50f0</t>
+          <t>https://www.indeed.com/viewjob?jk=45b842ee858dea9c</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Applications New</t>
+          <t>Sr. Solutions Engineer - AI Natives Business</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Temporal Technologies</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -8615,111 +8615,6 @@
         </is>
       </c>
       <c r="G234" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6b0c42ad13150702</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>Digital Enterprise DevSecOps Engineer</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>BNH</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>Arnold AFB, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D235" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a9f43023d7db0b07</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>Ai Architect</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Five Below</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D236" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=45b842ee858dea9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>Sr. Solutions Engineer - AI Natives Business</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D237" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d884fcaeec353d16</t>
         </is>

--- a/results/job_matches_2026-05-30.xlsx
+++ b/results/job_matches_2026-05-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G234"/>
+  <dimension ref="A1:G233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer with AI/ML</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c250c7540d478f32</t>
+          <t>https://www.indeed.com/viewjob?jk=836bfed93aa23557</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a88dfb056c5c3b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=c250c7540d478f32</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Platform Engineer- 6 Month Assignment</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5d273dd8b89dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=a88dfb056c5c3b9b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer- 6 Month Assignment</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aptean</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13c44a8aef4fd0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5d273dd8b89dfc</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef802648dc8c758d</t>
+          <t>https://www.indeed.com/viewjob?jk=13c44a8aef4fd0a0</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Decagon</t>
+          <t>Aptean</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3d218109f5a2e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=ef802648dc8c758d</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb96afd07bcd39f3</t>
+          <t>https://www.indeed.com/viewjob?jk=d3d218109f5a2e7c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Platform Software Engineer (Remote)</t>
+          <t>Senior Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Happy Returns, Inc.</t>
+          <t>Decagon</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Data Modeling</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa757e1e92cc3c3</t>
+          <t>https://www.indeed.com/viewjob?jk=cb96afd07bcd39f3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer- Snowflake &amp; Azure</t>
+          <t>Platform Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Happy Returns, Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763fd8f53ea47c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa757e1e92cc3c3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. DevOps Engineer- Snowflake &amp; Azure</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Echo Global Logistics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, GCP, Scala, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae8bcb49c9597d5</t>
+          <t>https://www.indeed.com/viewjob?jk=763fd8f53ea47c3f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer (Agent Systems)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Faraday Future</t>
+          <t>Echo Global Logistics</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>S3, RDS, BigQuery, Spark, Kafka, Snowflake, PostgreSQL, MySQL, dbt, CI/CD</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3701c804c9b0b189</t>
+          <t>https://www.indeed.com/viewjob?jk=eae8bcb49c9597d5</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Azure Full Stack Engineer</t>
+          <t>Senior Software Engineer - Infrastructure and Tools</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Hiro Talent Solutions</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Scala, Power BI, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c770b1c4f512c431</t>
+          <t>https://www.indeed.com/viewjob?jk=92d9bf233ed60118</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Infrastructure and Tools</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>First Command Financial Services</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow</t>
+          <t>RDS, Data Factory, Scala, Oracle, SQL Server, NoSQL, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92d9bf233ed60118</t>
+          <t>https://www.indeed.com/viewjob?jk=5a2bba3746f32469</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Sales Engineer, Commercial</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>First Command Financial Services</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Scala, Oracle, SQL Server, NoSQL, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a2bba3746f32469</t>
+          <t>https://www.indeed.com/viewjob?jk=0487f884b026bec9</t>
         </is>
       </c>
     </row>
@@ -6733,17 +6733,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr. Software Engineer - Shared Services</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>HeroDevs</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6761,24 +6761,24 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b96821caf0970503</t>
+          <t>https://www.indeed.com/viewjob?jk=6847e3d78dab687e</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Shared Services</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>HeroDevs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6847e3d78dab687e</t>
+          <t>https://www.indeed.com/viewjob?jk=cc42c2a4e5140f69</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc42c2a4e5140f69</t>
+          <t>https://www.indeed.com/viewjob?jk=66e65258ac69fefd</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66e65258ac69fefd</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b8c309e1dd4b82</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b8c309e1dd4b82</t>
+          <t>https://www.indeed.com/viewjob?jk=3f98038822e26dd8</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f98038822e26dd8</t>
+          <t>https://www.indeed.com/viewjob?jk=a55ba7ce9c7c4713</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a55ba7ce9c7c4713</t>
+          <t>https://www.indeed.com/viewjob?jk=85557e4da3ee4405</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85557e4da3ee4405</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c9edfc26a261dd</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c9edfc26a261dd</t>
+          <t>https://www.indeed.com/viewjob?jk=bc933305859d57b2</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc933305859d57b2</t>
+          <t>https://www.indeed.com/viewjob?jk=18e6b1969d6c7210</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18e6b1969d6c7210</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e1d701408b5626</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e1d701408b5626</t>
+          <t>https://www.indeed.com/viewjob?jk=288dfb7ead95495d</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=288dfb7ead95495d</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa85911435d672d</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fa85911435d672d</t>
+          <t>https://www.indeed.com/viewjob?jk=d9b1c071eb4265fc</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9b1c071eb4265fc</t>
+          <t>https://www.indeed.com/viewjob?jk=16f343db215cfb2f</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f343db215cfb2f</t>
+          <t>https://www.indeed.com/viewjob?jk=c44c288bccc8a6a7</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44c288bccc8a6a7</t>
+          <t>https://www.indeed.com/viewjob?jk=211ece43a6639e15</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211ece43a6639e15</t>
+          <t>https://www.indeed.com/viewjob?jk=117b69fc0cf106cd</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117b69fc0cf106cd</t>
+          <t>https://www.indeed.com/viewjob?jk=3a31df839c27886a</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a31df839c27886a</t>
+          <t>https://www.indeed.com/viewjob?jk=c2e202fe647fc8c9</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2e202fe647fc8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=7c1275067df0fefc</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c1275067df0fefc</t>
+          <t>https://www.indeed.com/viewjob?jk=0b046a816c53c475</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b046a816c53c475</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0dcc0f31186adf</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0dcc0f31186adf</t>
+          <t>https://www.indeed.com/viewjob?jk=26a73c1c18e4feb1</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26a73c1c18e4feb1</t>
+          <t>https://www.indeed.com/viewjob?jk=c162c04d00001e41</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c162c04d00001e41</t>
+          <t>https://www.indeed.com/viewjob?jk=d72aa3d302823165</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72aa3d302823165</t>
+          <t>https://www.indeed.com/viewjob?jk=437542252a94a7bd</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=437542252a94a7bd</t>
+          <t>https://www.indeed.com/viewjob?jk=1db9b5fd4ad91c79</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1db9b5fd4ad91c79</t>
+          <t>https://www.indeed.com/viewjob?jk=c338c18f5cc8b343</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c338c18f5cc8b343</t>
+          <t>https://www.indeed.com/viewjob?jk=9b85cee4884732fd</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b85cee4884732fd</t>
+          <t>https://www.indeed.com/viewjob?jk=87011ec9083a8b23</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87011ec9083a8b23</t>
+          <t>https://www.indeed.com/viewjob?jk=c1d4cefa45bd4112</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1d4cefa45bd4112</t>
+          <t>https://www.indeed.com/viewjob?jk=66e3413d7b223f3a</t>
         </is>
       </c>
     </row>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66e3413d7b223f3a</t>
+          <t>https://www.indeed.com/viewjob?jk=5f780ced93a3bc16</t>
         </is>
       </c>
     </row>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f780ced93a3bc16</t>
+          <t>https://www.indeed.com/viewjob?jk=5a4ad2ff105c8b83</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a4ad2ff105c8b83</t>
+          <t>https://www.indeed.com/viewjob?jk=430e2adbc8757712</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=430e2adbc8757712</t>
+          <t>https://www.indeed.com/viewjob?jk=43daf093c3246e39</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43daf093c3246e39</t>
+          <t>https://www.indeed.com/viewjob?jk=90d2c0b1b77db71f</t>
         </is>
       </c>
     </row>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d2c0b1b77db71f</t>
+          <t>https://www.indeed.com/viewjob?jk=db8c787399aa7569</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db8c787399aa7569</t>
+          <t>https://www.indeed.com/viewjob?jk=afd791e19de5a0fe</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd791e19de5a0fe</t>
+          <t>https://www.indeed.com/viewjob?jk=1e23b8b93066067d</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e23b8b93066067d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa821c9250f94164</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -8231,24 +8231,24 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa821c9250f94164</t>
+          <t>https://www.indeed.com/viewjob?jk=8f15f76b6c67bbdd</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>DevOps Engineer - Mid</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nalley Consulting</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -8266,24 +8266,24 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f15f76b6c67bbdd</t>
+          <t>https://www.indeed.com/viewjob?jk=35023775c057de52</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Mid</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Nalley Consulting</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -8291,34 +8291,34 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35023775c057de52</t>
+          <t>https://www.indeed.com/viewjob?jk=c3ac436669ece2e5</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Senior Software Engineer - Application Traffic team</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -8326,34 +8326,34 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3ac436669ece2e5</t>
+          <t>https://www.indeed.com/viewjob?jk=dc893f4e11c92275</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Application Traffic team</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow</t>
+          <t>RDS, Azure, Event Hubs, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -8371,24 +8371,24 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc893f4e11c92275</t>
+          <t>https://www.indeed.com/viewjob?jk=64c482ee7d2fd8be</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -8406,24 +8406,24 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64c482ee7d2fd8be</t>
+          <t>https://www.indeed.com/viewjob?jk=a6b981d8b3e30244</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Teza Technologies</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -8441,24 +8441,24 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6b981d8b3e30244</t>
+          <t>https://www.indeed.com/viewjob?jk=8521b827213a9dde</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Teza Technologies</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -8476,24 +8476,24 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8521b827213a9dde</t>
+          <t>https://www.indeed.com/viewjob?jk=b971d4cbb76a50f0</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer</t>
+          <t>Senior Software Engineer, Cloud Applications New</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>Temporal Technologies</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -8511,24 +8511,24 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b971d4cbb76a50f0</t>
+          <t>https://www.indeed.com/viewjob?jk=6b0c42ad13150702</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Applications New</t>
+          <t>Ai Architect</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Temporal Technologies</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -8546,24 +8546,24 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b0c42ad13150702</t>
+          <t>https://www.indeed.com/viewjob?jk=45b842ee858dea9c</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Ai Architect</t>
+          <t>Sr. Solutions Engineer - AI Natives Business</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -8580,41 +8580,6 @@
         </is>
       </c>
       <c r="G233" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=45b842ee858dea9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>Sr. Solutions Engineer - AI Natives Business</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D234" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d884fcaeec353d16</t>
         </is>

--- a/results/job_matches_2026-05-30.xlsx
+++ b/results/job_matches_2026-05-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G233"/>
+  <dimension ref="A1:G214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Solutions Architect - Platform, Cloud Infrastructure and Security</t>
+          <t>Databricks Administrator</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SunnyData</t>
+          <t>Avnet</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47aa02c81d1c7a60</t>
+          <t>https://www.indeed.com/viewjob?jk=e4012204380caba1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data</t>
+          <t>Solutions Architect - Platform, Cloud Infrastructure and Security</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sightview Software</t>
+          <t>SunnyData</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102fc288fbb9abdd</t>
+          <t>https://www.indeed.com/viewjob?jk=47aa02c81d1c7a60</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Engineer - DevOps</t>
+          <t>Software Engineer III - Big Data</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Innovative Solutions</t>
+          <t>Sightview Software</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521ed8a47e56a014</t>
+          <t>https://www.indeed.com/viewjob?jk=102fc288fbb9abdd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - IGEN</t>
+          <t>Cloud Engineer - DevOps</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>Innovative Solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0ca36351ff88fb</t>
+          <t>https://www.indeed.com/viewjob?jk=521ed8a47e56a014</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - IGEN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Appleton, WI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330bf279fb8cd838</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0ca36351ff88fb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Spark, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0761c7021676d118</t>
+          <t>https://www.indeed.com/viewjob?jk=330bf279fb8cd838</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Spark, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cd40cf715d1757e</t>
+          <t>https://www.indeed.com/viewjob?jk=0761c7021676d118</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3efe7a4e50700ee</t>
+          <t>https://www.indeed.com/viewjob?jk=1cd40cf715d1757e</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alachua, FL, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3185efffc8151880</t>
+          <t>https://www.indeed.com/viewjob?jk=c3efe7a4e50700ee</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bar Harbor, ME, US USA</t>
+          <t>Alachua, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b53f7ddb0026dea4</t>
+          <t>https://www.indeed.com/viewjob?jk=3185efffc8151880</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Bar Harbor, ME, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf3b9815a50b381</t>
+          <t>https://www.indeed.com/viewjob?jk=b53f7ddb0026dea4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Informatica Product Owner - Remote</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0769674b72ae58f</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf3b9815a50b381</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Data Solutions Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aef1c5cf0ee00174</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd4faeed9a50a59</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Solutions Architect</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd4faeed9a50a59</t>
+          <t>https://www.indeed.com/viewjob?jk=d0769674b72ae58f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Architect - Remote</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c32603ea351f9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=aef1c5cf0ee00174</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Infrastructure</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,59 +1336,59 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bcc3fe3fd715833</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd2d99f50f24a3c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
+          <t>Data Engineer with AI/ML</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd2d99f50f24a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=836bfed93aa23557</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer with AI/ML</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=836bfed93aa23557</t>
+          <t>https://www.indeed.com/viewjob?jk=c250c7540d478f32</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform Engineer- 6 Month Assignment</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c250c7540d478f32</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5d273dd8b89dfc</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>Aptean</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a88dfb056c5c3b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=13c44a8aef4fd0a0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Platform Engineer- 6 Month Assignment</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>Aptean</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5d273dd8b89dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=ef802648dc8c758d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Aptean</t>
+          <t>Decagon</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13c44a8aef4fd0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=d3d218109f5a2e7c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Aptean</t>
+          <t>Decagon</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef802648dc8c758d</t>
+          <t>https://www.indeed.com/viewjob?jk=cb96afd07bcd39f3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Infrastructure</t>
+          <t>Platform Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Decagon</t>
+          <t>Happy Returns, Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3d218109f5a2e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa757e1e92cc3c3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Infrastructure</t>
+          <t>Sr. DevOps Engineer- Snowflake &amp; Azure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Decagon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb96afd07bcd39f3</t>
+          <t>https://www.indeed.com/viewjob?jk=763fd8f53ea47c3f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Platform Software Engineer (Remote)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Happy Returns, Inc.</t>
+          <t>Echo Global Logistics</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Data Modeling</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa757e1e92cc3c3</t>
+          <t>https://www.indeed.com/viewjob?jk=eae8bcb49c9597d5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer- Snowflake &amp; Azure</t>
+          <t>Cloud &amp; Digital Platform Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Diality</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763fd8f53ea47c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=7fe3f1dbc64665df</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Echo Global Logistics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, GCP, Scala, NoSQL</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae8bcb49c9597d5</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab00f608359b4fd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud &amp; Digital Platform Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Diality</t>
+          <t>MAGNETO &amp; DIESEL INJECTOR SERVICE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Humble, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hive, Sqoop, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fe3f1dbc64665df</t>
+          <t>https://www.indeed.com/viewjob?jk=d19cafe12d10dcef</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Emerging</t>
+          <t>Sr. Systems Engineer- Cloud Infrastructure Engineering</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,59 +1826,59 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7afdce6cf8faaddf</t>
+          <t>https://www.indeed.com/viewjob?jk=4de6e8c6244caa58</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>First Command Financial Services</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>RDS, Data Factory, Scala, Oracle, SQL Server, NoSQL, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ce1a2957006a72</t>
+          <t>https://www.indeed.com/viewjob?jk=5a2bba3746f32469</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Sales Engineer, Commercial</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MAGNETO &amp; DIESEL INJECTOR SERVICE</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Humble, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hive, Sqoop, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d19cafe12d10dcef</t>
+          <t>https://www.indeed.com/viewjob?jk=0487f884b026bec9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer- Cloud Infrastructure Engineering</t>
+          <t>Software Engineer II - Full Stack Java</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de6e8c6244caa58</t>
+          <t>https://www.indeed.com/viewjob?jk=2c274b0f05e69603</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Cloud Data Architect (Full-time Remote, NC Based)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Alliance Health Plan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be471e01eea2f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=8cb114578f5bf1e9</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>AI Engineer/Solution Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>andrew morgan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb8f91201caafc33</t>
+          <t>https://www.indeed.com/viewjob?jk=7604b89af99ba406</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Senior Software Engineer, Product Foundations</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, SQS, IAM, RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a68b9b44071451</t>
+          <t>https://www.indeed.com/viewjob?jk=dd2bfc17d54981e1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Senior Software Engineer, Product Foundations</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, SQS, IAM, RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,19 +2071,19 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d8a92dff07ca15</t>
+          <t>https://www.indeed.com/viewjob?jk=0277abc185dfb7c6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Infrastructure and Tools</t>
+          <t>Software Engineer 4</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Castlight</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92d9bf233ed60118</t>
+          <t>https://www.indeed.com/viewjob?jk=3ce519e36124f5ab</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Full Stack Developer -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>First Command Financial Services</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Scala, Oracle, SQL Server, NoSQL, Data Modeling, ETL, dbt, Power BI</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a2bba3746f32469</t>
+          <t>https://www.indeed.com/viewjob?jk=adcfd5cf564b5b00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial</t>
+          <t>Software Engineer 4</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Castlight</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0487f884b026bec9</t>
+          <t>https://www.indeed.com/viewjob?jk=b5023cf7cd4ba777</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer II - Full Stack Java</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c274b0f05e69603</t>
+          <t>https://www.indeed.com/viewjob?jk=8f9b9650d1bc3a54</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud Data Architect (Full-time Remote, NC Based)</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Alliance Health Plan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cb114578f5bf1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=efb82b07adb9feba</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Engineer/Solution Architect</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>andrew morgan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, NoSQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7604b89af99ba406</t>
+          <t>https://www.indeed.com/viewjob?jk=65195644bb1b9e0b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Product Foundations</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd2bfc17d54981e1</t>
+          <t>https://www.indeed.com/viewjob?jk=75e8ade515a41a57</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Product Foundations</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0277abc185dfb7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=859e82cabfb17666</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer 4</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Castlight</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ce519e36124f5ab</t>
+          <t>https://www.indeed.com/viewjob?jk=f143b13efb8ce9b6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Full Stack Developer -In office, Alpharetta, GA</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd5cf564b5b00</t>
+          <t>https://www.indeed.com/viewjob?jk=5a031b4964c2a255</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f9b9650d1bc3a54</t>
+          <t>https://www.indeed.com/viewjob?jk=c4349cc4f94a5d87</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb82b07adb9feba</t>
+          <t>https://www.indeed.com/viewjob?jk=e66448573f4489d1</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65195644bb1b9e0b</t>
+          <t>https://www.indeed.com/viewjob?jk=ddbf7440ad773888</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e8ade515a41a57</t>
+          <t>https://www.indeed.com/viewjob?jk=b72f3a18139b7e54</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859e82cabfb17666</t>
+          <t>https://www.indeed.com/viewjob?jk=7467917f2474b2e9</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f143b13efb8ce9b6</t>
+          <t>https://www.indeed.com/viewjob?jk=741f313dfe0a4767</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a031b4964c2a255</t>
+          <t>https://www.indeed.com/viewjob?jk=fb549dda19deb4df</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4349cc4f94a5d87</t>
+          <t>https://www.indeed.com/viewjob?jk=ad53455736c94aa1</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66448573f4489d1</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf96d3e5672d2dd</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddbf7440ad773888</t>
+          <t>https://www.indeed.com/viewjob?jk=a2abd6bece93c89e</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b72f3a18139b7e54</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7b4a6316115547</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7467917f2474b2e9</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef2a2c6485dc8ce</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=741f313dfe0a4767</t>
+          <t>https://www.indeed.com/viewjob?jk=f8777195f0640326</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb549dda19deb4df</t>
+          <t>https://www.indeed.com/viewjob?jk=8b251c80469648dc</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad53455736c94aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad5e6a6c6033f66</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf96d3e5672d2dd</t>
+          <t>https://www.indeed.com/viewjob?jk=4439501b54b34a7a</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2abd6bece93c89e</t>
+          <t>https://www.indeed.com/viewjob?jk=1151c815185cd79e</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7b4a6316115547</t>
+          <t>https://www.indeed.com/viewjob?jk=d6614c39234b9da2</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef2a2c6485dc8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7e23c7f438f8c8</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8777195f0640326</t>
+          <t>https://www.indeed.com/viewjob?jk=e8663ead75611c2e</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b251c80469648dc</t>
+          <t>https://www.indeed.com/viewjob?jk=51de78e580811e18</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad5e6a6c6033f66</t>
+          <t>https://www.indeed.com/viewjob?jk=548feeaa37b8c916</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4439501b54b34a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=9cf7d70224611ecc</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1151c815185cd79e</t>
+          <t>https://www.indeed.com/viewjob?jk=08e283453e85139f</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6614c39234b9da2</t>
+          <t>https://www.indeed.com/viewjob?jk=ecaa2a1fd433f4a4</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7e23c7f438f8c8</t>
+          <t>https://www.indeed.com/viewjob?jk=dd01c10e73409cc8</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8663ead75611c2e</t>
+          <t>https://www.indeed.com/viewjob?jk=3166241cc8c62f5d</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51de78e580811e18</t>
+          <t>https://www.indeed.com/viewjob?jk=1572589542133e74</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=548feeaa37b8c916</t>
+          <t>https://www.indeed.com/viewjob?jk=a2ec3f9f81325aa0</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cf7d70224611ecc</t>
+          <t>https://www.indeed.com/viewjob?jk=492f0c5d5b1026f4</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e283453e85139f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5a1bf124fcc939</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecaa2a1fd433f4a4</t>
+          <t>https://www.indeed.com/viewjob?jk=e7780a9fb7958201</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd01c10e73409cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=fd18a128a4672b91</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3166241cc8c62f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=ea676aaaba70e2d7</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1572589542133e74</t>
+          <t>https://www.indeed.com/viewjob?jk=cab3ba747ce4a550</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2ec3f9f81325aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=d65e39a595440fab</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=492f0c5d5b1026f4</t>
+          <t>https://www.indeed.com/viewjob?jk=55cb9c48e2f72a54</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5a1bf124fcc939</t>
+          <t>https://www.indeed.com/viewjob?jk=b3a01b8449781d9b</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7780a9fb7958201</t>
+          <t>https://www.indeed.com/viewjob?jk=5fa7561c868d2097</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd18a128a4672b91</t>
+          <t>https://www.indeed.com/viewjob?jk=3a729d7eaa711e20</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea676aaaba70e2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=1f022796cfb8fbcc</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab3ba747ce4a550</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c33b5572cf45fa</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65e39a595440fab</t>
+          <t>https://www.indeed.com/viewjob?jk=8762f88f61ad7223</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55cb9c48e2f72a54</t>
+          <t>https://www.indeed.com/viewjob?jk=efdfb03d10f7ec00</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Forward Deployed Data Engineer Expert</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3a01b8449781d9b</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1f104bd0b18db7</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irvington, NY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fa7561c868d2097</t>
+          <t>https://www.indeed.com/viewjob?jk=a189ac16e1f72f61</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Senior Associate, Data Analytics Engineering</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Options Clearing Corporation</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a729d7eaa711e20</t>
+          <t>https://www.indeed.com/viewjob?jk=1ad61eb5cd2a5633</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Fabletics</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f022796cfb8fbcc</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac7bdb141d55008</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>DevOps Engineer, II</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NRCCUA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c33b5572cf45fa</t>
+          <t>https://www.indeed.com/viewjob?jk=e257db597eccae8d</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>DevOps Engineer, II</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Encoura</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,67 +4171,67 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8762f88f61ad7223</t>
+          <t>https://www.indeed.com/viewjob?jk=22172251f6a1ea83</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Uber Freight</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Scala, Kafka, Oracle, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdfb03d10f7ec00</t>
+          <t>https://www.indeed.com/viewjob?jk=1b1465e42f01feff</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer Expert</t>
+          <t>Sr. Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1f104bd0b18db7</t>
+          <t>https://www.indeed.com/viewjob?jk=ae7ce0b79b127907</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Irvington, NY, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a189ac16e1f72f61</t>
+          <t>https://www.indeed.com/viewjob?jk=dc99c4d09fcc8c74</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Distributed Data Systems</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f494d2abfb9b3a</t>
+          <t>https://www.indeed.com/viewjob?jk=a2644095339b05a5</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Distributed Data Systems</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Mimecast</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, S3, SQS, RDS, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35301f7890450ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=ca736f22eed6fef2</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Distributed Data Systems</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f178ac0bdca2782a</t>
+          <t>https://www.indeed.com/viewjob?jk=b7994c3eb46bae42</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Analytics Engineering</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Options Clearing Corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, dbt, Tableau, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ad61eb5cd2a5633</t>
+          <t>https://www.indeed.com/viewjob?jk=649242ee28a33ae5</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Fabletics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac7bdb141d55008</t>
+          <t>https://www.indeed.com/viewjob?jk=4b46b87f1359f8f5</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DevOps Engineer, II</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>NRCCUA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e257db597eccae8d</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a7b9a70e68cf9f</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DevOps Engineer, II</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Encoura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,67 +4521,67 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22172251f6a1ea83</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a148e3a41849d9</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Uber Freight</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Scala, Kafka, Oracle, CI/CD, Maven</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b1465e42f01feff</t>
+          <t>https://www.indeed.com/viewjob?jk=fa4b4fcc410a503a</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Fullstack</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e1d5edd7f6cfacc</t>
+          <t>https://www.indeed.com/viewjob?jk=6147a561d729a0dd</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - GSI's and FinTech Data</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44ec35e1f7566eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab5bc5f32a7b9a0</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Financial Services (Insurance)</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df17d8e1960c7150</t>
+          <t>https://www.indeed.com/viewjob?jk=29f309b16d064eae</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae7ce0b79b127907</t>
+          <t>https://www.indeed.com/viewjob?jk=f0b6e4cc0b843bf8</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc99c4d09fcc8c74</t>
+          <t>https://www.indeed.com/viewjob?jk=9d739c3bc7cf38d1</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,19 +4766,19 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2644095339b05a5</t>
+          <t>https://www.indeed.com/viewjob?jk=70aa889c4c9efda8</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Mimecast</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca736f22eed6fef2</t>
+          <t>https://www.indeed.com/viewjob?jk=97557fcc3403a036</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7994c3eb46bae42</t>
+          <t>https://www.indeed.com/viewjob?jk=01009226e788120d</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=649242ee28a33ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b0eb4fb08e6514</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b46b87f1359f8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7b1778e389048a</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a7b9a70e68cf9f</t>
+          <t>https://www.indeed.com/viewjob?jk=a5c63e693a3dd615</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a148e3a41849d9</t>
+          <t>https://www.indeed.com/viewjob?jk=91abed51133c7c23</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa4b4fcc410a503a</t>
+          <t>https://www.indeed.com/viewjob?jk=432b655803995623</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6147a561d729a0dd</t>
+          <t>https://www.indeed.com/viewjob?jk=04006a1fe4e66850</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab5bc5f32a7b9a0</t>
+          <t>https://www.indeed.com/viewjob?jk=4786e7810dfbd42c</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29f309b16d064eae</t>
+          <t>https://www.indeed.com/viewjob?jk=a73d9c78e32edfcb</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0b6e4cc0b843bf8</t>
+          <t>https://www.indeed.com/viewjob?jk=f6e14d6ec4b8aeb0</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d739c3bc7cf38d1</t>
+          <t>https://www.indeed.com/viewjob?jk=f49fd486a1470d4a</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70aa889c4c9efda8</t>
+          <t>https://www.indeed.com/viewjob?jk=bb0d75494367b7de</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97557fcc3403a036</t>
+          <t>https://www.indeed.com/viewjob?jk=3194fbbe9c9c6915</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01009226e788120d</t>
+          <t>https://www.indeed.com/viewjob?jk=28e73925baaee988</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b0eb4fb08e6514</t>
+          <t>https://www.indeed.com/viewjob?jk=fd07d9e8d85d17ee</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7b1778e389048a</t>
+          <t>https://www.indeed.com/viewjob?jk=518960648e6b46f0</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5c63e693a3dd615</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5b4030fed54c3d</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91abed51133c7c23</t>
+          <t>https://www.indeed.com/viewjob?jk=25174fd8817164ea</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432b655803995623</t>
+          <t>https://www.indeed.com/viewjob?jk=69b7427915d34288</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04006a1fe4e66850</t>
+          <t>https://www.indeed.com/viewjob?jk=4964a3b46fec8c52</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Cost Engineer – Data Analytics</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4786e7810dfbd42c</t>
+          <t>https://www.indeed.com/viewjob?jk=69730719f6ab06e5</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Data Engineer / Database Management Specialist for Fish Data</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a73d9c78e32edfcb</t>
+          <t>https://www.indeed.com/viewjob?jk=47ce35760bca7d80</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6e14d6ec4b8aeb0</t>
+          <t>https://www.indeed.com/viewjob?jk=308aad1cd4d5b8e2</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Sr Associate Engineer, IT Software</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f49fd486a1470d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=8fda6cb70fb70e09</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb0d75494367b7de</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd22b9c4b47341c</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3194fbbe9c9c6915</t>
+          <t>https://www.indeed.com/viewjob?jk=4edb47917f0e6215</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e73925baaee988</t>
+          <t>https://www.indeed.com/viewjob?jk=e84f993a048191bd</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>BI Engineer - Data Analytics</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,24 +5781,24 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd07d9e8d85d17ee</t>
+          <t>https://www.indeed.com/viewjob?jk=ca97d35c293c8ce6</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior BI Analyst - IGEN</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Appleton, WI, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, dbt, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,32 +5816,32 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518960648e6b46f0</t>
+          <t>https://www.indeed.com/viewjob?jk=acd6baf60c6afe77</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SmartAsset</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, ECS, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,102 +5851,102 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5b4030fed54c3d</t>
+          <t>https://www.indeed.com/viewjob?jk=4f326fc2210a7954</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25174fd8817164ea</t>
+          <t>https://www.indeed.com/viewjob?jk=53279f54b14e6849</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b7427915d34288</t>
+          <t>https://www.indeed.com/viewjob?jk=0a92d266fe841f72</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Insight Software</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,32 +5956,32 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4964a3b46fec8c52</t>
+          <t>https://www.indeed.com/viewjob?jk=4f17a3a493c5baa0</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Cost Engineer – Data Analytics</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Gesa Credit Union</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Spokane Valley, WA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,32 +5991,32 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69730719f6ab06e5</t>
+          <t>https://www.indeed.com/viewjob?jk=05b11f37b58c06df</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Data Engineer / Database Management Specialist for Fish Data</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
+          <t>Gesa Credit Union</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,32 +6026,32 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ce35760bca7d80</t>
+          <t>https://www.indeed.com/viewjob?jk=9e166dda8b8fb2c2</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Gesa Credit Union</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Richland, WA, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,32 +6061,32 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aad1cd4d5b8e2</t>
+          <t>https://www.indeed.com/viewjob?jk=38d66edddd66e10c</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer, IT Software</t>
+          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,32 +6096,32 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fda6cb70fb70e09</t>
+          <t>https://www.indeed.com/viewjob?jk=89dd9964d8bd40d3</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Youth Villages</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chesterfield, VA, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,32 +6131,32 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd22b9c4b47341c</t>
+          <t>https://www.indeed.com/viewjob?jk=db40921aad59c33b</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Fullstack</t>
+          <t>Sr. Software Engineer - Shared Services</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>HeroDevs</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,32 +6166,32 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d41030c2a031bc3</t>
+          <t>https://www.indeed.com/viewjob?jk=6847e3d78dab687e</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Fullstack</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6201,32 +6201,32 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e37bcb174213c7a</t>
+          <t>https://www.indeed.com/viewjob?jk=cc42c2a4e5140f69</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,32 +6236,32 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4edb47917f0e6215</t>
+          <t>https://www.indeed.com/viewjob?jk=66e65258ac69fefd</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,32 +6271,32 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e84f993a048191bd</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b8c309e1dd4b82</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Senior BI Analyst - IGEN</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, dbt, Power BI, Tableau, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,32 +6306,32 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd6baf60c6afe77</t>
+          <t>https://www.indeed.com/viewjob?jk=3f98038822e26dd8</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>BI Engineer - Data Analytics</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,19 +6341,19 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca97d35c293c8ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=a55ba7ce9c7c4713</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>SmartAsset</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,24 +6376,24 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f326fc2210a7954</t>
+          <t>https://www.indeed.com/viewjob?jk=85557e4da3ee4405</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,24 +6411,24 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9446abbf0a9e21d5</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c9edfc26a261dd</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6446,24 +6446,24 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cf9f394fc466cab</t>
+          <t>https://www.indeed.com/viewjob?jk=bc933305859d57b2</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,34 +6471,34 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53279f54b14e6849</t>
+          <t>https://www.indeed.com/viewjob?jk=18e6b1969d6c7210</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,34 +6506,34 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a92d266fe841f72</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e1d701408b5626</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Insight Software</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,24 +6551,24 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f17a3a493c5baa0</t>
+          <t>https://www.indeed.com/viewjob?jk=288dfb7ead95495d</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Spokane Valley, WA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,24 +6586,24 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b11f37b58c06df</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa85911435d672d</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,24 +6621,24 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e166dda8b8fb2c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d9b1c071eb4265fc</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Richland, WA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6656,24 +6656,24 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38d66edddd66e10c</t>
+          <t>https://www.indeed.com/viewjob?jk=16f343db215cfb2f</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6691,24 +6691,24 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89dd9964d8bd40d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c44c288bccc8a6a7</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Youth Villages</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Chesterfield, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,24 +6726,24 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db40921aad59c33b</t>
+          <t>https://www.indeed.com/viewjob?jk=211ece43a6639e15</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Shared Services</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>HeroDevs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6847e3d78dab687e</t>
+          <t>https://www.indeed.com/viewjob?jk=117b69fc0cf106cd</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc42c2a4e5140f69</t>
+          <t>https://www.indeed.com/viewjob?jk=3a31df839c27886a</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66e65258ac69fefd</t>
+          <t>https://www.indeed.com/viewjob?jk=c2e202fe647fc8c9</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b8c309e1dd4b82</t>
+          <t>https://www.indeed.com/viewjob?jk=7c1275067df0fefc</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f98038822e26dd8</t>
+          <t>https://www.indeed.com/viewjob?jk=0b046a816c53c475</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a55ba7ce9c7c4713</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0dcc0f31186adf</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85557e4da3ee4405</t>
+          <t>https://www.indeed.com/viewjob?jk=26a73c1c18e4feb1</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c9edfc26a261dd</t>
+          <t>https://www.indeed.com/viewjob?jk=c162c04d00001e41</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc933305859d57b2</t>
+          <t>https://www.indeed.com/viewjob?jk=d72aa3d302823165</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18e6b1969d6c7210</t>
+          <t>https://www.indeed.com/viewjob?jk=437542252a94a7bd</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e1d701408b5626</t>
+          <t>https://www.indeed.com/viewjob?jk=1db9b5fd4ad91c79</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=288dfb7ead95495d</t>
+          <t>https://www.indeed.com/viewjob?jk=c338c18f5cc8b343</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fa85911435d672d</t>
+          <t>https://www.indeed.com/viewjob?jk=9b85cee4884732fd</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9b1c071eb4265fc</t>
+          <t>https://www.indeed.com/viewjob?jk=87011ec9083a8b23</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f343db215cfb2f</t>
+          <t>https://www.indeed.com/viewjob?jk=c1d4cefa45bd4112</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44c288bccc8a6a7</t>
+          <t>https://www.indeed.com/viewjob?jk=66e3413d7b223f3a</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211ece43a6639e15</t>
+          <t>https://www.indeed.com/viewjob?jk=5f780ced93a3bc16</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117b69fc0cf106cd</t>
+          <t>https://www.indeed.com/viewjob?jk=5a4ad2ff105c8b83</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a31df839c27886a</t>
+          <t>https://www.indeed.com/viewjob?jk=430e2adbc8757712</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2e202fe647fc8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=43daf093c3246e39</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c1275067df0fefc</t>
+          <t>https://www.indeed.com/viewjob?jk=90d2c0b1b77db71f</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b046a816c53c475</t>
+          <t>https://www.indeed.com/viewjob?jk=db8c787399aa7569</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0dcc0f31186adf</t>
+          <t>https://www.indeed.com/viewjob?jk=afd791e19de5a0fe</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26a73c1c18e4feb1</t>
+          <t>https://www.indeed.com/viewjob?jk=1e23b8b93066067d</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c162c04d00001e41</t>
+          <t>https://www.indeed.com/viewjob?jk=aa821c9250f94164</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7636,24 +7636,24 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72aa3d302823165</t>
+          <t>https://www.indeed.com/viewjob?jk=8f15f76b6c67bbdd</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>DevOps Engineer - Mid</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nalley Consulting</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -7671,24 +7671,24 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=437542252a94a7bd</t>
+          <t>https://www.indeed.com/viewjob?jk=35023775c057de52</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Event Hubs, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -7706,24 +7706,24 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1db9b5fd4ad91c79</t>
+          <t>https://www.indeed.com/viewjob?jk=64c482ee7d2fd8be</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -7741,24 +7741,24 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c338c18f5cc8b343</t>
+          <t>https://www.indeed.com/viewjob?jk=a6b981d8b3e30244</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Teza Technologies</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -7776,24 +7776,24 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b85cee4884732fd</t>
+          <t>https://www.indeed.com/viewjob?jk=8521b827213a9dde</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -7811,24 +7811,24 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87011ec9083a8b23</t>
+          <t>https://www.indeed.com/viewjob?jk=b971d4cbb76a50f0</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Senior Software Engineer, Cloud Applications New</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Temporal Technologies</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -7846,24 +7846,24 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1d4cefa45bd4112</t>
+          <t>https://www.indeed.com/viewjob?jk=6b0c42ad13150702</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7871,34 +7871,34 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66e3413d7b223f3a</t>
+          <t>https://www.indeed.com/viewjob?jk=c3ac436669ece2e5</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Ai Architect</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -7916,672 +7916,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f780ced93a3bc16</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D215" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a4ad2ff105c8b83</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D216" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=430e2adbc8757712</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D217" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=43daf093c3246e39</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D218" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90d2c0b1b77db71f</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D219" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db8c787399aa7569</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D220" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=afd791e19de5a0fe</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Costa Mesa, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D221" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1e23b8b93066067d</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>New Orleans, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D222" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa821c9250f94164</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D223" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f15f76b6c67bbdd</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>DevOps Engineer - Mid</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Nalley Consulting</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Doral, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D224" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35023775c057de52</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>Senior Applied AI Engineer</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D225" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c3ac436669ece2e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Application Traffic team</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Mountain View, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D226" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc893f4e11c92275</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>Database Architect</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>McKesson</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D227" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Event Hubs, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=64c482ee7d2fd8be</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>Zoom Communications</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D228" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a6b981d8b3e30244</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Teza Technologies</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D229" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8521b827213a9dde</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Alight Solutions</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D230" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b971d4cbb76a50f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Cloud Applications New</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Temporal Technologies</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D231" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Kafka, PostgreSQL</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6b0c42ad13150702</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>Ai Architect</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>Five Below</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D232" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=45b842ee858dea9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>Sr. Solutions Engineer - AI Natives Business</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D233" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
-        </is>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d884fcaeec353d16</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-30.xlsx
+++ b/results/job_matches_2026-05-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G214"/>
+  <dimension ref="A1:G212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Data Modeler</t>
+          <t>Cloud &amp; Digital Platform DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Republic Services</t>
+          <t>Diality</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, RDS, Medallion Architecture, Spark</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633c48c04bec794a</t>
+          <t>https://www.indeed.com/viewjob?jk=905414e7ceb13800</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud &amp; Digital Platform DevSecOps Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Diality</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Splunk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905414e7ceb13800</t>
+          <t>https://www.indeed.com/viewjob?jk=7d54cb6fb55273d2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Databricks Administrator</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>Avnet</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d54cb6fb55273d2</t>
+          <t>https://www.indeed.com/viewjob?jk=e4012204380caba1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Databricks Administrator</t>
+          <t>Solutions Architect - Platform, Cloud Infrastructure and Security</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Avnet</t>
+          <t>SunnyData</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4012204380caba1</t>
+          <t>https://www.indeed.com/viewjob?jk=47aa02c81d1c7a60</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Solutions Architect - Platform, Cloud Infrastructure and Security</t>
+          <t>Software Engineer III - Big Data</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SunnyData</t>
+          <t>Sightview Software</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47aa02c81d1c7a60</t>
+          <t>https://www.indeed.com/viewjob?jk=102fc288fbb9abdd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data</t>
+          <t>Cloud Engineer - DevOps</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sightview Software</t>
+          <t>Innovative Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102fc288fbb9abdd</t>
+          <t>https://www.indeed.com/viewjob?jk=521ed8a47e56a014</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud Engineer - DevOps</t>
+          <t>Senior Data Engineer - IGEN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Innovative Solutions</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Appleton, WI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521ed8a47e56a014</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0ca36351ff88fb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - IGEN</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
+          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0ca36351ff88fb</t>
+          <t>https://www.indeed.com/viewjob?jk=330bf279fb8cd838</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Spark, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330bf279fb8cd838</t>
+          <t>https://www.indeed.com/viewjob?jk=0761c7021676d118</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Informatica Product Owner - Remote</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Spark, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0761c7021676d118</t>
+          <t>https://www.indeed.com/viewjob?jk=1cd40cf715d1757e</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cd40cf715d1757e</t>
+          <t>https://www.indeed.com/viewjob?jk=c3efe7a4e50700ee</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Alachua, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3efe7a4e50700ee</t>
+          <t>https://www.indeed.com/viewjob?jk=3185efffc8151880</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alachua, FL, US USA</t>
+          <t>Bar Harbor, ME, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3185efffc8151880</t>
+          <t>https://www.indeed.com/viewjob?jk=b53f7ddb0026dea4</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bar Harbor, ME, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b53f7ddb0026dea4</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf3b9815a50b381</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Senior Data Solutions Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf3b9815a50b381</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd4faeed9a50a59</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Solutions Architect</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd4faeed9a50a59</t>
+          <t>https://www.indeed.com/viewjob?jk=d0769674b72ae58f</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0769674b72ae58f</t>
+          <t>https://www.indeed.com/viewjob?jk=aef1c5cf0ee00174</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Kafka, PostgreSQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aef1c5cf0ee00174</t>
+          <t>https://www.indeed.com/viewjob?jk=17cb9776bd0e7f4a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Kafka, PostgreSQL, MongoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,59 +1301,59 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cb9776bd0e7f4a</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd2d99f50f24a3c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
+          <t>Data Engineer with AI/ML</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd2d99f50f24a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=836bfed93aa23557</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer with AI/ML</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=836bfed93aa23557</t>
+          <t>https://www.indeed.com/viewjob?jk=c250c7540d478f32</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform Engineer- 6 Month Assignment</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c250c7540d478f32</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5d273dd8b89dfc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Platform Engineer- 6 Month Assignment</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>Aptean</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5d273dd8b89dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=13c44a8aef4fd0a0</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13c44a8aef4fd0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=ef802648dc8c758d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aptean</t>
+          <t>Decagon</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef802648dc8c758d</t>
+          <t>https://www.indeed.com/viewjob?jk=d3d218109f5a2e7c</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3d218109f5a2e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=cb96afd07bcd39f3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Infrastructure</t>
+          <t>Platform Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Decagon</t>
+          <t>Happy Returns, Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb96afd07bcd39f3</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa757e1e92cc3c3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Platform Software Engineer (Remote)</t>
+          <t>Sr. DevOps Engineer- Snowflake &amp; Azure</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Happy Returns, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa757e1e92cc3c3</t>
+          <t>https://www.indeed.com/viewjob?jk=763fd8f53ea47c3f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer- Snowflake &amp; Azure</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Echo Global Logistics</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763fd8f53ea47c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=eae8bcb49c9597d5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Cloud &amp; Digital Platform Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Echo Global Logistics</t>
+          <t>Diality</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, GCP, Scala, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,59 +1686,59 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae8bcb49c9597d5</t>
+          <t>https://www.indeed.com/viewjob?jk=7fe3f1dbc64665df</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud &amp; Digital Platform Architect</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Diality</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fe3f1dbc64665df</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab00f608359b4fd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MAGNETO &amp; DIESEL INJECTOR SERVICE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Humble, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hive, Sqoop, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab00f608359b4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=d19cafe12d10dcef</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Systems Engineer- Cloud Infrastructure Engineering</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MAGNETO &amp; DIESEL INJECTOR SERVICE</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Humble, TX, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hive, Sqoop, Spark, Scala, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d19cafe12d10dcef</t>
+          <t>https://www.indeed.com/viewjob?jk=4de6e8c6244caa58</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer- Cloud Infrastructure Engineering</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>First Command Financial Services</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Data Factory, Scala, Oracle, SQL Server, NoSQL, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de6e8c6244caa58</t>
+          <t>https://www.indeed.com/viewjob?jk=5a2bba3746f32469</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Sales Engineer, Commercial</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>First Command Financial Services</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Scala, Oracle, SQL Server, NoSQL, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a2bba3746f32469</t>
+          <t>https://www.indeed.com/viewjob?jk=0487f884b026bec9</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial</t>
+          <t>Software Engineer II - Full Stack Java</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0487f884b026bec9</t>
+          <t>https://www.indeed.com/viewjob?jk=2c274b0f05e69603</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer II - Full Stack Java</t>
+          <t>Cloud Data Architect (Full-time Remote, NC Based)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Alliance Health Plan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c274b0f05e69603</t>
+          <t>https://www.indeed.com/viewjob?jk=8cb114578f5bf1e9</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud Data Architect (Full-time Remote, NC Based)</t>
+          <t>AI Engineer/Solution Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Alliance Health Plan</t>
+          <t>andrew morgan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cb114578f5bf1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=7604b89af99ba406</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Engineer/Solution Architect</t>
+          <t>Senior Software Engineer, Product Foundations</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>andrew morgan</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, NoSQL</t>
+          <t>AWS, SQS, IAM, RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7604b89af99ba406</t>
+          <t>https://www.indeed.com/viewjob?jk=dd2bfc17d54981e1</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd2bfc17d54981e1</t>
+          <t>https://www.indeed.com/viewjob?jk=0277abc185dfb7c6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Product Foundations</t>
+          <t>Software Engineer 4</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Castlight</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0277abc185dfb7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=3ce519e36124f5ab</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer 4</t>
+          <t>Full Stack Developer -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Castlight</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling, CI/CD</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ce519e36124f5ab</t>
+          <t>https://www.indeed.com/viewjob?jk=adcfd5cf564b5b00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full Stack Developer -In office, Alpharetta, GA</t>
+          <t>Software Engineer 4</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Castlight</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd5cf564b5b00</t>
+          <t>https://www.indeed.com/viewjob?jk=b5023cf7cd4ba777</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer 4</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Castlight</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5023cf7cd4ba777</t>
+          <t>https://www.indeed.com/viewjob?jk=8f9b9650d1bc3a54</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f9b9650d1bc3a54</t>
+          <t>https://www.indeed.com/viewjob?jk=efb82b07adb9feba</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb82b07adb9feba</t>
+          <t>https://www.indeed.com/viewjob?jk=65195644bb1b9e0b</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65195644bb1b9e0b</t>
+          <t>https://www.indeed.com/viewjob?jk=75e8ade515a41a57</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e8ade515a41a57</t>
+          <t>https://www.indeed.com/viewjob?jk=859e82cabfb17666</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859e82cabfb17666</t>
+          <t>https://www.indeed.com/viewjob?jk=f143b13efb8ce9b6</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f143b13efb8ce9b6</t>
+          <t>https://www.indeed.com/viewjob?jk=5a031b4964c2a255</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a031b4964c2a255</t>
+          <t>https://www.indeed.com/viewjob?jk=c4349cc4f94a5d87</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4349cc4f94a5d87</t>
+          <t>https://www.indeed.com/viewjob?jk=e66448573f4489d1</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66448573f4489d1</t>
+          <t>https://www.indeed.com/viewjob?jk=ddbf7440ad773888</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddbf7440ad773888</t>
+          <t>https://www.indeed.com/viewjob?jk=b72f3a18139b7e54</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b72f3a18139b7e54</t>
+          <t>https://www.indeed.com/viewjob?jk=7467917f2474b2e9</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7467917f2474b2e9</t>
+          <t>https://www.indeed.com/viewjob?jk=741f313dfe0a4767</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=741f313dfe0a4767</t>
+          <t>https://www.indeed.com/viewjob?jk=fb549dda19deb4df</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb549dda19deb4df</t>
+          <t>https://www.indeed.com/viewjob?jk=ad53455736c94aa1</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad53455736c94aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf96d3e5672d2dd</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf96d3e5672d2dd</t>
+          <t>https://www.indeed.com/viewjob?jk=a2abd6bece93c89e</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2abd6bece93c89e</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7b4a6316115547</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7b4a6316115547</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef2a2c6485dc8ce</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef2a2c6485dc8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=f8777195f0640326</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8777195f0640326</t>
+          <t>https://www.indeed.com/viewjob?jk=8b251c80469648dc</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b251c80469648dc</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad5e6a6c6033f66</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad5e6a6c6033f66</t>
+          <t>https://www.indeed.com/viewjob?jk=4439501b54b34a7a</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4439501b54b34a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=1151c815185cd79e</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1151c815185cd79e</t>
+          <t>https://www.indeed.com/viewjob?jk=d6614c39234b9da2</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6614c39234b9da2</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7e23c7f438f8c8</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7e23c7f438f8c8</t>
+          <t>https://www.indeed.com/viewjob?jk=e8663ead75611c2e</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8663ead75611c2e</t>
+          <t>https://www.indeed.com/viewjob?jk=51de78e580811e18</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51de78e580811e18</t>
+          <t>https://www.indeed.com/viewjob?jk=548feeaa37b8c916</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=548feeaa37b8c916</t>
+          <t>https://www.indeed.com/viewjob?jk=9cf7d70224611ecc</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cf7d70224611ecc</t>
+          <t>https://www.indeed.com/viewjob?jk=08e283453e85139f</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e283453e85139f</t>
+          <t>https://www.indeed.com/viewjob?jk=ecaa2a1fd433f4a4</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecaa2a1fd433f4a4</t>
+          <t>https://www.indeed.com/viewjob?jk=dd01c10e73409cc8</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd01c10e73409cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=3166241cc8c62f5d</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3166241cc8c62f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=1572589542133e74</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1572589542133e74</t>
+          <t>https://www.indeed.com/viewjob?jk=a2ec3f9f81325aa0</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2ec3f9f81325aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=492f0c5d5b1026f4</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=492f0c5d5b1026f4</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5a1bf124fcc939</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5a1bf124fcc939</t>
+          <t>https://www.indeed.com/viewjob?jk=e7780a9fb7958201</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7780a9fb7958201</t>
+          <t>https://www.indeed.com/viewjob?jk=fd18a128a4672b91</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd18a128a4672b91</t>
+          <t>https://www.indeed.com/viewjob?jk=ea676aaaba70e2d7</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea676aaaba70e2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=cab3ba747ce4a550</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab3ba747ce4a550</t>
+          <t>https://www.indeed.com/viewjob?jk=d65e39a595440fab</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65e39a595440fab</t>
+          <t>https://www.indeed.com/viewjob?jk=55cb9c48e2f72a54</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55cb9c48e2f72a54</t>
+          <t>https://www.indeed.com/viewjob?jk=b3a01b8449781d9b</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3a01b8449781d9b</t>
+          <t>https://www.indeed.com/viewjob?jk=5fa7561c868d2097</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fa7561c868d2097</t>
+          <t>https://www.indeed.com/viewjob?jk=3a729d7eaa711e20</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a729d7eaa711e20</t>
+          <t>https://www.indeed.com/viewjob?jk=1f022796cfb8fbcc</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f022796cfb8fbcc</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c33b5572cf45fa</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c33b5572cf45fa</t>
+          <t>https://www.indeed.com/viewjob?jk=8762f88f61ad7223</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8762f88f61ad7223</t>
+          <t>https://www.indeed.com/viewjob?jk=efdfb03d10f7ec00</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Forward Deployed Data Engineer Expert</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdfb03d10f7ec00</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1f104bd0b18db7</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer Expert</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Irvington, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1f104bd0b18db7</t>
+          <t>https://www.indeed.com/viewjob?jk=a189ac16e1f72f61</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Associate, Data Analytics Engineering</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Options Clearing Corporation</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Irvington, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a189ac16e1f72f61</t>
+          <t>https://www.indeed.com/viewjob?jk=1ad61eb5cd2a5633</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Analytics Engineering</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Options Clearing Corporation</t>
+          <t>Fabletics</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, dbt, Tableau, CI/CD</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ad61eb5cd2a5633</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac7bdb141d55008</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>DevOps Engineer, II</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Fabletics</t>
+          <t>NRCCUA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac7bdb141d55008</t>
+          <t>https://www.indeed.com/viewjob?jk=e257db597eccae8d</t>
         </is>
       </c>
     </row>
@@ -4113,12 +4113,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>NRCCUA</t>
+          <t>Encoura</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e257db597eccae8d</t>
+          <t>https://www.indeed.com/viewjob?jk=22172251f6a1ea83</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>DevOps Engineer, II</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Encoura</t>
+          <t>Uber Freight</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,69 +4161,69 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Scala, Kafka, Oracle, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22172251f6a1ea83</t>
+          <t>https://www.indeed.com/viewjob?jk=1b1465e42f01feff</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Sr. Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Uber Freight</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Scala, Kafka, Oracle, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b1465e42f01feff</t>
+          <t>https://www.indeed.com/viewjob?jk=ae7ce0b79b127907</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae7ce0b79b127907</t>
+          <t>https://www.indeed.com/viewjob?jk=dc99c4d09fcc8c74</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc99c4d09fcc8c74</t>
+          <t>https://www.indeed.com/viewjob?jk=a2644095339b05a5</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>Mimecast</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, S3, SQS, RDS, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2644095339b05a5</t>
+          <t>https://www.indeed.com/viewjob?jk=ca736f22eed6fef2</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Mimecast</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca736f22eed6fef2</t>
+          <t>https://www.indeed.com/viewjob?jk=b7994c3eb46bae42</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7994c3eb46bae42</t>
+          <t>https://www.indeed.com/viewjob?jk=649242ee28a33ae5</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=649242ee28a33ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=4b46b87f1359f8f5</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b46b87f1359f8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a7b9a70e68cf9f</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a7b9a70e68cf9f</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a148e3a41849d9</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a148e3a41849d9</t>
+          <t>https://www.indeed.com/viewjob?jk=fa4b4fcc410a503a</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa4b4fcc410a503a</t>
+          <t>https://www.indeed.com/viewjob?jk=6147a561d729a0dd</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6147a561d729a0dd</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab5bc5f32a7b9a0</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab5bc5f32a7b9a0</t>
+          <t>https://www.indeed.com/viewjob?jk=29f309b16d064eae</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29f309b16d064eae</t>
+          <t>https://www.indeed.com/viewjob?jk=f0b6e4cc0b843bf8</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0b6e4cc0b843bf8</t>
+          <t>https://www.indeed.com/viewjob?jk=9d739c3bc7cf38d1</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d739c3bc7cf38d1</t>
+          <t>https://www.indeed.com/viewjob?jk=70aa889c4c9efda8</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70aa889c4c9efda8</t>
+          <t>https://www.indeed.com/viewjob?jk=97557fcc3403a036</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97557fcc3403a036</t>
+          <t>https://www.indeed.com/viewjob?jk=01009226e788120d</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01009226e788120d</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b0eb4fb08e6514</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b0eb4fb08e6514</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7b1778e389048a</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7b1778e389048a</t>
+          <t>https://www.indeed.com/viewjob?jk=a5c63e693a3dd615</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5c63e693a3dd615</t>
+          <t>https://www.indeed.com/viewjob?jk=91abed51133c7c23</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91abed51133c7c23</t>
+          <t>https://www.indeed.com/viewjob?jk=432b655803995623</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432b655803995623</t>
+          <t>https://www.indeed.com/viewjob?jk=04006a1fe4e66850</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04006a1fe4e66850</t>
+          <t>https://www.indeed.com/viewjob?jk=4786e7810dfbd42c</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4786e7810dfbd42c</t>
+          <t>https://www.indeed.com/viewjob?jk=a73d9c78e32edfcb</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a73d9c78e32edfcb</t>
+          <t>https://www.indeed.com/viewjob?jk=f6e14d6ec4b8aeb0</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6e14d6ec4b8aeb0</t>
+          <t>https://www.indeed.com/viewjob?jk=f49fd486a1470d4a</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f49fd486a1470d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=bb0d75494367b7de</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb0d75494367b7de</t>
+          <t>https://www.indeed.com/viewjob?jk=3194fbbe9c9c6915</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3194fbbe9c9c6915</t>
+          <t>https://www.indeed.com/viewjob?jk=28e73925baaee988</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e73925baaee988</t>
+          <t>https://www.indeed.com/viewjob?jk=fd07d9e8d85d17ee</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd07d9e8d85d17ee</t>
+          <t>https://www.indeed.com/viewjob?jk=518960648e6b46f0</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518960648e6b46f0</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5b4030fed54c3d</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5b4030fed54c3d</t>
+          <t>https://www.indeed.com/viewjob?jk=25174fd8817164ea</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25174fd8817164ea</t>
+          <t>https://www.indeed.com/viewjob?jk=69b7427915d34288</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b7427915d34288</t>
+          <t>https://www.indeed.com/viewjob?jk=4964a3b46fec8c52</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Cost Engineer – Data Analytics</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4964a3b46fec8c52</t>
+          <t>https://www.indeed.com/viewjob?jk=69730719f6ab06e5</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Cost Engineer – Data Analytics</t>
+          <t>Data Engineer / Database Management Specialist for Fish Data</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69730719f6ab06e5</t>
+          <t>https://www.indeed.com/viewjob?jk=47ce35760bca7d80</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Data Engineer / Database Management Specialist for Fish Data</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ce35760bca7d80</t>
+          <t>https://www.indeed.com/viewjob?jk=308aad1cd4d5b8e2</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Sr Associate Engineer, IT Software</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,14 +5606,14 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aad1cd4d5b8e2</t>
+          <t>https://www.indeed.com/viewjob?jk=8fda6cb70fb70e09</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer, IT Software</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fda6cb70fb70e09</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd22b9c4b47341c</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd22b9c4b47341c</t>
+          <t>https://www.indeed.com/viewjob?jk=4edb47917f0e6215</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4edb47917f0e6215</t>
+          <t>https://www.indeed.com/viewjob?jk=e84f993a048191bd</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>BI Engineer - Data Analytics</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e84f993a048191bd</t>
+          <t>https://www.indeed.com/viewjob?jk=ca97d35c293c8ce6</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BI Engineer - Data Analytics</t>
+          <t>Senior BI Analyst - IGEN</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Appleton, WI, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
+          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, dbt, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,32 +5781,32 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca97d35c293c8ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=acd6baf60c6afe77</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Senior BI Analyst - IGEN</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>SmartAsset</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, dbt, Power BI, Tableau, Git</t>
+          <t>AWS, ECS, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd6baf60c6afe77</t>
+          <t>https://www.indeed.com/viewjob?jk=4f326fc2210a7954</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SmartAsset</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,17 +5841,17 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f326fc2210a7954</t>
+          <t>https://www.indeed.com/viewjob?jk=53279f54b14e6849</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53279f54b14e6849</t>
+          <t>https://www.indeed.com/viewjob?jk=0a92d266fe841f72</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Insight Software</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,34 +5911,34 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a92d266fe841f72</t>
+          <t>https://www.indeed.com/viewjob?jk=4f17a3a493c5baa0</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Insight Software</t>
+          <t>Gesa Credit Union</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Spokane Valley, WA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f17a3a493c5baa0</t>
+          <t>https://www.indeed.com/viewjob?jk=05b11f37b58c06df</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Spokane Valley, WA, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b11f37b58c06df</t>
+          <t>https://www.indeed.com/viewjob?jk=9e166dda8b8fb2c2</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Richland, WA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e166dda8b8fb2c2</t>
+          <t>https://www.indeed.com/viewjob?jk=38d66edddd66e10c</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Richland, WA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38d66edddd66e10c</t>
+          <t>https://www.indeed.com/viewjob?jk=89dd9964d8bd40d3</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Youth Villages</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Chesterfield, VA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89dd9964d8bd40d3</t>
+          <t>https://www.indeed.com/viewjob?jk=db40921aad59c33b</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer - Shared Services</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Youth Villages</t>
+          <t>HeroDevs</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Chesterfield, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,24 +6131,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db40921aad59c33b</t>
+          <t>https://www.indeed.com/viewjob?jk=6847e3d78dab687e</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Shared Services</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>HeroDevs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6847e3d78dab687e</t>
+          <t>https://www.indeed.com/viewjob?jk=cc42c2a4e5140f69</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc42c2a4e5140f69</t>
+          <t>https://www.indeed.com/viewjob?jk=66e65258ac69fefd</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66e65258ac69fefd</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b8c309e1dd4b82</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b8c309e1dd4b82</t>
+          <t>https://www.indeed.com/viewjob?jk=3f98038822e26dd8</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f98038822e26dd8</t>
+          <t>https://www.indeed.com/viewjob?jk=a55ba7ce9c7c4713</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a55ba7ce9c7c4713</t>
+          <t>https://www.indeed.com/viewjob?jk=85557e4da3ee4405</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85557e4da3ee4405</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c9edfc26a261dd</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c9edfc26a261dd</t>
+          <t>https://www.indeed.com/viewjob?jk=bc933305859d57b2</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc933305859d57b2</t>
+          <t>https://www.indeed.com/viewjob?jk=18e6b1969d6c7210</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18e6b1969d6c7210</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e1d701408b5626</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e1d701408b5626</t>
+          <t>https://www.indeed.com/viewjob?jk=288dfb7ead95495d</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=288dfb7ead95495d</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa85911435d672d</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fa85911435d672d</t>
+          <t>https://www.indeed.com/viewjob?jk=d9b1c071eb4265fc</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9b1c071eb4265fc</t>
+          <t>https://www.indeed.com/viewjob?jk=16f343db215cfb2f</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f343db215cfb2f</t>
+          <t>https://www.indeed.com/viewjob?jk=c44c288bccc8a6a7</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44c288bccc8a6a7</t>
+          <t>https://www.indeed.com/viewjob?jk=211ece43a6639e15</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211ece43a6639e15</t>
+          <t>https://www.indeed.com/viewjob?jk=117b69fc0cf106cd</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117b69fc0cf106cd</t>
+          <t>https://www.indeed.com/viewjob?jk=3a31df839c27886a</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a31df839c27886a</t>
+          <t>https://www.indeed.com/viewjob?jk=c2e202fe647fc8c9</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2e202fe647fc8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=7c1275067df0fefc</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c1275067df0fefc</t>
+          <t>https://www.indeed.com/viewjob?jk=0b046a816c53c475</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b046a816c53c475</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0dcc0f31186adf</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0dcc0f31186adf</t>
+          <t>https://www.indeed.com/viewjob?jk=26a73c1c18e4feb1</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26a73c1c18e4feb1</t>
+          <t>https://www.indeed.com/viewjob?jk=c162c04d00001e41</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c162c04d00001e41</t>
+          <t>https://www.indeed.com/viewjob?jk=d72aa3d302823165</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72aa3d302823165</t>
+          <t>https://www.indeed.com/viewjob?jk=437542252a94a7bd</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=437542252a94a7bd</t>
+          <t>https://www.indeed.com/viewjob?jk=1db9b5fd4ad91c79</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1db9b5fd4ad91c79</t>
+          <t>https://www.indeed.com/viewjob?jk=c338c18f5cc8b343</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c338c18f5cc8b343</t>
+          <t>https://www.indeed.com/viewjob?jk=9b85cee4884732fd</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b85cee4884732fd</t>
+          <t>https://www.indeed.com/viewjob?jk=87011ec9083a8b23</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87011ec9083a8b23</t>
+          <t>https://www.indeed.com/viewjob?jk=c1d4cefa45bd4112</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1d4cefa45bd4112</t>
+          <t>https://www.indeed.com/viewjob?jk=66e3413d7b223f3a</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66e3413d7b223f3a</t>
+          <t>https://www.indeed.com/viewjob?jk=5f780ced93a3bc16</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f780ced93a3bc16</t>
+          <t>https://www.indeed.com/viewjob?jk=5a4ad2ff105c8b83</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a4ad2ff105c8b83</t>
+          <t>https://www.indeed.com/viewjob?jk=430e2adbc8757712</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=430e2adbc8757712</t>
+          <t>https://www.indeed.com/viewjob?jk=43daf093c3246e39</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43daf093c3246e39</t>
+          <t>https://www.indeed.com/viewjob?jk=90d2c0b1b77db71f</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d2c0b1b77db71f</t>
+          <t>https://www.indeed.com/viewjob?jk=db8c787399aa7569</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db8c787399aa7569</t>
+          <t>https://www.indeed.com/viewjob?jk=afd791e19de5a0fe</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd791e19de5a0fe</t>
+          <t>https://www.indeed.com/viewjob?jk=1e23b8b93066067d</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e23b8b93066067d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa821c9250f94164</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7601,24 +7601,24 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa821c9250f94164</t>
+          <t>https://www.indeed.com/viewjob?jk=8f15f76b6c67bbdd</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>DevOps Engineer - Mid</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nalley Consulting</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -7636,24 +7636,24 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f15f76b6c67bbdd</t>
+          <t>https://www.indeed.com/viewjob?jk=35023775c057de52</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Mid</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Nalley Consulting</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Event Hubs, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -7671,24 +7671,24 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35023775c057de52</t>
+          <t>https://www.indeed.com/viewjob?jk=64c482ee7d2fd8be</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -7706,24 +7706,24 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64c482ee7d2fd8be</t>
+          <t>https://www.indeed.com/viewjob?jk=a6b981d8b3e30244</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Teza Technologies</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -7741,24 +7741,24 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6b981d8b3e30244</t>
+          <t>https://www.indeed.com/viewjob?jk=8521b827213a9dde</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Teza Technologies</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -7776,24 +7776,24 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8521b827213a9dde</t>
+          <t>https://www.indeed.com/viewjob?jk=b971d4cbb76a50f0</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7801,34 +7801,34 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b971d4cbb76a50f0</t>
+          <t>https://www.indeed.com/viewjob?jk=c3ac436669ece2e5</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Applications New</t>
+          <t>Ai Architect</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Temporal Technologies</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -7845,76 +7845,6 @@
         </is>
       </c>
       <c r="G212" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6b0c42ad13150702</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>Senior Applied AI Engineer</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D213" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c3ac436669ece2e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>Ai Architect</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Five Below</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D214" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=45b842ee858dea9c</t>
         </is>

--- a/results/job_matches_2026-05-30.xlsx
+++ b/results/job_matches_2026-05-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G212"/>
+  <dimension ref="A1:G208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,25 +748,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Solutions Architect - Platform, Cloud Infrastructure and Security</t>
+          <t>Cloud Engineer - DevOps</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SunnyData</t>
+          <t>Innovative Solutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47aa02c81d1c7a60</t>
+          <t>https://www.indeed.com/viewjob?jk=521ed8a47e56a014</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data</t>
+          <t>Senior Data Engineer - IGEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sightview Software</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Appleton, WI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
+          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102fc288fbb9abdd</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0ca36351ff88fb</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Engineer - DevOps</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Innovative Solutions</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521ed8a47e56a014</t>
+          <t>https://www.indeed.com/viewjob?jk=330bf279fb8cd838</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - IGEN</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Spark, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0ca36351ff88fb</t>
+          <t>https://www.indeed.com/viewjob?jk=0761c7021676d118</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Informatica Product Owner - Remote</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330bf279fb8cd838</t>
+          <t>https://www.indeed.com/viewjob?jk=1cd40cf715d1757e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Informatica Product Owner - Remote</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Spark, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0761c7021676d118</t>
+          <t>https://www.indeed.com/viewjob?jk=c3efe7a4e50700ee</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alachua, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cd40cf715d1757e</t>
+          <t>https://www.indeed.com/viewjob?jk=3185efffc8151880</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Bar Harbor, ME, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3efe7a4e50700ee</t>
+          <t>https://www.indeed.com/viewjob?jk=b53f7ddb0026dea4</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alachua, FL, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3185efffc8151880</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf3b9815a50b381</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bar Harbor, ME, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b53f7ddb0026dea4</t>
+          <t>https://www.indeed.com/viewjob?jk=d0769674b72ae58f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf3b9815a50b381</t>
+          <t>https://www.indeed.com/viewjob?jk=aef1c5cf0ee00174</t>
         </is>
       </c>
     </row>
@@ -1168,25 +1168,25 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Kafka, PostgreSQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0769674b72ae58f</t>
+          <t>https://www.indeed.com/viewjob?jk=17cb9776bd0e7f4a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,67 +1231,67 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aef1c5cf0ee00174</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd2d99f50f24a3c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer with AI/ML</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Kafka, PostgreSQL, MongoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cb9776bd0e7f4a</t>
+          <t>https://www.indeed.com/viewjob?jk=836bfed93aa23557</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd2d99f50f24a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=c250c7540d478f32</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer with AI/ML</t>
+          <t>Data Platform Engineer- 6 Month Assignment</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,29 +1326,29 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=836bfed93aa23557</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5d273dd8b89dfc</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Aptean</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c250c7540d478f32</t>
+          <t>https://www.indeed.com/viewjob?jk=13c44a8aef4fd0a0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Platform Engineer- 6 Month Assignment</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>Aptean</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5d273dd8b89dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=ef802648dc8c758d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aptean</t>
+          <t>Decagon</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13c44a8aef4fd0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=d3d218109f5a2e7c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Aptean</t>
+          <t>Decagon</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef802648dc8c758d</t>
+          <t>https://www.indeed.com/viewjob?jk=cb96afd07bcd39f3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Infrastructure</t>
+          <t>Platform Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Decagon</t>
+          <t>Happy Returns, Inc.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3d218109f5a2e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa757e1e92cc3c3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Infrastructure</t>
+          <t>Sr. DevOps Engineer- Snowflake &amp; Azure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Decagon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb96afd07bcd39f3</t>
+          <t>https://www.indeed.com/viewjob?jk=763fd8f53ea47c3f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Platform Software Engineer (Remote)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Happy Returns, Inc.</t>
+          <t>Echo Global Logistics</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Data Modeling</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa757e1e92cc3c3</t>
+          <t>https://www.indeed.com/viewjob?jk=eae8bcb49c9597d5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer- Snowflake &amp; Azure</t>
+          <t>Cloud &amp; Digital Platform Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Diality</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763fd8f53ea47c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=7fe3f1dbc64665df</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Echo Global Logistics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, GCP, Scala, NoSQL</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae8bcb49c9597d5</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab00f608359b4fd</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cloud &amp; Digital Platform Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Diality</t>
+          <t>MAGNETO &amp; DIESEL INJECTOR SERVICE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Humble, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hive, Sqoop, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fe3f1dbc64665df</t>
+          <t>https://www.indeed.com/viewjob?jk=d19cafe12d10dcef</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Sr. Systems Engineer- Cloud Infrastructure Engineering</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab00f608359b4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=4de6e8c6244caa58</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MAGNETO &amp; DIESEL INJECTOR SERVICE</t>
+          <t>First Command Financial Services</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Humble, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hive, Sqoop, Spark, Scala, ETL, ELT</t>
+          <t>RDS, Data Factory, Scala, Oracle, SQL Server, NoSQL, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d19cafe12d10dcef</t>
+          <t>https://www.indeed.com/viewjob?jk=5a2bba3746f32469</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer- Cloud Infrastructure Engineering</t>
+          <t>Senior Sales Engineer, Commercial</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de6e8c6244caa58</t>
+          <t>https://www.indeed.com/viewjob?jk=0487f884b026bec9</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer II - Full Stack Java</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>First Command Financial Services</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Scala, Oracle, SQL Server, NoSQL, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a2bba3746f32469</t>
+          <t>https://www.indeed.com/viewjob?jk=2c274b0f05e69603</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial</t>
+          <t>Cloud Data Architect (Full-time Remote, NC Based)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Alliance Health Plan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0487f884b026bec9</t>
+          <t>https://www.indeed.com/viewjob?jk=8cb114578f5bf1e9</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer II - Full Stack Java</t>
+          <t>AI Engineer/Solution Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>andrew morgan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c274b0f05e69603</t>
+          <t>https://www.indeed.com/viewjob?jk=7604b89af99ba406</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Data Architect (Full-time Remote, NC Based)</t>
+          <t>Senior Software Engineer, Product Foundations</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Alliance Health Plan</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, SQS, IAM, RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cb114578f5bf1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=dd2bfc17d54981e1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Engineer/Solution Architect</t>
+          <t>Senior Software Engineer, Product Foundations</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>andrew morgan</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, NoSQL</t>
+          <t>AWS, SQS, IAM, RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7604b89af99ba406</t>
+          <t>https://www.indeed.com/viewjob?jk=0277abc185dfb7c6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Product Foundations</t>
+          <t>Software Engineer 4</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Castlight</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd2bfc17d54981e1</t>
+          <t>https://www.indeed.com/viewjob?jk=3ce519e36124f5ab</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Product Foundations</t>
+          <t>Full Stack Developer -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0277abc185dfb7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=adcfd5cf564b5b00</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ce519e36124f5ab</t>
+          <t>https://www.indeed.com/viewjob?jk=b5023cf7cd4ba777</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Full Stack Developer -In office, Alpharetta, GA</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd5cf564b5b00</t>
+          <t>https://www.indeed.com/viewjob?jk=8f9b9650d1bc3a54</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer 4</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Castlight</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5023cf7cd4ba777</t>
+          <t>https://www.indeed.com/viewjob?jk=efb82b07adb9feba</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f9b9650d1bc3a54</t>
+          <t>https://www.indeed.com/viewjob?jk=65195644bb1b9e0b</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb82b07adb9feba</t>
+          <t>https://www.indeed.com/viewjob?jk=75e8ade515a41a57</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65195644bb1b9e0b</t>
+          <t>https://www.indeed.com/viewjob?jk=859e82cabfb17666</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e8ade515a41a57</t>
+          <t>https://www.indeed.com/viewjob?jk=f143b13efb8ce9b6</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859e82cabfb17666</t>
+          <t>https://www.indeed.com/viewjob?jk=5a031b4964c2a255</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f143b13efb8ce9b6</t>
+          <t>https://www.indeed.com/viewjob?jk=c4349cc4f94a5d87</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a031b4964c2a255</t>
+          <t>https://www.indeed.com/viewjob?jk=e66448573f4489d1</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4349cc4f94a5d87</t>
+          <t>https://www.indeed.com/viewjob?jk=ddbf7440ad773888</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66448573f4489d1</t>
+          <t>https://www.indeed.com/viewjob?jk=b72f3a18139b7e54</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddbf7440ad773888</t>
+          <t>https://www.indeed.com/viewjob?jk=7467917f2474b2e9</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b72f3a18139b7e54</t>
+          <t>https://www.indeed.com/viewjob?jk=741f313dfe0a4767</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7467917f2474b2e9</t>
+          <t>https://www.indeed.com/viewjob?jk=fb549dda19deb4df</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=741f313dfe0a4767</t>
+          <t>https://www.indeed.com/viewjob?jk=ad53455736c94aa1</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb549dda19deb4df</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf96d3e5672d2dd</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad53455736c94aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=a2abd6bece93c89e</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf96d3e5672d2dd</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7b4a6316115547</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2abd6bece93c89e</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef2a2c6485dc8ce</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7b4a6316115547</t>
+          <t>https://www.indeed.com/viewjob?jk=f8777195f0640326</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef2a2c6485dc8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=8b251c80469648dc</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8777195f0640326</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad5e6a6c6033f66</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b251c80469648dc</t>
+          <t>https://www.indeed.com/viewjob?jk=4439501b54b34a7a</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad5e6a6c6033f66</t>
+          <t>https://www.indeed.com/viewjob?jk=1151c815185cd79e</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4439501b54b34a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=d6614c39234b9da2</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1151c815185cd79e</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7e23c7f438f8c8</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6614c39234b9da2</t>
+          <t>https://www.indeed.com/viewjob?jk=e8663ead75611c2e</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7e23c7f438f8c8</t>
+          <t>https://www.indeed.com/viewjob?jk=51de78e580811e18</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8663ead75611c2e</t>
+          <t>https://www.indeed.com/viewjob?jk=548feeaa37b8c916</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51de78e580811e18</t>
+          <t>https://www.indeed.com/viewjob?jk=9cf7d70224611ecc</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=548feeaa37b8c916</t>
+          <t>https://www.indeed.com/viewjob?jk=08e283453e85139f</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cf7d70224611ecc</t>
+          <t>https://www.indeed.com/viewjob?jk=ecaa2a1fd433f4a4</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e283453e85139f</t>
+          <t>https://www.indeed.com/viewjob?jk=dd01c10e73409cc8</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecaa2a1fd433f4a4</t>
+          <t>https://www.indeed.com/viewjob?jk=3166241cc8c62f5d</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd01c10e73409cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=1572589542133e74</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3166241cc8c62f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=a2ec3f9f81325aa0</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1572589542133e74</t>
+          <t>https://www.indeed.com/viewjob?jk=492f0c5d5b1026f4</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2ec3f9f81325aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5a1bf124fcc939</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=492f0c5d5b1026f4</t>
+          <t>https://www.indeed.com/viewjob?jk=e7780a9fb7958201</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5a1bf124fcc939</t>
+          <t>https://www.indeed.com/viewjob?jk=fd18a128a4672b91</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7780a9fb7958201</t>
+          <t>https://www.indeed.com/viewjob?jk=ea676aaaba70e2d7</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd18a128a4672b91</t>
+          <t>https://www.indeed.com/viewjob?jk=cab3ba747ce4a550</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea676aaaba70e2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=d65e39a595440fab</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab3ba747ce4a550</t>
+          <t>https://www.indeed.com/viewjob?jk=55cb9c48e2f72a54</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65e39a595440fab</t>
+          <t>https://www.indeed.com/viewjob?jk=b3a01b8449781d9b</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55cb9c48e2f72a54</t>
+          <t>https://www.indeed.com/viewjob?jk=5fa7561c868d2097</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3a01b8449781d9b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a729d7eaa711e20</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fa7561c868d2097</t>
+          <t>https://www.indeed.com/viewjob?jk=1f022796cfb8fbcc</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a729d7eaa711e20</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c33b5572cf45fa</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f022796cfb8fbcc</t>
+          <t>https://www.indeed.com/viewjob?jk=8762f88f61ad7223</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c33b5572cf45fa</t>
+          <t>https://www.indeed.com/viewjob?jk=efdfb03d10f7ec00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Forward Deployed Data Engineer Expert</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8762f88f61ad7223</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1f104bd0b18db7</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Senior Associate, Data Analytics Engineering</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Options Clearing Corporation</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdfb03d10f7ec00</t>
+          <t>https://www.indeed.com/viewjob?jk=1ad61eb5cd2a5633</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer Expert</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Fabletics</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1f104bd0b18db7</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac7bdb141d55008</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer, II</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NRCCUA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Irvington, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a189ac16e1f72f61</t>
+          <t>https://www.indeed.com/viewjob?jk=e257db597eccae8d</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Analytics Engineering</t>
+          <t>DevOps Engineer, II</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Options Clearing Corporation</t>
+          <t>Encoura</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, dbt, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ad61eb5cd2a5633</t>
+          <t>https://www.indeed.com/viewjob?jk=22172251f6a1ea83</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Fabletics</t>
+          <t>Uber Freight</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,42 +4056,42 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Scala, Kafka, Oracle, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac7bdb141d55008</t>
+          <t>https://www.indeed.com/viewjob?jk=1b1465e42f01feff</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>DevOps Engineer, II</t>
+          <t>Sr. Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NRCCUA</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e257db597eccae8d</t>
+          <t>https://www.indeed.com/viewjob?jk=ae7ce0b79b127907</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>DevOps Engineer, II</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Encoura</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,59 +4136,59 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22172251f6a1ea83</t>
+          <t>https://www.indeed.com/viewjob?jk=dc99c4d09fcc8c74</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Uber Freight</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Scala, Kafka, Oracle, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b1465e42f01feff</t>
+          <t>https://www.indeed.com/viewjob?jk=a2644095339b05a5</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae7ce0b79b127907</t>
+          <t>https://www.indeed.com/viewjob?jk=b7994c3eb46bae42</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc99c4d09fcc8c74</t>
+          <t>https://www.indeed.com/viewjob?jk=649242ee28a33ae5</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2644095339b05a5</t>
+          <t>https://www.indeed.com/viewjob?jk=4b46b87f1359f8f5</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Mimecast</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca736f22eed6fef2</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a7b9a70e68cf9f</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7994c3eb46bae42</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a148e3a41849d9</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=649242ee28a33ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=fa4b4fcc410a503a</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b46b87f1359f8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=6147a561d729a0dd</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a7b9a70e68cf9f</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab5bc5f32a7b9a0</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a148e3a41849d9</t>
+          <t>https://www.indeed.com/viewjob?jk=29f309b16d064eae</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa4b4fcc410a503a</t>
+          <t>https://www.indeed.com/viewjob?jk=f0b6e4cc0b843bf8</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6147a561d729a0dd</t>
+          <t>https://www.indeed.com/viewjob?jk=9d739c3bc7cf38d1</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab5bc5f32a7b9a0</t>
+          <t>https://www.indeed.com/viewjob?jk=70aa889c4c9efda8</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29f309b16d064eae</t>
+          <t>https://www.indeed.com/viewjob?jk=97557fcc3403a036</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0b6e4cc0b843bf8</t>
+          <t>https://www.indeed.com/viewjob?jk=01009226e788120d</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d739c3bc7cf38d1</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b0eb4fb08e6514</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70aa889c4c9efda8</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7b1778e389048a</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97557fcc3403a036</t>
+          <t>https://www.indeed.com/viewjob?jk=a5c63e693a3dd615</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01009226e788120d</t>
+          <t>https://www.indeed.com/viewjob?jk=91abed51133c7c23</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b0eb4fb08e6514</t>
+          <t>https://www.indeed.com/viewjob?jk=432b655803995623</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7b1778e389048a</t>
+          <t>https://www.indeed.com/viewjob?jk=04006a1fe4e66850</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5c63e693a3dd615</t>
+          <t>https://www.indeed.com/viewjob?jk=4786e7810dfbd42c</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91abed51133c7c23</t>
+          <t>https://www.indeed.com/viewjob?jk=a73d9c78e32edfcb</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432b655803995623</t>
+          <t>https://www.indeed.com/viewjob?jk=f6e14d6ec4b8aeb0</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04006a1fe4e66850</t>
+          <t>https://www.indeed.com/viewjob?jk=f49fd486a1470d4a</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4786e7810dfbd42c</t>
+          <t>https://www.indeed.com/viewjob?jk=bb0d75494367b7de</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a73d9c78e32edfcb</t>
+          <t>https://www.indeed.com/viewjob?jk=3194fbbe9c9c6915</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6e14d6ec4b8aeb0</t>
+          <t>https://www.indeed.com/viewjob?jk=28e73925baaee988</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f49fd486a1470d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=fd07d9e8d85d17ee</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb0d75494367b7de</t>
+          <t>https://www.indeed.com/viewjob?jk=518960648e6b46f0</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3194fbbe9c9c6915</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5b4030fed54c3d</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e73925baaee988</t>
+          <t>https://www.indeed.com/viewjob?jk=25174fd8817164ea</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd07d9e8d85d17ee</t>
+          <t>https://www.indeed.com/viewjob?jk=69b7427915d34288</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518960648e6b46f0</t>
+          <t>https://www.indeed.com/viewjob?jk=4964a3b46fec8c52</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Cost Engineer – Data Analytics</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5b4030fed54c3d</t>
+          <t>https://www.indeed.com/viewjob?jk=69730719f6ab06e5</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Data Engineer / Database Management Specialist for Fish Data</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25174fd8817164ea</t>
+          <t>https://www.indeed.com/viewjob?jk=47ce35760bca7d80</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b7427915d34288</t>
+          <t>https://www.indeed.com/viewjob?jk=308aad1cd4d5b8e2</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Sr Associate Engineer, IT Software</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4964a3b46fec8c52</t>
+          <t>https://www.indeed.com/viewjob?jk=8fda6cb70fb70e09</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Cost Engineer – Data Analytics</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69730719f6ab06e5</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd22b9c4b47341c</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Data Engineer / Database Management Specialist for Fish Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ce35760bca7d80</t>
+          <t>https://www.indeed.com/viewjob?jk=4edb47917f0e6215</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aad1cd4d5b8e2</t>
+          <t>https://www.indeed.com/viewjob?jk=e84f993a048191bd</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer, IT Software</t>
+          <t>BI Engineer - Data Analytics</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fda6cb70fb70e09</t>
+          <t>https://www.indeed.com/viewjob?jk=ca97d35c293c8ce6</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior BI Analyst - IGEN</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Appleton, WI, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, dbt, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,32 +5641,32 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd22b9c4b47341c</t>
+          <t>https://www.indeed.com/viewjob?jk=acd6baf60c6afe77</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>SmartAsset</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, ECS, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,102 +5676,102 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4edb47917f0e6215</t>
+          <t>https://www.indeed.com/viewjob?jk=4f326fc2210a7954</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e84f993a048191bd</t>
+          <t>https://www.indeed.com/viewjob?jk=53279f54b14e6849</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>BI Engineer - Data Analytics</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca97d35c293c8ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=0a92d266fe841f72</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Senior BI Analyst - IGEN</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>Insight Software</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, dbt, Power BI, Tableau, Git</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,24 +5781,24 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd6baf60c6afe77</t>
+          <t>https://www.indeed.com/viewjob?jk=4f17a3a493c5baa0</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SmartAsset</t>
+          <t>Gesa Credit Union</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Spokane Valley, WA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f326fc2210a7954</t>
+          <t>https://www.indeed.com/viewjob?jk=05b11f37b58c06df</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Gesa Credit Union</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53279f54b14e6849</t>
+          <t>https://www.indeed.com/viewjob?jk=9e166dda8b8fb2c2</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Gesa Credit Union</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Richland, WA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,34 +5876,34 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a92d266fe841f72</t>
+          <t>https://www.indeed.com/viewjob?jk=38d66edddd66e10c</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Insight Software</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f17a3a493c5baa0</t>
+          <t>https://www.indeed.com/viewjob?jk=89dd9964d8bd40d3</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>Youth Villages</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Spokane Valley, WA, US USA</t>
+          <t>Chesterfield, VA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b11f37b58c06df</t>
+          <t>https://www.indeed.com/viewjob?jk=db40921aad59c33b</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Software Engineer - Shared Services</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>HeroDevs</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e166dda8b8fb2c2</t>
+          <t>https://www.indeed.com/viewjob?jk=6847e3d78dab687e</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Richland, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38d66edddd66e10c</t>
+          <t>https://www.indeed.com/viewjob?jk=cc42c2a4e5140f69</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89dd9964d8bd40d3</t>
+          <t>https://www.indeed.com/viewjob?jk=66e65258ac69fefd</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Youth Villages</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Chesterfield, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db40921aad59c33b</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b8c309e1dd4b82</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Shared Services</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>HeroDevs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6847e3d78dab687e</t>
+          <t>https://www.indeed.com/viewjob?jk=3f98038822e26dd8</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc42c2a4e5140f69</t>
+          <t>https://www.indeed.com/viewjob?jk=a55ba7ce9c7c4713</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66e65258ac69fefd</t>
+          <t>https://www.indeed.com/viewjob?jk=85557e4da3ee4405</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b8c309e1dd4b82</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c9edfc26a261dd</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f98038822e26dd8</t>
+          <t>https://www.indeed.com/viewjob?jk=bc933305859d57b2</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a55ba7ce9c7c4713</t>
+          <t>https://www.indeed.com/viewjob?jk=18e6b1969d6c7210</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85557e4da3ee4405</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e1d701408b5626</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c9edfc26a261dd</t>
+          <t>https://www.indeed.com/viewjob?jk=288dfb7ead95495d</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc933305859d57b2</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa85911435d672d</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18e6b1969d6c7210</t>
+          <t>https://www.indeed.com/viewjob?jk=d9b1c071eb4265fc</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e1d701408b5626</t>
+          <t>https://www.indeed.com/viewjob?jk=16f343db215cfb2f</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=288dfb7ead95495d</t>
+          <t>https://www.indeed.com/viewjob?jk=c44c288bccc8a6a7</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fa85911435d672d</t>
+          <t>https://www.indeed.com/viewjob?jk=211ece43a6639e15</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9b1c071eb4265fc</t>
+          <t>https://www.indeed.com/viewjob?jk=117b69fc0cf106cd</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f343db215cfb2f</t>
+          <t>https://www.indeed.com/viewjob?jk=3a31df839c27886a</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44c288bccc8a6a7</t>
+          <t>https://www.indeed.com/viewjob?jk=c2e202fe647fc8c9</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211ece43a6639e15</t>
+          <t>https://www.indeed.com/viewjob?jk=7c1275067df0fefc</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117b69fc0cf106cd</t>
+          <t>https://www.indeed.com/viewjob?jk=0b046a816c53c475</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a31df839c27886a</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0dcc0f31186adf</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2e202fe647fc8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=26a73c1c18e4feb1</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c1275067df0fefc</t>
+          <t>https://www.indeed.com/viewjob?jk=c162c04d00001e41</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b046a816c53c475</t>
+          <t>https://www.indeed.com/viewjob?jk=d72aa3d302823165</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0dcc0f31186adf</t>
+          <t>https://www.indeed.com/viewjob?jk=437542252a94a7bd</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26a73c1c18e4feb1</t>
+          <t>https://www.indeed.com/viewjob?jk=1db9b5fd4ad91c79</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c162c04d00001e41</t>
+          <t>https://www.indeed.com/viewjob?jk=c338c18f5cc8b343</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72aa3d302823165</t>
+          <t>https://www.indeed.com/viewjob?jk=9b85cee4884732fd</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=437542252a94a7bd</t>
+          <t>https://www.indeed.com/viewjob?jk=87011ec9083a8b23</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1db9b5fd4ad91c79</t>
+          <t>https://www.indeed.com/viewjob?jk=c1d4cefa45bd4112</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c338c18f5cc8b343</t>
+          <t>https://www.indeed.com/viewjob?jk=66e3413d7b223f3a</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b85cee4884732fd</t>
+          <t>https://www.indeed.com/viewjob?jk=5f780ced93a3bc16</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87011ec9083a8b23</t>
+          <t>https://www.indeed.com/viewjob?jk=5a4ad2ff105c8b83</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1d4cefa45bd4112</t>
+          <t>https://www.indeed.com/viewjob?jk=430e2adbc8757712</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66e3413d7b223f3a</t>
+          <t>https://www.indeed.com/viewjob?jk=43daf093c3246e39</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f780ced93a3bc16</t>
+          <t>https://www.indeed.com/viewjob?jk=90d2c0b1b77db71f</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a4ad2ff105c8b83</t>
+          <t>https://www.indeed.com/viewjob?jk=db8c787399aa7569</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=430e2adbc8757712</t>
+          <t>https://www.indeed.com/viewjob?jk=afd791e19de5a0fe</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43daf093c3246e39</t>
+          <t>https://www.indeed.com/viewjob?jk=1e23b8b93066067d</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d2c0b1b77db71f</t>
+          <t>https://www.indeed.com/viewjob?jk=aa821c9250f94164</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7461,24 +7461,24 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db8c787399aa7569</t>
+          <t>https://www.indeed.com/viewjob?jk=8f15f76b6c67bbdd</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>DevOps Engineer - Mid</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nalley Consulting</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -7496,24 +7496,24 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd791e19de5a0fe</t>
+          <t>https://www.indeed.com/viewjob?jk=35023775c057de52</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7521,34 +7521,34 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e23b8b93066067d</t>
+          <t>https://www.indeed.com/viewjob?jk=c3ac436669ece2e5</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Event Hubs, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -7566,24 +7566,24 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa821c9250f94164</t>
+          <t>https://www.indeed.com/viewjob?jk=64c482ee7d2fd8be</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -7601,24 +7601,24 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f15f76b6c67bbdd</t>
+          <t>https://www.indeed.com/viewjob?jk=a6b981d8b3e30244</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Mid</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Nalley Consulting</t>
+          <t>Teza Technologies</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -7636,24 +7636,24 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35023775c057de52</t>
+          <t>https://www.indeed.com/viewjob?jk=8521b827213a9dde</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -7671,24 +7671,24 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64c482ee7d2fd8be</t>
+          <t>https://www.indeed.com/viewjob?jk=b971d4cbb76a50f0</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Ai Architect</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -7705,146 +7705,6 @@
         </is>
       </c>
       <c r="G208" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a6b981d8b3e30244</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Teza Technologies</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D209" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8521b827213a9dde</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Alight Solutions</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D210" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b971d4cbb76a50f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>Senior Applied AI Engineer</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D211" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c3ac436669ece2e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>Ai Architect</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Five Below</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D212" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=45b842ee858dea9c</t>
         </is>

--- a/results/job_matches_2026-05-30.xlsx
+++ b/results/job_matches_2026-05-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G208"/>
+  <dimension ref="A1:G199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Databricks Administrator</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>Avnet</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d54cb6fb55273d2</t>
+          <t>https://www.indeed.com/viewjob?jk=e4012204380caba1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Databricks Administrator</t>
+          <t>Senior Data Engineer - IGEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Avnet</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Appleton, WI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4012204380caba1</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0ca36351ff88fb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Engineer - DevOps</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Innovative Solutions</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521ed8a47e56a014</t>
+          <t>https://www.indeed.com/viewjob?jk=330bf279fb8cd838</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - IGEN</t>
+          <t>Informatica Product Owner - Remote</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0ca36351ff88fb</t>
+          <t>https://www.indeed.com/viewjob?jk=1cd40cf715d1757e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Informatica Product Owner - Remote</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330bf279fb8cd838</t>
+          <t>https://www.indeed.com/viewjob?jk=c3efe7a4e50700ee</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Informatica Product Owner - Remote</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Alachua, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Spark, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0761c7021676d118</t>
+          <t>https://www.indeed.com/viewjob?jk=3185efffc8151880</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bar Harbor, ME, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cd40cf715d1757e</t>
+          <t>https://www.indeed.com/viewjob?jk=b53f7ddb0026dea4</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3efe7a4e50700ee</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf3b9815a50b381</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Senior Data Solutions Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alachua, FL, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3185efffc8151880</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd4faeed9a50a59</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bar Harbor, ME, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b53f7ddb0026dea4</t>
+          <t>https://www.indeed.com/viewjob?jk=d0769674b72ae58f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf3b9815a50b381</t>
+          <t>https://www.indeed.com/viewjob?jk=aef1c5cf0ee00174</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Kafka, PostgreSQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0769674b72ae58f</t>
+          <t>https://www.indeed.com/viewjob?jk=17cb9776bd0e7f4a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aef1c5cf0ee00174</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd2d99f50f24a3c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Solutions Architect</t>
+          <t>Data Engineer with AI/ML</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd4faeed9a50a59</t>
+          <t>https://www.indeed.com/viewjob?jk=836bfed93aa23557</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Kafka, PostgreSQL, MongoDB, Data Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cb9776bd0e7f4a</t>
+          <t>https://www.indeed.com/viewjob?jk=c250c7540d478f32</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
+          <t>Data Platform Engineer- 6 Month Assignment</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd2d99f50f24a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5d273dd8b89dfc</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer with AI/ML</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Aptean</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=836bfed93aa23557</t>
+          <t>https://www.indeed.com/viewjob?jk=13c44a8aef4fd0a0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Aptean</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c250c7540d478f32</t>
+          <t>https://www.indeed.com/viewjob?jk=ef802648dc8c758d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Platform Engineer- 6 Month Assignment</t>
+          <t>Senior Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>Decagon</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5d273dd8b89dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=d3d218109f5a2e7c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aptean</t>
+          <t>Decagon</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,19 +1371,19 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13c44a8aef4fd0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=cb96afd07bcd39f3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aptean</t>
+          <t>Happy Returns, Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1392,11 +1392,11 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef802648dc8c758d</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa757e1e92cc3c3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Infrastructure</t>
+          <t>Sr. DevOps Engineer- Snowflake &amp; Azure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Decagon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3d218109f5a2e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=763fd8f53ea47c3f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Infrastructure</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Decagon</t>
+          <t>Echo Global Logistics</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb96afd07bcd39f3</t>
+          <t>https://www.indeed.com/viewjob?jk=eae8bcb49c9597d5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Platform Software Engineer (Remote)</t>
+          <t>Cloud &amp; Digital Platform Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Happy Returns, Inc.</t>
+          <t>Diality</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa757e1e92cc3c3</t>
+          <t>https://www.indeed.com/viewjob?jk=7fe3f1dbc64665df</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer- Snowflake &amp; Azure</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1528,50 +1528,50 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763fd8f53ea47c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab00f608359b4fd</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Echo Global Logistics</t>
+          <t>MAGNETO &amp; DIESEL INJECTOR SERVICE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Humble, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, GCP, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hive, Sqoop, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae8bcb49c9597d5</t>
+          <t>https://www.indeed.com/viewjob?jk=d19cafe12d10dcef</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud &amp; Digital Platform Architect</t>
+          <t>Sr. Systems Engineer- Cloud Infrastructure Engineering</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Diality</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fe3f1dbc64665df</t>
+          <t>https://www.indeed.com/viewjob?jk=4de6e8c6244caa58</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Sr. Product Mgr. &amp; Enterprise App Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Vomela Companies</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Elk Grove Village, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Scala, Kafka, SQL Server, MongoDB, Power BI, Tableau, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab00f608359b4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=f0c1cd41ea8edf5b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MAGNETO &amp; DIESEL INJECTOR SERVICE</t>
+          <t>First Command Financial Services</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Humble, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hive, Sqoop, Spark, Scala, ETL, ELT</t>
+          <t>RDS, Data Factory, Scala, Oracle, SQL Server, NoSQL, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d19cafe12d10dcef</t>
+          <t>https://www.indeed.com/viewjob?jk=5a2bba3746f32469</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer- Cloud Infrastructure Engineering</t>
+          <t>Senior Sales Engineer, Commercial</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de6e8c6244caa58</t>
+          <t>https://www.indeed.com/viewjob?jk=0487f884b026bec9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer II - Full Stack Java</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>First Command Financial Services</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Scala, Oracle, SQL Server, NoSQL, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a2bba3746f32469</t>
+          <t>https://www.indeed.com/viewjob?jk=2c274b0f05e69603</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial</t>
+          <t>AI Engineer/Solution Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>andrew morgan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0487f884b026bec9</t>
+          <t>https://www.indeed.com/viewjob?jk=7604b89af99ba406</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer II - Full Stack Java</t>
+          <t>Senior Software Engineer, Product Foundations</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, SQS, IAM, RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c274b0f05e69603</t>
+          <t>https://www.indeed.com/viewjob?jk=dd2bfc17d54981e1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud Data Architect (Full-time Remote, NC Based)</t>
+          <t>Senior Software Engineer, Product Foundations</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Alliance Health Plan</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, SQS, IAM, RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cb114578f5bf1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=0277abc185dfb7c6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Engineer/Solution Architect</t>
+          <t>Software Engineer 4</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>andrew morgan</t>
+          <t>Castlight</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, NoSQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7604b89af99ba406</t>
+          <t>https://www.indeed.com/viewjob?jk=3ce519e36124f5ab</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Product Foundations</t>
+          <t>Full Stack Developer -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd2bfc17d54981e1</t>
+          <t>https://www.indeed.com/viewjob?jk=adcfd5cf564b5b00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Product Foundations</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0277abc185dfb7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=8f9b9650d1bc3a54</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer 4</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Castlight</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ce519e36124f5ab</t>
+          <t>https://www.indeed.com/viewjob?jk=efb82b07adb9feba</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full Stack Developer -In office, Alpharetta, GA</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd5cf564b5b00</t>
+          <t>https://www.indeed.com/viewjob?jk=65195644bb1b9e0b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer 4</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Castlight</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5023cf7cd4ba777</t>
+          <t>https://www.indeed.com/viewjob?jk=75e8ade515a41a57</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f9b9650d1bc3a54</t>
+          <t>https://www.indeed.com/viewjob?jk=859e82cabfb17666</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb82b07adb9feba</t>
+          <t>https://www.indeed.com/viewjob?jk=f143b13efb8ce9b6</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65195644bb1b9e0b</t>
+          <t>https://www.indeed.com/viewjob?jk=5a031b4964c2a255</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e8ade515a41a57</t>
+          <t>https://www.indeed.com/viewjob?jk=c4349cc4f94a5d87</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859e82cabfb17666</t>
+          <t>https://www.indeed.com/viewjob?jk=e66448573f4489d1</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f143b13efb8ce9b6</t>
+          <t>https://www.indeed.com/viewjob?jk=ddbf7440ad773888</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a031b4964c2a255</t>
+          <t>https://www.indeed.com/viewjob?jk=b72f3a18139b7e54</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4349cc4f94a5d87</t>
+          <t>https://www.indeed.com/viewjob?jk=7467917f2474b2e9</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66448573f4489d1</t>
+          <t>https://www.indeed.com/viewjob?jk=741f313dfe0a4767</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddbf7440ad773888</t>
+          <t>https://www.indeed.com/viewjob?jk=fb549dda19deb4df</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b72f3a18139b7e54</t>
+          <t>https://www.indeed.com/viewjob?jk=ad53455736c94aa1</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7467917f2474b2e9</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf96d3e5672d2dd</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=741f313dfe0a4767</t>
+          <t>https://www.indeed.com/viewjob?jk=a2abd6bece93c89e</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb549dda19deb4df</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7b4a6316115547</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad53455736c94aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef2a2c6485dc8ce</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf96d3e5672d2dd</t>
+          <t>https://www.indeed.com/viewjob?jk=f8777195f0640326</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2abd6bece93c89e</t>
+          <t>https://www.indeed.com/viewjob?jk=8b251c80469648dc</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7b4a6316115547</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad5e6a6c6033f66</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef2a2c6485dc8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=4439501b54b34a7a</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8777195f0640326</t>
+          <t>https://www.indeed.com/viewjob?jk=1151c815185cd79e</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b251c80469648dc</t>
+          <t>https://www.indeed.com/viewjob?jk=d6614c39234b9da2</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad5e6a6c6033f66</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7e23c7f438f8c8</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4439501b54b34a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=e8663ead75611c2e</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1151c815185cd79e</t>
+          <t>https://www.indeed.com/viewjob?jk=51de78e580811e18</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6614c39234b9da2</t>
+          <t>https://www.indeed.com/viewjob?jk=548feeaa37b8c916</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7e23c7f438f8c8</t>
+          <t>https://www.indeed.com/viewjob?jk=9cf7d70224611ecc</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8663ead75611c2e</t>
+          <t>https://www.indeed.com/viewjob?jk=08e283453e85139f</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51de78e580811e18</t>
+          <t>https://www.indeed.com/viewjob?jk=ecaa2a1fd433f4a4</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=548feeaa37b8c916</t>
+          <t>https://www.indeed.com/viewjob?jk=dd01c10e73409cc8</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cf7d70224611ecc</t>
+          <t>https://www.indeed.com/viewjob?jk=3166241cc8c62f5d</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e283453e85139f</t>
+          <t>https://www.indeed.com/viewjob?jk=1572589542133e74</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecaa2a1fd433f4a4</t>
+          <t>https://www.indeed.com/viewjob?jk=a2ec3f9f81325aa0</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd01c10e73409cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=492f0c5d5b1026f4</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3166241cc8c62f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5a1bf124fcc939</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1572589542133e74</t>
+          <t>https://www.indeed.com/viewjob?jk=e7780a9fb7958201</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2ec3f9f81325aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=fd18a128a4672b91</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=492f0c5d5b1026f4</t>
+          <t>https://www.indeed.com/viewjob?jk=ea676aaaba70e2d7</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5a1bf124fcc939</t>
+          <t>https://www.indeed.com/viewjob?jk=cab3ba747ce4a550</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7780a9fb7958201</t>
+          <t>https://www.indeed.com/viewjob?jk=d65e39a595440fab</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd18a128a4672b91</t>
+          <t>https://www.indeed.com/viewjob?jk=55cb9c48e2f72a54</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea676aaaba70e2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=b3a01b8449781d9b</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab3ba747ce4a550</t>
+          <t>https://www.indeed.com/viewjob?jk=5fa7561c868d2097</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65e39a595440fab</t>
+          <t>https://www.indeed.com/viewjob?jk=3a729d7eaa711e20</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55cb9c48e2f72a54</t>
+          <t>https://www.indeed.com/viewjob?jk=1f022796cfb8fbcc</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3a01b8449781d9b</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c33b5572cf45fa</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fa7561c868d2097</t>
+          <t>https://www.indeed.com/viewjob?jk=8762f88f61ad7223</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a729d7eaa711e20</t>
+          <t>https://www.indeed.com/viewjob?jk=efdfb03d10f7ec00</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Senior Associate, Data Analytics Engineering</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Options Clearing Corporation</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f022796cfb8fbcc</t>
+          <t>https://www.indeed.com/viewjob?jk=1ad61eb5cd2a5633</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Fabletics</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c33b5572cf45fa</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac7bdb141d55008</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>DevOps Engineer, II</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NRCCUA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8762f88f61ad7223</t>
+          <t>https://www.indeed.com/viewjob?jk=e257db597eccae8d</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>DevOps Engineer, II</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Encoura</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdfb03d10f7ec00</t>
+          <t>https://www.indeed.com/viewjob?jk=22172251f6a1ea83</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer Expert</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Uber Freight</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,42 +3881,42 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Scala, Kafka, Oracle, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1f104bd0b18db7</t>
+          <t>https://www.indeed.com/viewjob?jk=1b1465e42f01feff</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Analytics Engineering</t>
+          <t>Sr. Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Options Clearing Corporation</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, dbt, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ad61eb5cd2a5633</t>
+          <t>https://www.indeed.com/viewjob?jk=ae7ce0b79b127907</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Fabletics</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac7bdb141d55008</t>
+          <t>https://www.indeed.com/viewjob?jk=dc99c4d09fcc8c74</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>DevOps Engineer, II</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>NRCCUA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e257db597eccae8d</t>
+          <t>https://www.indeed.com/viewjob?jk=b7994c3eb46bae42</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DevOps Engineer, II</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Encoura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,59 +4031,59 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22172251f6a1ea83</t>
+          <t>https://www.indeed.com/viewjob?jk=649242ee28a33ae5</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Uber Freight</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Scala, Kafka, Oracle, CI/CD, Maven</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b1465e42f01feff</t>
+          <t>https://www.indeed.com/viewjob?jk=4b46b87f1359f8f5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae7ce0b79b127907</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a7b9a70e68cf9f</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc99c4d09fcc8c74</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a148e3a41849d9</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2644095339b05a5</t>
+          <t>https://www.indeed.com/viewjob?jk=fa4b4fcc410a503a</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7994c3eb46bae42</t>
+          <t>https://www.indeed.com/viewjob?jk=6147a561d729a0dd</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=649242ee28a33ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab5bc5f32a7b9a0</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b46b87f1359f8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=29f309b16d064eae</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a7b9a70e68cf9f</t>
+          <t>https://www.indeed.com/viewjob?jk=f0b6e4cc0b843bf8</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a148e3a41849d9</t>
+          <t>https://www.indeed.com/viewjob?jk=9d739c3bc7cf38d1</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa4b4fcc410a503a</t>
+          <t>https://www.indeed.com/viewjob?jk=70aa889c4c9efda8</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6147a561d729a0dd</t>
+          <t>https://www.indeed.com/viewjob?jk=97557fcc3403a036</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab5bc5f32a7b9a0</t>
+          <t>https://www.indeed.com/viewjob?jk=01009226e788120d</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29f309b16d064eae</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b0eb4fb08e6514</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0b6e4cc0b843bf8</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7b1778e389048a</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d739c3bc7cf38d1</t>
+          <t>https://www.indeed.com/viewjob?jk=a5c63e693a3dd615</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70aa889c4c9efda8</t>
+          <t>https://www.indeed.com/viewjob?jk=91abed51133c7c23</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97557fcc3403a036</t>
+          <t>https://www.indeed.com/viewjob?jk=432b655803995623</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01009226e788120d</t>
+          <t>https://www.indeed.com/viewjob?jk=04006a1fe4e66850</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b0eb4fb08e6514</t>
+          <t>https://www.indeed.com/viewjob?jk=4786e7810dfbd42c</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7b1778e389048a</t>
+          <t>https://www.indeed.com/viewjob?jk=a73d9c78e32edfcb</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5c63e693a3dd615</t>
+          <t>https://www.indeed.com/viewjob?jk=f6e14d6ec4b8aeb0</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91abed51133c7c23</t>
+          <t>https://www.indeed.com/viewjob?jk=f49fd486a1470d4a</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432b655803995623</t>
+          <t>https://www.indeed.com/viewjob?jk=bb0d75494367b7de</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04006a1fe4e66850</t>
+          <t>https://www.indeed.com/viewjob?jk=3194fbbe9c9c6915</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4786e7810dfbd42c</t>
+          <t>https://www.indeed.com/viewjob?jk=28e73925baaee988</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a73d9c78e32edfcb</t>
+          <t>https://www.indeed.com/viewjob?jk=fd07d9e8d85d17ee</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6e14d6ec4b8aeb0</t>
+          <t>https://www.indeed.com/viewjob?jk=518960648e6b46f0</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f49fd486a1470d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5b4030fed54c3d</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb0d75494367b7de</t>
+          <t>https://www.indeed.com/viewjob?jk=25174fd8817164ea</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3194fbbe9c9c6915</t>
+          <t>https://www.indeed.com/viewjob?jk=69b7427915d34288</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e73925baaee988</t>
+          <t>https://www.indeed.com/viewjob?jk=4964a3b46fec8c52</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Cost Engineer – Data Analytics</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd07d9e8d85d17ee</t>
+          <t>https://www.indeed.com/viewjob?jk=69730719f6ab06e5</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Data Engineer / Database Management Specialist for Fish Data</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518960648e6b46f0</t>
+          <t>https://www.indeed.com/viewjob?jk=47ce35760bca7d80</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5b4030fed54c3d</t>
+          <t>https://www.indeed.com/viewjob?jk=308aad1cd4d5b8e2</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Sr Associate Engineer, IT Software</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25174fd8817164ea</t>
+          <t>https://www.indeed.com/viewjob?jk=8fda6cb70fb70e09</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b7427915d34288</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd22b9c4b47341c</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4964a3b46fec8c52</t>
+          <t>https://www.indeed.com/viewjob?jk=4edb47917f0e6215</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Cost Engineer – Data Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69730719f6ab06e5</t>
+          <t>https://www.indeed.com/viewjob?jk=e84f993a048191bd</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Data Engineer / Database Management Specialist for Fish Data</t>
+          <t>BI Engineer - Data Analytics</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ce35760bca7d80</t>
+          <t>https://www.indeed.com/viewjob?jk=ca97d35c293c8ce6</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Senior BI Analyst - IGEN</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Appleton, WI, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, dbt, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,102 +5431,102 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aad1cd4d5b8e2</t>
+          <t>https://www.indeed.com/viewjob?jk=acd6baf60c6afe77</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer, IT Software</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fda6cb70fb70e09</t>
+          <t>https://www.indeed.com/viewjob?jk=53279f54b14e6849</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd22b9c4b47341c</t>
+          <t>https://www.indeed.com/viewjob?jk=0a92d266fe841f72</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>Insight Software</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,32 +5536,32 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4edb47917f0e6215</t>
+          <t>https://www.indeed.com/viewjob?jk=4f17a3a493c5baa0</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>Gesa Credit Union</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Spokane Valley, WA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,32 +5571,32 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e84f993a048191bd</t>
+          <t>https://www.indeed.com/viewjob?jk=05b11f37b58c06df</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>BI Engineer - Data Analytics</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>Gesa Credit Union</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,32 +5606,32 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca97d35c293c8ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=9e166dda8b8fb2c2</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior BI Analyst - IGEN</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>Gesa Credit Union</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>Richland, WA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, dbt, Power BI, Tableau, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd6baf60c6afe77</t>
+          <t>https://www.indeed.com/viewjob?jk=38d66edddd66e10c</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Sr. Software Engineer - Shared Services</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SmartAsset</t>
+          <t>HeroDevs</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f326fc2210a7954</t>
+          <t>https://www.indeed.com/viewjob?jk=6847e3d78dab687e</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,34 +5701,34 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53279f54b14e6849</t>
+          <t>https://www.indeed.com/viewjob?jk=cc42c2a4e5140f69</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a92d266fe841f72</t>
+          <t>https://www.indeed.com/viewjob?jk=66e65258ac69fefd</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Insight Software</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,24 +5781,24 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f17a3a493c5baa0</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b8c309e1dd4b82</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Spokane Valley, WA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b11f37b58c06df</t>
+          <t>https://www.indeed.com/viewjob?jk=3f98038822e26dd8</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e166dda8b8fb2c2</t>
+          <t>https://www.indeed.com/viewjob?jk=a55ba7ce9c7c4713</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Richland, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38d66edddd66e10c</t>
+          <t>https://www.indeed.com/viewjob?jk=85557e4da3ee4405</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89dd9964d8bd40d3</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c9edfc26a261dd</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Youth Villages</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Chesterfield, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db40921aad59c33b</t>
+          <t>https://www.indeed.com/viewjob?jk=bc933305859d57b2</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Shared Services</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>HeroDevs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6847e3d78dab687e</t>
+          <t>https://www.indeed.com/viewjob?jk=18e6b1969d6c7210</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc42c2a4e5140f69</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e1d701408b5626</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66e65258ac69fefd</t>
+          <t>https://www.indeed.com/viewjob?jk=288dfb7ead95495d</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b8c309e1dd4b82</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa85911435d672d</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f98038822e26dd8</t>
+          <t>https://www.indeed.com/viewjob?jk=d9b1c071eb4265fc</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a55ba7ce9c7c4713</t>
+          <t>https://www.indeed.com/viewjob?jk=16f343db215cfb2f</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85557e4da3ee4405</t>
+          <t>https://www.indeed.com/viewjob?jk=c44c288bccc8a6a7</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c9edfc26a261dd</t>
+          <t>https://www.indeed.com/viewjob?jk=211ece43a6639e15</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc933305859d57b2</t>
+          <t>https://www.indeed.com/viewjob?jk=117b69fc0cf106cd</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18e6b1969d6c7210</t>
+          <t>https://www.indeed.com/viewjob?jk=3a31df839c27886a</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e1d701408b5626</t>
+          <t>https://www.indeed.com/viewjob?jk=c2e202fe647fc8c9</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=288dfb7ead95495d</t>
+          <t>https://www.indeed.com/viewjob?jk=7c1275067df0fefc</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fa85911435d672d</t>
+          <t>https://www.indeed.com/viewjob?jk=0b046a816c53c475</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9b1c071eb4265fc</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0dcc0f31186adf</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f343db215cfb2f</t>
+          <t>https://www.indeed.com/viewjob?jk=26a73c1c18e4feb1</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44c288bccc8a6a7</t>
+          <t>https://www.indeed.com/viewjob?jk=c162c04d00001e41</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211ece43a6639e15</t>
+          <t>https://www.indeed.com/viewjob?jk=d72aa3d302823165</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117b69fc0cf106cd</t>
+          <t>https://www.indeed.com/viewjob?jk=437542252a94a7bd</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a31df839c27886a</t>
+          <t>https://www.indeed.com/viewjob?jk=1db9b5fd4ad91c79</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2e202fe647fc8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=c338c18f5cc8b343</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c1275067df0fefc</t>
+          <t>https://www.indeed.com/viewjob?jk=9b85cee4884732fd</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b046a816c53c475</t>
+          <t>https://www.indeed.com/viewjob?jk=87011ec9083a8b23</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0dcc0f31186adf</t>
+          <t>https://www.indeed.com/viewjob?jk=c1d4cefa45bd4112</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26a73c1c18e4feb1</t>
+          <t>https://www.indeed.com/viewjob?jk=66e3413d7b223f3a</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c162c04d00001e41</t>
+          <t>https://www.indeed.com/viewjob?jk=5f780ced93a3bc16</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72aa3d302823165</t>
+          <t>https://www.indeed.com/viewjob?jk=5a4ad2ff105c8b83</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=437542252a94a7bd</t>
+          <t>https://www.indeed.com/viewjob?jk=430e2adbc8757712</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1db9b5fd4ad91c79</t>
+          <t>https://www.indeed.com/viewjob?jk=43daf093c3246e39</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c338c18f5cc8b343</t>
+          <t>https://www.indeed.com/viewjob?jk=90d2c0b1b77db71f</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b85cee4884732fd</t>
+          <t>https://www.indeed.com/viewjob?jk=db8c787399aa7569</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87011ec9083a8b23</t>
+          <t>https://www.indeed.com/viewjob?jk=afd791e19de5a0fe</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1d4cefa45bd4112</t>
+          <t>https://www.indeed.com/viewjob?jk=1e23b8b93066067d</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66e3413d7b223f3a</t>
+          <t>https://www.indeed.com/viewjob?jk=aa821c9250f94164</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7146,24 +7146,24 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f780ced93a3bc16</t>
+          <t>https://www.indeed.com/viewjob?jk=8f15f76b6c67bbdd</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>DevOps Engineer - Mid</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nalley Consulting</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -7181,24 +7181,24 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a4ad2ff105c8b83</t>
+          <t>https://www.indeed.com/viewjob?jk=35023775c057de52</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Event Hubs, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -7216,24 +7216,24 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=430e2adbc8757712</t>
+          <t>https://www.indeed.com/viewjob?jk=64c482ee7d2fd8be</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -7251,24 +7251,24 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43daf093c3246e39</t>
+          <t>https://www.indeed.com/viewjob?jk=a6b981d8b3e30244</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Teza Technologies</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -7286,24 +7286,24 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d2c0b1b77db71f</t>
+          <t>https://www.indeed.com/viewjob?jk=8521b827213a9dde</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -7321,24 +7321,24 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db8c787399aa7569</t>
+          <t>https://www.indeed.com/viewjob?jk=b971d4cbb76a50f0</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Ai Architect</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -7356,24 +7356,24 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd791e19de5a0fe</t>
+          <t>https://www.indeed.com/viewjob?jk=45b842ee858dea9c</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7381,332 +7381,17 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e23b8b93066067d</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>New Orleans, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D200" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa821c9250f94164</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D201" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f15f76b6c67bbdd</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>DevOps Engineer - Mid</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Nalley Consulting</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Doral, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D202" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35023775c057de52</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>Senior Applied AI Engineer</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D203" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=c3ac436669ece2e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>Database Architect</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>McKesson</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D204" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Event Hubs, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=64c482ee7d2fd8be</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Zoom Communications</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D205" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a6b981d8b3e30244</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Teza Technologies</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D206" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8521b827213a9dde</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Alight Solutions</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D207" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b971d4cbb76a50f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>Ai Architect</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Five Below</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D208" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=45b842ee858dea9c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-30.xlsx
+++ b/results/job_matches_2026-05-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G199"/>
+  <dimension ref="A1:G195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,25 +713,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - IGEN</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
+          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0ca36351ff88fb</t>
+          <t>https://www.indeed.com/viewjob?jk=330bf279fb8cd838</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330bf279fb8cd838</t>
+          <t>https://www.indeed.com/viewjob?jk=d0769674b72ae58f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cd40cf715d1757e</t>
+          <t>https://www.indeed.com/viewjob?jk=aef1c5cf0ee00174</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Senior Data Solutions Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3efe7a4e50700ee</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd4faeed9a50a59</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Sr Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alachua, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3185efffc8151880</t>
+          <t>https://www.indeed.com/viewjob?jk=1bcc3fe3fd715833</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bar Harbor, ME, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b53f7ddb0026dea4</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd2d99f50f24a3c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Data Engineer with AI/ML</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf3b9815a50b381</t>
+          <t>https://www.indeed.com/viewjob?jk=836bfed93aa23557</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Solutions Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd4faeed9a50a59</t>
+          <t>https://www.indeed.com/viewjob?jk=c250c7540d478f32</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Platform Engineer- 6 Month Assignment</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0769674b72ae58f</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5d273dd8b89dfc</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>Aptean</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aef1c5cf0ee00174</t>
+          <t>https://www.indeed.com/viewjob?jk=13c44a8aef4fd0a0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Aptean</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Kafka, PostgreSQL, MongoDB, Data Modeling</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cb9776bd0e7f4a</t>
+          <t>https://www.indeed.com/viewjob?jk=ef802648dc8c758d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
+          <t>Senior Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>Decagon</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd2d99f50f24a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=d3d218109f5a2e7c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer with AI/ML</t>
+          <t>Senior Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Decagon</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=836bfed93aa23557</t>
+          <t>https://www.indeed.com/viewjob?jk=cb96afd07bcd39f3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Platform Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Happy Returns, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c250c7540d478f32</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa757e1e92cc3c3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Platform Engineer- 6 Month Assignment</t>
+          <t>Sr. DevOps Engineer- Snowflake &amp; Azure</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5d273dd8b89dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=763fd8f53ea47c3f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Aptean</t>
+          <t>Echo Global Logistics</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13c44a8aef4fd0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=eae8bcb49c9597d5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud &amp; Digital Platform Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Aptean</t>
+          <t>Diality</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef802648dc8c758d</t>
+          <t>https://www.indeed.com/viewjob?jk=7fe3f1dbc64665df</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Infrastructure</t>
+          <t>Sr. Solutions Architect - Emerging</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Decagon</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3d218109f5a2e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=7afdce6cf8faaddf</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Infrastructure</t>
+          <t>Sr. Solutions Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Decagon</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb96afd07bcd39f3</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ce1a2957006a72</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Platform Software Engineer (Remote)</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Happy Returns, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Data Modeling</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa757e1e92cc3c3</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab00f608359b4fd</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer- Snowflake &amp; Azure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MAGNETO &amp; DIESEL INJECTOR SERVICE</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Humble, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hive, Sqoop, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763fd8f53ea47c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=d19cafe12d10dcef</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. Systems Engineer- Cloud Infrastructure Engineering</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Echo Global Logistics</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, GCP, Scala, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae8bcb49c9597d5</t>
+          <t>https://www.indeed.com/viewjob?jk=4de6e8c6244caa58</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud &amp; Digital Platform Architect</t>
+          <t>Senior Software Engineer - Infrastructure and Tools</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Diality</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fe3f1dbc64665df</t>
+          <t>https://www.indeed.com/viewjob?jk=92d9bf233ed60118</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Sr. Product Mgr. &amp; Enterprise App Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Vomela Companies</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Elk Grove Village, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Scala, Kafka, SQL Server, MongoDB, Power BI, Tableau, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab00f608359b4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=f0c1cd41ea8edf5b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MAGNETO &amp; DIESEL INJECTOR SERVICE</t>
+          <t>First Command Financial Services</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Humble, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hive, Sqoop, Spark, Scala, ETL, ELT</t>
+          <t>RDS, Data Factory, Scala, Oracle, SQL Server, NoSQL, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d19cafe12d10dcef</t>
+          <t>https://www.indeed.com/viewjob?jk=5a2bba3746f32469</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer- Cloud Infrastructure Engineering</t>
+          <t>Senior Sales Engineer, Commercial</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de6e8c6244caa58</t>
+          <t>https://www.indeed.com/viewjob?jk=0487f884b026bec9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Product Mgr. &amp; Enterprise App Developer</t>
+          <t>Software Engineer II - Full Stack Java</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Vomela Companies</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Elk Grove Village, IL, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, SQL Server, MongoDB, Power BI, Tableau, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0c1cd41ea8edf5b</t>
+          <t>https://www.indeed.com/viewjob?jk=2c274b0f05e69603</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>First Command Financial Services</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Scala, Oracle, SQL Server, NoSQL, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a2bba3746f32469</t>
+          <t>https://www.indeed.com/viewjob?jk=8f9b9650d1bc3a54</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0487f884b026bec9</t>
+          <t>https://www.indeed.com/viewjob?jk=efb82b07adb9feba</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer II - Full Stack Java</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c274b0f05e69603</t>
+          <t>https://www.indeed.com/viewjob?jk=65195644bb1b9e0b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Engineer/Solution Architect</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>andrew morgan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, NoSQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7604b89af99ba406</t>
+          <t>https://www.indeed.com/viewjob?jk=75e8ade515a41a57</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Product Foundations</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd2bfc17d54981e1</t>
+          <t>https://www.indeed.com/viewjob?jk=859e82cabfb17666</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Product Foundations</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0277abc185dfb7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f143b13efb8ce9b6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer 4</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Castlight</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ce519e36124f5ab</t>
+          <t>https://www.indeed.com/viewjob?jk=5a031b4964c2a255</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full Stack Developer -In office, Alpharetta, GA</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd5cf564b5b00</t>
+          <t>https://www.indeed.com/viewjob?jk=c4349cc4f94a5d87</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f9b9650d1bc3a54</t>
+          <t>https://www.indeed.com/viewjob?jk=e66448573f4489d1</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb82b07adb9feba</t>
+          <t>https://www.indeed.com/viewjob?jk=ddbf7440ad773888</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65195644bb1b9e0b</t>
+          <t>https://www.indeed.com/viewjob?jk=b72f3a18139b7e54</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e8ade515a41a57</t>
+          <t>https://www.indeed.com/viewjob?jk=7467917f2474b2e9</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859e82cabfb17666</t>
+          <t>https://www.indeed.com/viewjob?jk=741f313dfe0a4767</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f143b13efb8ce9b6</t>
+          <t>https://www.indeed.com/viewjob?jk=fb549dda19deb4df</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a031b4964c2a255</t>
+          <t>https://www.indeed.com/viewjob?jk=ad53455736c94aa1</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4349cc4f94a5d87</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf96d3e5672d2dd</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66448573f4489d1</t>
+          <t>https://www.indeed.com/viewjob?jk=a2abd6bece93c89e</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddbf7440ad773888</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7b4a6316115547</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b72f3a18139b7e54</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef2a2c6485dc8ce</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7467917f2474b2e9</t>
+          <t>https://www.indeed.com/viewjob?jk=f8777195f0640326</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=741f313dfe0a4767</t>
+          <t>https://www.indeed.com/viewjob?jk=8b251c80469648dc</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb549dda19deb4df</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad5e6a6c6033f66</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad53455736c94aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=4439501b54b34a7a</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf96d3e5672d2dd</t>
+          <t>https://www.indeed.com/viewjob?jk=1151c815185cd79e</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2abd6bece93c89e</t>
+          <t>https://www.indeed.com/viewjob?jk=d6614c39234b9da2</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7b4a6316115547</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7e23c7f438f8c8</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef2a2c6485dc8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=e8663ead75611c2e</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8777195f0640326</t>
+          <t>https://www.indeed.com/viewjob?jk=51de78e580811e18</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b251c80469648dc</t>
+          <t>https://www.indeed.com/viewjob?jk=548feeaa37b8c916</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad5e6a6c6033f66</t>
+          <t>https://www.indeed.com/viewjob?jk=9cf7d70224611ecc</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4439501b54b34a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=08e283453e85139f</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1151c815185cd79e</t>
+          <t>https://www.indeed.com/viewjob?jk=ecaa2a1fd433f4a4</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6614c39234b9da2</t>
+          <t>https://www.indeed.com/viewjob?jk=dd01c10e73409cc8</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7e23c7f438f8c8</t>
+          <t>https://www.indeed.com/viewjob?jk=3166241cc8c62f5d</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8663ead75611c2e</t>
+          <t>https://www.indeed.com/viewjob?jk=1572589542133e74</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51de78e580811e18</t>
+          <t>https://www.indeed.com/viewjob?jk=a2ec3f9f81325aa0</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=548feeaa37b8c916</t>
+          <t>https://www.indeed.com/viewjob?jk=492f0c5d5b1026f4</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cf7d70224611ecc</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5a1bf124fcc939</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e283453e85139f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7780a9fb7958201</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecaa2a1fd433f4a4</t>
+          <t>https://www.indeed.com/viewjob?jk=fd18a128a4672b91</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd01c10e73409cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=ea676aaaba70e2d7</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3166241cc8c62f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=cab3ba747ce4a550</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1572589542133e74</t>
+          <t>https://www.indeed.com/viewjob?jk=d65e39a595440fab</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2ec3f9f81325aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=55cb9c48e2f72a54</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=492f0c5d5b1026f4</t>
+          <t>https://www.indeed.com/viewjob?jk=b3a01b8449781d9b</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5a1bf124fcc939</t>
+          <t>https://www.indeed.com/viewjob?jk=5fa7561c868d2097</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7780a9fb7958201</t>
+          <t>https://www.indeed.com/viewjob?jk=3a729d7eaa711e20</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd18a128a4672b91</t>
+          <t>https://www.indeed.com/viewjob?jk=1f022796cfb8fbcc</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea676aaaba70e2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c33b5572cf45fa</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab3ba747ce4a550</t>
+          <t>https://www.indeed.com/viewjob?jk=8762f88f61ad7223</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65e39a595440fab</t>
+          <t>https://www.indeed.com/viewjob?jk=efdfb03d10f7ec00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Senior Software Engineer - Distributed Data Systems</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55cb9c48e2f72a54</t>
+          <t>https://www.indeed.com/viewjob?jk=68f494d2abfb9b3a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Senior Software Engineer - Distributed Data Systems</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3a01b8449781d9b</t>
+          <t>https://www.indeed.com/viewjob?jk=35301f7890450ed0</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Senior Software Engineer - Distributed Data Systems</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fa7561c868d2097</t>
+          <t>https://www.indeed.com/viewjob?jk=f178ac0bdca2782a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Senior Associate, Data Analytics Engineering</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Options Clearing Corporation</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a729d7eaa711e20</t>
+          <t>https://www.indeed.com/viewjob?jk=1ad61eb5cd2a5633</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Fabletics</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f022796cfb8fbcc</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac7bdb141d55008</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>DevOps Engineer, II</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NRCCUA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,67 +3646,67 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c33b5572cf45fa</t>
+          <t>https://www.indeed.com/viewjob?jk=e257db597eccae8d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Uber Freight</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Scala, Kafka, Oracle, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8762f88f61ad7223</t>
+          <t>https://www.indeed.com/viewjob?jk=1b1465e42f01feff</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Senior Software Engineer - Fullstack</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdfb03d10f7ec00</t>
+          <t>https://www.indeed.com/viewjob?jk=6e1d5edd7f6cfacc</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Analytics Engineering</t>
+          <t>Sr. Solutions Engineer - GSI's and FinTech Data</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Options Clearing Corporation</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, dbt, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ad61eb5cd2a5633</t>
+          <t>https://www.indeed.com/viewjob?jk=44ec35e1f7566eb4</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Solutions Engineer - Financial Services (Insurance)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Fabletics</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac7bdb141d55008</t>
+          <t>https://www.indeed.com/viewjob?jk=df17d8e1960c7150</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>DevOps Engineer, II</t>
+          <t>Sr. Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>NRCCUA</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e257db597eccae8d</t>
+          <t>https://www.indeed.com/viewjob?jk=ae7ce0b79b127907</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DevOps Engineer, II</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Encoura</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,59 +3856,59 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22172251f6a1ea83</t>
+          <t>https://www.indeed.com/viewjob?jk=dc99c4d09fcc8c74</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Uber Freight</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Scala, Kafka, Oracle, CI/CD, Maven</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b1465e42f01feff</t>
+          <t>https://www.indeed.com/viewjob?jk=b7994c3eb46bae42</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae7ce0b79b127907</t>
+          <t>https://www.indeed.com/viewjob?jk=649242ee28a33ae5</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc99c4d09fcc8c74</t>
+          <t>https://www.indeed.com/viewjob?jk=4b46b87f1359f8f5</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7994c3eb46bae42</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a7b9a70e68cf9f</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=649242ee28a33ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a148e3a41849d9</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b46b87f1359f8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=fa4b4fcc410a503a</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a7b9a70e68cf9f</t>
+          <t>https://www.indeed.com/viewjob?jk=6147a561d729a0dd</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a148e3a41849d9</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab5bc5f32a7b9a0</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa4b4fcc410a503a</t>
+          <t>https://www.indeed.com/viewjob?jk=29f309b16d064eae</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6147a561d729a0dd</t>
+          <t>https://www.indeed.com/viewjob?jk=f0b6e4cc0b843bf8</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab5bc5f32a7b9a0</t>
+          <t>https://www.indeed.com/viewjob?jk=9d739c3bc7cf38d1</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29f309b16d064eae</t>
+          <t>https://www.indeed.com/viewjob?jk=70aa889c4c9efda8</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0b6e4cc0b843bf8</t>
+          <t>https://www.indeed.com/viewjob?jk=97557fcc3403a036</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d739c3bc7cf38d1</t>
+          <t>https://www.indeed.com/viewjob?jk=01009226e788120d</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70aa889c4c9efda8</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b0eb4fb08e6514</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97557fcc3403a036</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7b1778e389048a</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01009226e788120d</t>
+          <t>https://www.indeed.com/viewjob?jk=a5c63e693a3dd615</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b0eb4fb08e6514</t>
+          <t>https://www.indeed.com/viewjob?jk=91abed51133c7c23</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7b1778e389048a</t>
+          <t>https://www.indeed.com/viewjob?jk=432b655803995623</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5c63e693a3dd615</t>
+          <t>https://www.indeed.com/viewjob?jk=04006a1fe4e66850</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91abed51133c7c23</t>
+          <t>https://www.indeed.com/viewjob?jk=4786e7810dfbd42c</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432b655803995623</t>
+          <t>https://www.indeed.com/viewjob?jk=a73d9c78e32edfcb</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04006a1fe4e66850</t>
+          <t>https://www.indeed.com/viewjob?jk=f6e14d6ec4b8aeb0</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4786e7810dfbd42c</t>
+          <t>https://www.indeed.com/viewjob?jk=f49fd486a1470d4a</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a73d9c78e32edfcb</t>
+          <t>https://www.indeed.com/viewjob?jk=bb0d75494367b7de</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6e14d6ec4b8aeb0</t>
+          <t>https://www.indeed.com/viewjob?jk=3194fbbe9c9c6915</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f49fd486a1470d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=28e73925baaee988</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb0d75494367b7de</t>
+          <t>https://www.indeed.com/viewjob?jk=fd07d9e8d85d17ee</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3194fbbe9c9c6915</t>
+          <t>https://www.indeed.com/viewjob?jk=518960648e6b46f0</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e73925baaee988</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5b4030fed54c3d</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd07d9e8d85d17ee</t>
+          <t>https://www.indeed.com/viewjob?jk=25174fd8817164ea</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518960648e6b46f0</t>
+          <t>https://www.indeed.com/viewjob?jk=69b7427915d34288</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5b4030fed54c3d</t>
+          <t>https://www.indeed.com/viewjob?jk=4964a3b46fec8c52</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25174fd8817164ea</t>
+          <t>https://www.indeed.com/viewjob?jk=308aad1cd4d5b8e2</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Software Engineer - Fullstack</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b7427915d34288</t>
+          <t>https://www.indeed.com/viewjob?jk=3d41030c2a031bc3</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Software Engineer - Fullstack</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4964a3b46fec8c52</t>
+          <t>https://www.indeed.com/viewjob?jk=9e37bcb174213c7a</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Cost Engineer – Data Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69730719f6ab06e5</t>
+          <t>https://www.indeed.com/viewjob?jk=4edb47917f0e6215</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Data Engineer / Database Management Specialist for Fish Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ce35760bca7d80</t>
+          <t>https://www.indeed.com/viewjob?jk=e84f993a048191bd</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>BI Engineer - Data Analytics</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,32 +5221,32 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aad1cd4d5b8e2</t>
+          <t>https://www.indeed.com/viewjob?jk=ca97d35c293c8ce6</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer, IT Software</t>
+          <t>Senior Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,32 +5256,32 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fda6cb70fb70e09</t>
+          <t>https://www.indeed.com/viewjob?jk=9446abbf0a9e21d5</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,102 +5291,102 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd22b9c4b47341c</t>
+          <t>https://www.indeed.com/viewjob?jk=4cf9f394fc466cab</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4edb47917f0e6215</t>
+          <t>https://www.indeed.com/viewjob?jk=53279f54b14e6849</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e84f993a048191bd</t>
+          <t>https://www.indeed.com/viewjob?jk=0a92d266fe841f72</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BI Engineer - Data Analytics</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>Insight Software</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,32 +5396,32 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca97d35c293c8ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=4f17a3a493c5baa0</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior BI Analyst - IGEN</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>Gesa Credit Union</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>Spokane Valley, WA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, dbt, Power BI, Tableau, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd6baf60c6afe77</t>
+          <t>https://www.indeed.com/viewjob?jk=05b11f37b58c06df</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Gesa Credit Union</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53279f54b14e6849</t>
+          <t>https://www.indeed.com/viewjob?jk=9e166dda8b8fb2c2</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Gesa Credit Union</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Richland, WA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,29 +5491,29 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a92d266fe841f72</t>
+          <t>https://www.indeed.com/viewjob?jk=38d66edddd66e10c</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr. Software Engineer - Shared Services</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Insight Software</t>
+          <t>HeroDevs</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f17a3a493c5baa0</t>
+          <t>https://www.indeed.com/viewjob?jk=6847e3d78dab687e</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spokane Valley, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b11f37b58c06df</t>
+          <t>https://www.indeed.com/viewjob?jk=cc42c2a4e5140f69</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e166dda8b8fb2c2</t>
+          <t>https://www.indeed.com/viewjob?jk=66e65258ac69fefd</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Richland, WA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38d66edddd66e10c</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b8c309e1dd4b82</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Shared Services</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>HeroDevs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6847e3d78dab687e</t>
+          <t>https://www.indeed.com/viewjob?jk=3f98038822e26dd8</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc42c2a4e5140f69</t>
+          <t>https://www.indeed.com/viewjob?jk=a55ba7ce9c7c4713</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66e65258ac69fefd</t>
+          <t>https://www.indeed.com/viewjob?jk=85557e4da3ee4405</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b8c309e1dd4b82</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c9edfc26a261dd</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f98038822e26dd8</t>
+          <t>https://www.indeed.com/viewjob?jk=bc933305859d57b2</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a55ba7ce9c7c4713</t>
+          <t>https://www.indeed.com/viewjob?jk=18e6b1969d6c7210</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85557e4da3ee4405</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e1d701408b5626</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c9edfc26a261dd</t>
+          <t>https://www.indeed.com/viewjob?jk=288dfb7ead95495d</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc933305859d57b2</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa85911435d672d</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18e6b1969d6c7210</t>
+          <t>https://www.indeed.com/viewjob?jk=d9b1c071eb4265fc</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e1d701408b5626</t>
+          <t>https://www.indeed.com/viewjob?jk=16f343db215cfb2f</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=288dfb7ead95495d</t>
+          <t>https://www.indeed.com/viewjob?jk=c44c288bccc8a6a7</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fa85911435d672d</t>
+          <t>https://www.indeed.com/viewjob?jk=211ece43a6639e15</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9b1c071eb4265fc</t>
+          <t>https://www.indeed.com/viewjob?jk=117b69fc0cf106cd</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f343db215cfb2f</t>
+          <t>https://www.indeed.com/viewjob?jk=3a31df839c27886a</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44c288bccc8a6a7</t>
+          <t>https://www.indeed.com/viewjob?jk=c2e202fe647fc8c9</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211ece43a6639e15</t>
+          <t>https://www.indeed.com/viewjob?jk=7c1275067df0fefc</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117b69fc0cf106cd</t>
+          <t>https://www.indeed.com/viewjob?jk=0b046a816c53c475</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a31df839c27886a</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0dcc0f31186adf</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2e202fe647fc8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=26a73c1c18e4feb1</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c1275067df0fefc</t>
+          <t>https://www.indeed.com/viewjob?jk=c162c04d00001e41</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b046a816c53c475</t>
+          <t>https://www.indeed.com/viewjob?jk=d72aa3d302823165</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0dcc0f31186adf</t>
+          <t>https://www.indeed.com/viewjob?jk=437542252a94a7bd</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26a73c1c18e4feb1</t>
+          <t>https://www.indeed.com/viewjob?jk=1db9b5fd4ad91c79</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c162c04d00001e41</t>
+          <t>https://www.indeed.com/viewjob?jk=c338c18f5cc8b343</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72aa3d302823165</t>
+          <t>https://www.indeed.com/viewjob?jk=9b85cee4884732fd</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=437542252a94a7bd</t>
+          <t>https://www.indeed.com/viewjob?jk=87011ec9083a8b23</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1db9b5fd4ad91c79</t>
+          <t>https://www.indeed.com/viewjob?jk=c1d4cefa45bd4112</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c338c18f5cc8b343</t>
+          <t>https://www.indeed.com/viewjob?jk=66e3413d7b223f3a</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b85cee4884732fd</t>
+          <t>https://www.indeed.com/viewjob?jk=5f780ced93a3bc16</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87011ec9083a8b23</t>
+          <t>https://www.indeed.com/viewjob?jk=5a4ad2ff105c8b83</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1d4cefa45bd4112</t>
+          <t>https://www.indeed.com/viewjob?jk=430e2adbc8757712</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66e3413d7b223f3a</t>
+          <t>https://www.indeed.com/viewjob?jk=43daf093c3246e39</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f780ced93a3bc16</t>
+          <t>https://www.indeed.com/viewjob?jk=90d2c0b1b77db71f</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a4ad2ff105c8b83</t>
+          <t>https://www.indeed.com/viewjob?jk=db8c787399aa7569</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=430e2adbc8757712</t>
+          <t>https://www.indeed.com/viewjob?jk=afd791e19de5a0fe</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43daf093c3246e39</t>
+          <t>https://www.indeed.com/viewjob?jk=1e23b8b93066067d</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d2c0b1b77db71f</t>
+          <t>https://www.indeed.com/viewjob?jk=aa821c9250f94164</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -7006,24 +7006,24 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db8c787399aa7569</t>
+          <t>https://www.indeed.com/viewjob?jk=8f15f76b6c67bbdd</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>DevOps Engineer - Mid</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nalley Consulting</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7041,24 +7041,24 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd791e19de5a0fe</t>
+          <t>https://www.indeed.com/viewjob?jk=35023775c057de52</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7066,34 +7066,34 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e23b8b93066067d</t>
+          <t>https://www.indeed.com/viewjob?jk=c3ac436669ece2e5</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Senior Software Engineer - Application Traffic team</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -7111,24 +7111,24 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa821c9250f94164</t>
+          <t>https://www.indeed.com/viewjob?jk=dc893f4e11c92275</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Event Hubs, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -7146,24 +7146,24 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f15f76b6c67bbdd</t>
+          <t>https://www.indeed.com/viewjob?jk=64c482ee7d2fd8be</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Mid</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Nalley Consulting</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -7181,24 +7181,24 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35023775c057de52</t>
+          <t>https://www.indeed.com/viewjob?jk=a6b981d8b3e30244</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Ai Architect</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -7216,24 +7216,24 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64c482ee7d2fd8be</t>
+          <t>https://www.indeed.com/viewjob?jk=45b842ee858dea9c</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Solutions Engineer - AI Natives Business</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -7251,147 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6b981d8b3e30244</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Teza Technologies</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D196" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8521b827213a9dde</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Alight Solutions</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D197" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b971d4cbb76a50f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>Ai Architect</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Five Below</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D198" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=45b842ee858dea9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>Senior Applied AI Engineer</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D199" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c3ac436669ece2e5</t>
+          <t>https://www.indeed.com/viewjob?jk=d884fcaeec353d16</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-30.xlsx
+++ b/results/job_matches_2026-05-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G195"/>
+  <dimension ref="A1:G188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,25 +818,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Solutions Architect</t>
+          <t>Sr Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd4faeed9a50a59</t>
+          <t>https://www.indeed.com/viewjob?jk=1bcc3fe3fd715833</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Infrastructure</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bcc3fe3fd715833</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd2d99f50f24a3c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
+          <t>Data Engineer with AI/ML</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd2d99f50f24a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=836bfed93aa23557</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer with AI/ML</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=836bfed93aa23557</t>
+          <t>https://www.indeed.com/viewjob?jk=c250c7540d478f32</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform Engineer- 6 Month Assignment</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c250c7540d478f32</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5d273dd8b89dfc</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Platform Engineer- 6 Month Assignment</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>Aptean</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5d273dd8b89dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=13c44a8aef4fd0a0</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13c44a8aef4fd0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=ef802648dc8c758d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aptean</t>
+          <t>Decagon</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef802648dc8c758d</t>
+          <t>https://www.indeed.com/viewjob?jk=d3d218109f5a2e7c</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3d218109f5a2e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=cb96afd07bcd39f3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Infrastructure</t>
+          <t>Platform Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Decagon</t>
+          <t>Happy Returns, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb96afd07bcd39f3</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa757e1e92cc3c3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Platform Software Engineer (Remote)</t>
+          <t>Sr. DevOps Engineer- Snowflake &amp; Azure</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Happy Returns, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa757e1e92cc3c3</t>
+          <t>https://www.indeed.com/viewjob?jk=763fd8f53ea47c3f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer- Snowflake &amp; Azure</t>
+          <t>Cloud &amp; Digital Platform Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Diality</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763fd8f53ea47c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=7fe3f1dbc64665df</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. Solutions Architect - Emerging</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Echo Global Logistics</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, GCP, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae8bcb49c9597d5</t>
+          <t>https://www.indeed.com/viewjob?jk=7afdce6cf8faaddf</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cloud &amp; Digital Platform Architect</t>
+          <t>Sr. Solutions Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Diality</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fe3f1dbc64665df</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ce1a2957006a72</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Emerging</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7afdce6cf8faaddf</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab00f608359b4fd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>MAGNETO &amp; DIESEL INJECTOR SERVICE</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Humble, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hive, Sqoop, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ce1a2957006a72</t>
+          <t>https://www.indeed.com/viewjob?jk=d19cafe12d10dcef</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Sr. Systems Engineer- Cloud Infrastructure Engineering</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab00f608359b4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=4de6e8c6244caa58</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Infrastructure and Tools</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MAGNETO &amp; DIESEL INJECTOR SERVICE</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Humble, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hive, Sqoop, Spark, Scala, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d19cafe12d10dcef</t>
+          <t>https://www.indeed.com/viewjob?jk=92d9bf233ed60118</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer- Cloud Infrastructure Engineering</t>
+          <t>Sr. Product Mgr. &amp; Enterprise App Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>The Vomela Companies</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Elk Grove Village, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Scala, Kafka, SQL Server, MongoDB, Power BI, Tableau, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de6e8c6244caa58</t>
+          <t>https://www.indeed.com/viewjob?jk=f0c1cd41ea8edf5b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Infrastructure and Tools</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>First Command Financial Services</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow</t>
+          <t>RDS, Data Factory, Scala, Oracle, SQL Server, NoSQL, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92d9bf233ed60118</t>
+          <t>https://www.indeed.com/viewjob?jk=5a2bba3746f32469</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Product Mgr. &amp; Enterprise App Developer</t>
+          <t>Senior Sales Engineer, Commercial</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The Vomela Companies</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Elk Grove Village, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, SQL Server, MongoDB, Power BI, Tableau, CI/CD, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0c1cd41ea8edf5b</t>
+          <t>https://www.indeed.com/viewjob?jk=0487f884b026bec9</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>First Command Financial Services</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Scala, Oracle, SQL Server, NoSQL, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a2bba3746f32469</t>
+          <t>https://www.indeed.com/viewjob?jk=8f9b9650d1bc3a54</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0487f884b026bec9</t>
+          <t>https://www.indeed.com/viewjob?jk=efb82b07adb9feba</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer II - Full Stack Java</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c274b0f05e69603</t>
+          <t>https://www.indeed.com/viewjob?jk=65195644bb1b9e0b</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f9b9650d1bc3a54</t>
+          <t>https://www.indeed.com/viewjob?jk=75e8ade515a41a57</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb82b07adb9feba</t>
+          <t>https://www.indeed.com/viewjob?jk=859e82cabfb17666</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65195644bb1b9e0b</t>
+          <t>https://www.indeed.com/viewjob?jk=f143b13efb8ce9b6</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e8ade515a41a57</t>
+          <t>https://www.indeed.com/viewjob?jk=5a031b4964c2a255</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859e82cabfb17666</t>
+          <t>https://www.indeed.com/viewjob?jk=c4349cc4f94a5d87</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f143b13efb8ce9b6</t>
+          <t>https://www.indeed.com/viewjob?jk=e66448573f4489d1</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a031b4964c2a255</t>
+          <t>https://www.indeed.com/viewjob?jk=ddbf7440ad773888</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4349cc4f94a5d87</t>
+          <t>https://www.indeed.com/viewjob?jk=b72f3a18139b7e54</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66448573f4489d1</t>
+          <t>https://www.indeed.com/viewjob?jk=7467917f2474b2e9</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddbf7440ad773888</t>
+          <t>https://www.indeed.com/viewjob?jk=741f313dfe0a4767</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b72f3a18139b7e54</t>
+          <t>https://www.indeed.com/viewjob?jk=fb549dda19deb4df</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7467917f2474b2e9</t>
+          <t>https://www.indeed.com/viewjob?jk=ad53455736c94aa1</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=741f313dfe0a4767</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf96d3e5672d2dd</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb549dda19deb4df</t>
+          <t>https://www.indeed.com/viewjob?jk=a2abd6bece93c89e</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad53455736c94aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7b4a6316115547</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf96d3e5672d2dd</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef2a2c6485dc8ce</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2abd6bece93c89e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8777195f0640326</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7b4a6316115547</t>
+          <t>https://www.indeed.com/viewjob?jk=8b251c80469648dc</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef2a2c6485dc8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad5e6a6c6033f66</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8777195f0640326</t>
+          <t>https://www.indeed.com/viewjob?jk=4439501b54b34a7a</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b251c80469648dc</t>
+          <t>https://www.indeed.com/viewjob?jk=1151c815185cd79e</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad5e6a6c6033f66</t>
+          <t>https://www.indeed.com/viewjob?jk=d6614c39234b9da2</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4439501b54b34a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7e23c7f438f8c8</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1151c815185cd79e</t>
+          <t>https://www.indeed.com/viewjob?jk=e8663ead75611c2e</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6614c39234b9da2</t>
+          <t>https://www.indeed.com/viewjob?jk=51de78e580811e18</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7e23c7f438f8c8</t>
+          <t>https://www.indeed.com/viewjob?jk=548feeaa37b8c916</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8663ead75611c2e</t>
+          <t>https://www.indeed.com/viewjob?jk=9cf7d70224611ecc</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51de78e580811e18</t>
+          <t>https://www.indeed.com/viewjob?jk=08e283453e85139f</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=548feeaa37b8c916</t>
+          <t>https://www.indeed.com/viewjob?jk=ecaa2a1fd433f4a4</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cf7d70224611ecc</t>
+          <t>https://www.indeed.com/viewjob?jk=dd01c10e73409cc8</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e283453e85139f</t>
+          <t>https://www.indeed.com/viewjob?jk=3166241cc8c62f5d</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecaa2a1fd433f4a4</t>
+          <t>https://www.indeed.com/viewjob?jk=1572589542133e74</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd01c10e73409cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=a2ec3f9f81325aa0</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3166241cc8c62f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=492f0c5d5b1026f4</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1572589542133e74</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5a1bf124fcc939</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2ec3f9f81325aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=e7780a9fb7958201</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=492f0c5d5b1026f4</t>
+          <t>https://www.indeed.com/viewjob?jk=fd18a128a4672b91</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5a1bf124fcc939</t>
+          <t>https://www.indeed.com/viewjob?jk=ea676aaaba70e2d7</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7780a9fb7958201</t>
+          <t>https://www.indeed.com/viewjob?jk=cab3ba747ce4a550</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd18a128a4672b91</t>
+          <t>https://www.indeed.com/viewjob?jk=d65e39a595440fab</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea676aaaba70e2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=55cb9c48e2f72a54</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab3ba747ce4a550</t>
+          <t>https://www.indeed.com/viewjob?jk=b3a01b8449781d9b</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65e39a595440fab</t>
+          <t>https://www.indeed.com/viewjob?jk=5fa7561c868d2097</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55cb9c48e2f72a54</t>
+          <t>https://www.indeed.com/viewjob?jk=3a729d7eaa711e20</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3a01b8449781d9b</t>
+          <t>https://www.indeed.com/viewjob?jk=1f022796cfb8fbcc</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fa7561c868d2097</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c33b5572cf45fa</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a729d7eaa711e20</t>
+          <t>https://www.indeed.com/viewjob?jk=8762f88f61ad7223</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f022796cfb8fbcc</t>
+          <t>https://www.indeed.com/viewjob?jk=efdfb03d10f7ec00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Senior Software Engineer - Distributed Data Systems</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c33b5572cf45fa</t>
+          <t>https://www.indeed.com/viewjob?jk=68f494d2abfb9b3a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Senior Software Engineer - Distributed Data Systems</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8762f88f61ad7223</t>
+          <t>https://www.indeed.com/viewjob?jk=35301f7890450ed0</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Senior Software Engineer - Distributed Data Systems</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdfb03d10f7ec00</t>
+          <t>https://www.indeed.com/viewjob?jk=f178ac0bdca2782a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Distributed Data Systems</t>
+          <t>Senior Associate, Data Analytics Engineering</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Options Clearing Corporation</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f494d2abfb9b3a</t>
+          <t>https://www.indeed.com/viewjob?jk=1ad61eb5cd2a5633</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Distributed Data Systems</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Fabletics</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Time Travel</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35301f7890450ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac7bdb141d55008</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Distributed Data Systems</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Uber Freight</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Scala, Kafka, Oracle, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f178ac0bdca2782a</t>
+          <t>https://www.indeed.com/viewjob?jk=1b1465e42f01feff</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Analytics Engineering</t>
+          <t>Senior Software Engineer - Fullstack</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Options Clearing Corporation</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, dbt, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ad61eb5cd2a5633</t>
+          <t>https://www.indeed.com/viewjob?jk=6e1d5edd7f6cfacc</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Solutions Engineer - GSI's and FinTech Data</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Fabletics</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac7bdb141d55008</t>
+          <t>https://www.indeed.com/viewjob?jk=44ec35e1f7566eb4</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DevOps Engineer, II</t>
+          <t>Sr. Solutions Engineer - Financial Services (Insurance)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>NRCCUA</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,67 +3646,67 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e257db597eccae8d</t>
+          <t>https://www.indeed.com/viewjob?jk=df17d8e1960c7150</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Sr. Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Uber Freight</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Scala, Kafka, Oracle, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b1465e42f01feff</t>
+          <t>https://www.indeed.com/viewjob?jk=ae7ce0b79b127907</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Fullstack</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e1d5edd7f6cfacc</t>
+          <t>https://www.indeed.com/viewjob?jk=dc99c4d09fcc8c74</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - GSI's and FinTech Data</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44ec35e1f7566eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=b7994c3eb46bae42</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Financial Services (Insurance)</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df17d8e1960c7150</t>
+          <t>https://www.indeed.com/viewjob?jk=649242ee28a33ae5</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae7ce0b79b127907</t>
+          <t>https://www.indeed.com/viewjob?jk=4b46b87f1359f8f5</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc99c4d09fcc8c74</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a7b9a70e68cf9f</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7994c3eb46bae42</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a148e3a41849d9</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=649242ee28a33ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=fa4b4fcc410a503a</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b46b87f1359f8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=6147a561d729a0dd</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a7b9a70e68cf9f</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab5bc5f32a7b9a0</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a148e3a41849d9</t>
+          <t>https://www.indeed.com/viewjob?jk=29f309b16d064eae</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa4b4fcc410a503a</t>
+          <t>https://www.indeed.com/viewjob?jk=f0b6e4cc0b843bf8</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6147a561d729a0dd</t>
+          <t>https://www.indeed.com/viewjob?jk=9d739c3bc7cf38d1</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab5bc5f32a7b9a0</t>
+          <t>https://www.indeed.com/viewjob?jk=70aa889c4c9efda8</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29f309b16d064eae</t>
+          <t>https://www.indeed.com/viewjob?jk=97557fcc3403a036</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0b6e4cc0b843bf8</t>
+          <t>https://www.indeed.com/viewjob?jk=01009226e788120d</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d739c3bc7cf38d1</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b0eb4fb08e6514</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70aa889c4c9efda8</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7b1778e389048a</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97557fcc3403a036</t>
+          <t>https://www.indeed.com/viewjob?jk=a5c63e693a3dd615</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01009226e788120d</t>
+          <t>https://www.indeed.com/viewjob?jk=91abed51133c7c23</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b0eb4fb08e6514</t>
+          <t>https://www.indeed.com/viewjob?jk=432b655803995623</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7b1778e389048a</t>
+          <t>https://www.indeed.com/viewjob?jk=04006a1fe4e66850</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5c63e693a3dd615</t>
+          <t>https://www.indeed.com/viewjob?jk=4786e7810dfbd42c</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91abed51133c7c23</t>
+          <t>https://www.indeed.com/viewjob?jk=a73d9c78e32edfcb</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432b655803995623</t>
+          <t>https://www.indeed.com/viewjob?jk=f6e14d6ec4b8aeb0</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04006a1fe4e66850</t>
+          <t>https://www.indeed.com/viewjob?jk=f49fd486a1470d4a</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4786e7810dfbd42c</t>
+          <t>https://www.indeed.com/viewjob?jk=bb0d75494367b7de</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a73d9c78e32edfcb</t>
+          <t>https://www.indeed.com/viewjob?jk=3194fbbe9c9c6915</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6e14d6ec4b8aeb0</t>
+          <t>https://www.indeed.com/viewjob?jk=28e73925baaee988</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f49fd486a1470d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=fd07d9e8d85d17ee</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb0d75494367b7de</t>
+          <t>https://www.indeed.com/viewjob?jk=518960648e6b46f0</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3194fbbe9c9c6915</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5b4030fed54c3d</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e73925baaee988</t>
+          <t>https://www.indeed.com/viewjob?jk=25174fd8817164ea</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd07d9e8d85d17ee</t>
+          <t>https://www.indeed.com/viewjob?jk=69b7427915d34288</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518960648e6b46f0</t>
+          <t>https://www.indeed.com/viewjob?jk=4964a3b46fec8c52</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5b4030fed54c3d</t>
+          <t>https://www.indeed.com/viewjob?jk=308aad1cd4d5b8e2</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Software Engineer - Fullstack</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25174fd8817164ea</t>
+          <t>https://www.indeed.com/viewjob?jk=3d41030c2a031bc3</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Software Engineer - Fullstack</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b7427915d34288</t>
+          <t>https://www.indeed.com/viewjob?jk=9e37bcb174213c7a</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4964a3b46fec8c52</t>
+          <t>https://www.indeed.com/viewjob?jk=4edb47917f0e6215</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,14 +5046,14 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aad1cd4d5b8e2</t>
+          <t>https://www.indeed.com/viewjob?jk=e84f993a048191bd</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Fullstack</t>
+          <t>Senior Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -5081,14 +5081,14 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d41030c2a031bc3</t>
+          <t>https://www.indeed.com/viewjob?jk=9446abbf0a9e21d5</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Fullstack</t>
+          <t>Senior Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5098,11 +5098,11 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -5116,102 +5116,102 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e37bcb174213c7a</t>
+          <t>https://www.indeed.com/viewjob?jk=4cf9f394fc466cab</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4edb47917f0e6215</t>
+          <t>https://www.indeed.com/viewjob?jk=53279f54b14e6849</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e84f993a048191bd</t>
+          <t>https://www.indeed.com/viewjob?jk=0a92d266fe841f72</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>BI Engineer - Data Analytics</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>Insight Software</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca97d35c293c8ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=4f17a3a493c5baa0</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Gesa Credit Union</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Spokane Valley, WA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9446abbf0a9e21d5</t>
+          <t>https://www.indeed.com/viewjob?jk=05b11f37b58c06df</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Gesa Credit Union</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cf9f394fc466cab</t>
+          <t>https://www.indeed.com/viewjob?jk=9e166dda8b8fb2c2</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Gesa Credit Union</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Richland, WA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53279f54b14e6849</t>
+          <t>https://www.indeed.com/viewjob?jk=38d66edddd66e10c</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr. Software Engineer - Shared Services</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>HeroDevs</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a92d266fe841f72</t>
+          <t>https://www.indeed.com/viewjob?jk=6847e3d78dab687e</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Insight Software</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f17a3a493c5baa0</t>
+          <t>https://www.indeed.com/viewjob?jk=cc42c2a4e5140f69</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spokane Valley, WA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b11f37b58c06df</t>
+          <t>https://www.indeed.com/viewjob?jk=66e65258ac69fefd</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e166dda8b8fb2c2</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b8c309e1dd4b82</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Richland, WA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38d66edddd66e10c</t>
+          <t>https://www.indeed.com/viewjob?jk=3f98038822e26dd8</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Shared Services</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>HeroDevs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6847e3d78dab687e</t>
+          <t>https://www.indeed.com/viewjob?jk=a55ba7ce9c7c4713</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc42c2a4e5140f69</t>
+          <t>https://www.indeed.com/viewjob?jk=85557e4da3ee4405</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66e65258ac69fefd</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c9edfc26a261dd</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b8c309e1dd4b82</t>
+          <t>https://www.indeed.com/viewjob?jk=bc933305859d57b2</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f98038822e26dd8</t>
+          <t>https://www.indeed.com/viewjob?jk=18e6b1969d6c7210</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a55ba7ce9c7c4713</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e1d701408b5626</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85557e4da3ee4405</t>
+          <t>https://www.indeed.com/viewjob?jk=288dfb7ead95495d</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c9edfc26a261dd</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa85911435d672d</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc933305859d57b2</t>
+          <t>https://www.indeed.com/viewjob?jk=d9b1c071eb4265fc</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18e6b1969d6c7210</t>
+          <t>https://www.indeed.com/viewjob?jk=16f343db215cfb2f</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e1d701408b5626</t>
+          <t>https://www.indeed.com/viewjob?jk=c44c288bccc8a6a7</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=288dfb7ead95495d</t>
+          <t>https://www.indeed.com/viewjob?jk=211ece43a6639e15</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fa85911435d672d</t>
+          <t>https://www.indeed.com/viewjob?jk=117b69fc0cf106cd</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9b1c071eb4265fc</t>
+          <t>https://www.indeed.com/viewjob?jk=3a31df839c27886a</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f343db215cfb2f</t>
+          <t>https://www.indeed.com/viewjob?jk=c2e202fe647fc8c9</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44c288bccc8a6a7</t>
+          <t>https://www.indeed.com/viewjob?jk=7c1275067df0fefc</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211ece43a6639e15</t>
+          <t>https://www.indeed.com/viewjob?jk=0b046a816c53c475</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117b69fc0cf106cd</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0dcc0f31186adf</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a31df839c27886a</t>
+          <t>https://www.indeed.com/viewjob?jk=26a73c1c18e4feb1</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2e202fe647fc8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=c162c04d00001e41</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c1275067df0fefc</t>
+          <t>https://www.indeed.com/viewjob?jk=d72aa3d302823165</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b046a816c53c475</t>
+          <t>https://www.indeed.com/viewjob?jk=437542252a94a7bd</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0dcc0f31186adf</t>
+          <t>https://www.indeed.com/viewjob?jk=1db9b5fd4ad91c79</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26a73c1c18e4feb1</t>
+          <t>https://www.indeed.com/viewjob?jk=c338c18f5cc8b343</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c162c04d00001e41</t>
+          <t>https://www.indeed.com/viewjob?jk=9b85cee4884732fd</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72aa3d302823165</t>
+          <t>https://www.indeed.com/viewjob?jk=87011ec9083a8b23</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=437542252a94a7bd</t>
+          <t>https://www.indeed.com/viewjob?jk=c1d4cefa45bd4112</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1db9b5fd4ad91c79</t>
+          <t>https://www.indeed.com/viewjob?jk=66e3413d7b223f3a</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c338c18f5cc8b343</t>
+          <t>https://www.indeed.com/viewjob?jk=5f780ced93a3bc16</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b85cee4884732fd</t>
+          <t>https://www.indeed.com/viewjob?jk=5a4ad2ff105c8b83</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87011ec9083a8b23</t>
+          <t>https://www.indeed.com/viewjob?jk=430e2adbc8757712</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1d4cefa45bd4112</t>
+          <t>https://www.indeed.com/viewjob?jk=43daf093c3246e39</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66e3413d7b223f3a</t>
+          <t>https://www.indeed.com/viewjob?jk=90d2c0b1b77db71f</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f780ced93a3bc16</t>
+          <t>https://www.indeed.com/viewjob?jk=db8c787399aa7569</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a4ad2ff105c8b83</t>
+          <t>https://www.indeed.com/viewjob?jk=afd791e19de5a0fe</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=430e2adbc8757712</t>
+          <t>https://www.indeed.com/viewjob?jk=1e23b8b93066067d</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43daf093c3246e39</t>
+          <t>https://www.indeed.com/viewjob?jk=aa821c9250f94164</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,24 +6831,24 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d2c0b1b77db71f</t>
+          <t>https://www.indeed.com/viewjob?jk=8f15f76b6c67bbdd</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>DevOps Engineer - Mid</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nalley Consulting</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6866,24 +6866,24 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db8c787399aa7569</t>
+          <t>https://www.indeed.com/viewjob?jk=35023775c057de52</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,34 +6891,34 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd791e19de5a0fe</t>
+          <t>https://www.indeed.com/viewjob?jk=c3ac436669ece2e5</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Senior Software Engineer - Application Traffic team</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6936,24 +6936,24 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e23b8b93066067d</t>
+          <t>https://www.indeed.com/viewjob?jk=dc893f4e11c92275</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Ai Architect</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6971,24 +6971,24 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa821c9250f94164</t>
+          <t>https://www.indeed.com/viewjob?jk=45b842ee858dea9c</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Sr. Solutions Engineer - AI Natives Business</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7005,251 +7005,6 @@
         </is>
       </c>
       <c r="G188" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f15f76b6c67bbdd</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>DevOps Engineer - Mid</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Nalley Consulting</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Doral, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35023775c057de52</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Senior Applied AI Engineer</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c3ac436669ece2e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Application Traffic team</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Mountain View, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc893f4e11c92275</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Database Architect</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>McKesson</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Event Hubs, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=64c482ee7d2fd8be</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Zoom Communications</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D193" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a6b981d8b3e30244</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Ai Architect</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Five Below</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D194" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=45b842ee858dea9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Sr. Solutions Engineer - AI Natives Business</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D195" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d884fcaeec353d16</t>
         </is>

--- a/results/job_matches_2026-05-30.xlsx
+++ b/results/job_matches_2026-05-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G188"/>
+  <dimension ref="A1:G164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote in CA)</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, clustering keys, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=096ec33d45508f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=100ea499e9e2ee80</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote in CA)</t>
+          <t>Full Stack Developer / AI Focused</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>CarParts.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88c69f0d47a40e9</t>
+          <t>https://www.indeed.com/viewjob?jk=c61c6b86bc3293d8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Cloud &amp; Digital Platform DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Diality</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, clustering keys, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100ea499e9e2ee80</t>
+          <t>https://www.indeed.com/viewjob?jk=905414e7ceb13800</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Developer / AI Focused</t>
+          <t>Databricks Administrator</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CarParts.com</t>
+          <t>Avnet</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,77 +636,77 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61c6b86bc3293d8</t>
+          <t>https://www.indeed.com/viewjob?jk=e4012204380caba1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud &amp; Digital Platform DevSecOps Engineer</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Diality</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905414e7ceb13800</t>
+          <t>https://www.indeed.com/viewjob?jk=a442a59c169c0e12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Databricks Administrator</t>
+          <t>Senior IT Big Data Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Avnet</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4012204380caba1</t>
+          <t>https://www.indeed.com/viewjob?jk=37fb3c3c32f07e3a</t>
         </is>
       </c>
     </row>
@@ -818,60 +818,60 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Infrastructure</t>
+          <t>Data Engineer with AI/ML</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bcc3fe3fd715833</t>
+          <t>https://www.indeed.com/viewjob?jk=836bfed93aa23557</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd2d99f50f24a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=c250c7540d478f32</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer with AI/ML</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Aptean</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=836bfed93aa23557</t>
+          <t>https://www.indeed.com/viewjob?jk=13c44a8aef4fd0a0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Decagon</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c250c7540d478f32</t>
+          <t>https://www.indeed.com/viewjob?jk=d3d218109f5a2e7c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Platform Engineer- 6 Month Assignment</t>
+          <t>Senior Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>Decagon</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5d273dd8b89dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=cb96afd07bcd39f3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Aptean</t>
+          <t>Happy Returns, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13c44a8aef4fd0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa757e1e92cc3c3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud &amp; Digital Platform Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Aptean</t>
+          <t>Diality</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,102 +1056,102 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef802648dc8c758d</t>
+          <t>https://www.indeed.com/viewjob?jk=7fe3f1dbc64665df</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Infrastructure</t>
+          <t>Data Engineer Remote - w2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Decagon</t>
+          <t>itheroes inc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3d218109f5a2e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=22ba56caa4808317</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Infrastructure</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Decagon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb96afd07bcd39f3</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab00f608359b4fd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Platform Software Engineer (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Happy Returns, Inc.</t>
+          <t>MAGNETO &amp; DIESEL INJECTOR SERVICE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Humble, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hive, Sqoop, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa757e1e92cc3c3</t>
+          <t>https://www.indeed.com/viewjob?jk=d19cafe12d10dcef</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer- Snowflake &amp; Azure</t>
+          <t>Sr. Systems Engineer- Cloud Infrastructure Engineering</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,129 +1196,129 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763fd8f53ea47c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=4de6e8c6244caa58</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cloud &amp; Digital Platform Architect</t>
+          <t>Sr. Product Mgr. &amp; Enterprise App Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Diality</t>
+          <t>The Vomela Companies</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Elk Grove Village, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS</t>
+          <t>RDS, Azure, Scala, Kafka, SQL Server, MongoDB, Power BI, Tableau, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fe3f1dbc64665df</t>
+          <t>https://www.indeed.com/viewjob?jk=f0c1cd41ea8edf5b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Emerging</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>First Command Financial Services</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>RDS, Data Factory, Scala, Oracle, SQL Server, NoSQL, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7afdce6cf8faaddf</t>
+          <t>https://www.indeed.com/viewjob?jk=5a2bba3746f32469</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer</t>
+          <t>Senior Sales Engineer, Commercial</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ce1a2957006a72</t>
+          <t>https://www.indeed.com/viewjob?jk=0487f884b026bec9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab00f608359b4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=8f9b9650d1bc3a54</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MAGNETO &amp; DIESEL INJECTOR SERVICE</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Humble, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hive, Sqoop, Spark, Scala, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d19cafe12d10dcef</t>
+          <t>https://www.indeed.com/viewjob?jk=efb82b07adb9feba</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer- Cloud Infrastructure Engineering</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de6e8c6244caa58</t>
+          <t>https://www.indeed.com/viewjob?jk=65195644bb1b9e0b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Infrastructure and Tools</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92d9bf233ed60118</t>
+          <t>https://www.indeed.com/viewjob?jk=75e8ade515a41a57</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Product Mgr. &amp; Enterprise App Developer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Vomela Companies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Elk Grove Village, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, SQL Server, MongoDB, Power BI, Tableau, CI/CD, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0c1cd41ea8edf5b</t>
+          <t>https://www.indeed.com/viewjob?jk=859e82cabfb17666</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>First Command Financial Services</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Scala, Oracle, SQL Server, NoSQL, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a2bba3746f32469</t>
+          <t>https://www.indeed.com/viewjob?jk=f143b13efb8ce9b6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0487f884b026bec9</t>
+          <t>https://www.indeed.com/viewjob?jk=5a031b4964c2a255</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f9b9650d1bc3a54</t>
+          <t>https://www.indeed.com/viewjob?jk=c4349cc4f94a5d87</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb82b07adb9feba</t>
+          <t>https://www.indeed.com/viewjob?jk=e66448573f4489d1</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65195644bb1b9e0b</t>
+          <t>https://www.indeed.com/viewjob?jk=ddbf7440ad773888</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e8ade515a41a57</t>
+          <t>https://www.indeed.com/viewjob?jk=b72f3a18139b7e54</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859e82cabfb17666</t>
+          <t>https://www.indeed.com/viewjob?jk=7467917f2474b2e9</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f143b13efb8ce9b6</t>
+          <t>https://www.indeed.com/viewjob?jk=741f313dfe0a4767</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a031b4964c2a255</t>
+          <t>https://www.indeed.com/viewjob?jk=fb549dda19deb4df</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4349cc4f94a5d87</t>
+          <t>https://www.indeed.com/viewjob?jk=ad53455736c94aa1</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66448573f4489d1</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf96d3e5672d2dd</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddbf7440ad773888</t>
+          <t>https://www.indeed.com/viewjob?jk=a2abd6bece93c89e</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b72f3a18139b7e54</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7b4a6316115547</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7467917f2474b2e9</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef2a2c6485dc8ce</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=741f313dfe0a4767</t>
+          <t>https://www.indeed.com/viewjob?jk=f8777195f0640326</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb549dda19deb4df</t>
+          <t>https://www.indeed.com/viewjob?jk=8b251c80469648dc</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad53455736c94aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad5e6a6c6033f66</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf96d3e5672d2dd</t>
+          <t>https://www.indeed.com/viewjob?jk=4439501b54b34a7a</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2abd6bece93c89e</t>
+          <t>https://www.indeed.com/viewjob?jk=1151c815185cd79e</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7b4a6316115547</t>
+          <t>https://www.indeed.com/viewjob?jk=d6614c39234b9da2</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef2a2c6485dc8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7e23c7f438f8c8</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8777195f0640326</t>
+          <t>https://www.indeed.com/viewjob?jk=e8663ead75611c2e</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b251c80469648dc</t>
+          <t>https://www.indeed.com/viewjob?jk=51de78e580811e18</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad5e6a6c6033f66</t>
+          <t>https://www.indeed.com/viewjob?jk=548feeaa37b8c916</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4439501b54b34a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=9cf7d70224611ecc</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1151c815185cd79e</t>
+          <t>https://www.indeed.com/viewjob?jk=08e283453e85139f</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6614c39234b9da2</t>
+          <t>https://www.indeed.com/viewjob?jk=ecaa2a1fd433f4a4</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7e23c7f438f8c8</t>
+          <t>https://www.indeed.com/viewjob?jk=dd01c10e73409cc8</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8663ead75611c2e</t>
+          <t>https://www.indeed.com/viewjob?jk=3166241cc8c62f5d</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51de78e580811e18</t>
+          <t>https://www.indeed.com/viewjob?jk=1572589542133e74</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=548feeaa37b8c916</t>
+          <t>https://www.indeed.com/viewjob?jk=a2ec3f9f81325aa0</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cf7d70224611ecc</t>
+          <t>https://www.indeed.com/viewjob?jk=492f0c5d5b1026f4</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e283453e85139f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5a1bf124fcc939</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecaa2a1fd433f4a4</t>
+          <t>https://www.indeed.com/viewjob?jk=e7780a9fb7958201</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd01c10e73409cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=fd18a128a4672b91</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3166241cc8c62f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=ea676aaaba70e2d7</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1572589542133e74</t>
+          <t>https://www.indeed.com/viewjob?jk=cab3ba747ce4a550</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2ec3f9f81325aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=d65e39a595440fab</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=492f0c5d5b1026f4</t>
+          <t>https://www.indeed.com/viewjob?jk=55cb9c48e2f72a54</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5a1bf124fcc939</t>
+          <t>https://www.indeed.com/viewjob?jk=b3a01b8449781d9b</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7780a9fb7958201</t>
+          <t>https://www.indeed.com/viewjob?jk=5fa7561c868d2097</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd18a128a4672b91</t>
+          <t>https://www.indeed.com/viewjob?jk=3a729d7eaa711e20</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea676aaaba70e2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=1f022796cfb8fbcc</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab3ba747ce4a550</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c33b5572cf45fa</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65e39a595440fab</t>
+          <t>https://www.indeed.com/viewjob?jk=8762f88f61ad7223</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55cb9c48e2f72a54</t>
+          <t>https://www.indeed.com/viewjob?jk=efdfb03d10f7ec00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Senior Associate, Data Analytics Engineering</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Options Clearing Corporation</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3a01b8449781d9b</t>
+          <t>https://www.indeed.com/viewjob?jk=1ad61eb5cd2a5633</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Fabletics</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,67 +3156,67 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fa7561c868d2097</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac7bdb141d55008</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Uber Freight</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Scala, Kafka, Oracle, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a729d7eaa711e20</t>
+          <t>https://www.indeed.com/viewjob?jk=1b1465e42f01feff</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Sr. Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,14 +3226,14 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f022796cfb8fbcc</t>
+          <t>https://www.indeed.com/viewjob?jk=ae7ce0b79b127907</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3243,15 +3243,15 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,14 +3261,14 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c33b5572cf45fa</t>
+          <t>https://www.indeed.com/viewjob?jk=b7994c3eb46bae42</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3278,15 +3278,15 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,14 +3296,14 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8762f88f61ad7223</t>
+          <t>https://www.indeed.com/viewjob?jk=649242ee28a33ae5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3313,15 +3313,15 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdfb03d10f7ec00</t>
+          <t>https://www.indeed.com/viewjob?jk=4b46b87f1359f8f5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Distributed Data Systems</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f494d2abfb9b3a</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a7b9a70e68cf9f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Distributed Data Systems</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35301f7890450ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a148e3a41849d9</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Distributed Data Systems</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,19 +3436,19 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f178ac0bdca2782a</t>
+          <t>https://www.indeed.com/viewjob?jk=fa4b4fcc410a503a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Analytics Engineering</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Options Clearing Corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3457,11 +3457,11 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, dbt, Tableau, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ad61eb5cd2a5633</t>
+          <t>https://www.indeed.com/viewjob?jk=6147a561d729a0dd</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Fabletics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,67 +3506,67 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac7bdb141d55008</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab5bc5f32a7b9a0</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Uber Freight</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Scala, Kafka, Oracle, CI/CD, Maven</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b1465e42f01feff</t>
+          <t>https://www.indeed.com/viewjob?jk=29f309b16d064eae</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Fullstack</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e1d5edd7f6cfacc</t>
+          <t>https://www.indeed.com/viewjob?jk=f0b6e4cc0b843bf8</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - GSI's and FinTech Data</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44ec35e1f7566eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=9d739c3bc7cf38d1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Financial Services (Insurance)</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df17d8e1960c7150</t>
+          <t>https://www.indeed.com/viewjob?jk=70aa889c4c9efda8</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae7ce0b79b127907</t>
+          <t>https://www.indeed.com/viewjob?jk=97557fcc3403a036</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc99c4d09fcc8c74</t>
+          <t>https://www.indeed.com/viewjob?jk=01009226e788120d</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7994c3eb46bae42</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b0eb4fb08e6514</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=649242ee28a33ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7b1778e389048a</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b46b87f1359f8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=a5c63e693a3dd615</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a7b9a70e68cf9f</t>
+          <t>https://www.indeed.com/viewjob?jk=91abed51133c7c23</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a148e3a41849d9</t>
+          <t>https://www.indeed.com/viewjob?jk=432b655803995623</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa4b4fcc410a503a</t>
+          <t>https://www.indeed.com/viewjob?jk=04006a1fe4e66850</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6147a561d729a0dd</t>
+          <t>https://www.indeed.com/viewjob?jk=4786e7810dfbd42c</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab5bc5f32a7b9a0</t>
+          <t>https://www.indeed.com/viewjob?jk=a73d9c78e32edfcb</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29f309b16d064eae</t>
+          <t>https://www.indeed.com/viewjob?jk=f6e14d6ec4b8aeb0</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0b6e4cc0b843bf8</t>
+          <t>https://www.indeed.com/viewjob?jk=f49fd486a1470d4a</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d739c3bc7cf38d1</t>
+          <t>https://www.indeed.com/viewjob?jk=bb0d75494367b7de</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70aa889c4c9efda8</t>
+          <t>https://www.indeed.com/viewjob?jk=3194fbbe9c9c6915</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97557fcc3403a036</t>
+          <t>https://www.indeed.com/viewjob?jk=28e73925baaee988</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01009226e788120d</t>
+          <t>https://www.indeed.com/viewjob?jk=fd07d9e8d85d17ee</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b0eb4fb08e6514</t>
+          <t>https://www.indeed.com/viewjob?jk=518960648e6b46f0</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7b1778e389048a</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5b4030fed54c3d</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5c63e693a3dd615</t>
+          <t>https://www.indeed.com/viewjob?jk=25174fd8817164ea</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91abed51133c7c23</t>
+          <t>https://www.indeed.com/viewjob?jk=69b7427915d34288</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432b655803995623</t>
+          <t>https://www.indeed.com/viewjob?jk=4964a3b46fec8c52</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04006a1fe4e66850</t>
+          <t>https://www.indeed.com/viewjob?jk=308aad1cd4d5b8e2</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4786e7810dfbd42c</t>
+          <t>https://www.indeed.com/viewjob?jk=4edb47917f0e6215</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,102 +4486,102 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a73d9c78e32edfcb</t>
+          <t>https://www.indeed.com/viewjob?jk=e84f993a048191bd</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6e14d6ec4b8aeb0</t>
+          <t>https://www.indeed.com/viewjob?jk=53279f54b14e6849</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f49fd486a1470d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=0a92d266fe841f72</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Insight Software</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb0d75494367b7de</t>
+          <t>https://www.indeed.com/viewjob?jk=4f17a3a493c5baa0</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Sr. Software Engineer - Shared Services</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HeroDevs</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,14 +4626,14 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3194fbbe9c9c6915</t>
+          <t>https://www.indeed.com/viewjob?jk=6847e3d78dab687e</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4643,15 +4643,15 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,14 +4661,14 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e73925baaee988</t>
+          <t>https://www.indeed.com/viewjob?jk=cc42c2a4e5140f69</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4678,15 +4678,15 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,14 +4696,14 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd07d9e8d85d17ee</t>
+          <t>https://www.indeed.com/viewjob?jk=66e65258ac69fefd</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4713,15 +4713,15 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,14 +4731,14 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518960648e6b46f0</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b8c309e1dd4b82</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4748,15 +4748,15 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,14 +4766,14 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5b4030fed54c3d</t>
+          <t>https://www.indeed.com/viewjob?jk=3f98038822e26dd8</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4783,15 +4783,15 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,14 +4801,14 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25174fd8817164ea</t>
+          <t>https://www.indeed.com/viewjob?jk=a55ba7ce9c7c4713</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4818,15 +4818,15 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,14 +4836,14 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b7427915d34288</t>
+          <t>https://www.indeed.com/viewjob?jk=85557e4da3ee4405</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4853,15 +4853,15 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4964a3b46fec8c52</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c9edfc26a261dd</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,32 +4906,32 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aad1cd4d5b8e2</t>
+          <t>https://www.indeed.com/viewjob?jk=bc933305859d57b2</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Fullstack</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,32 +4941,32 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d41030c2a031bc3</t>
+          <t>https://www.indeed.com/viewjob?jk=18e6b1969d6c7210</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Fullstack</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,32 +4976,32 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e37bcb174213c7a</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e1d701408b5626</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,32 +5011,32 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4edb47917f0e6215</t>
+          <t>https://www.indeed.com/viewjob?jk=288dfb7ead95495d</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e84f993a048191bd</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa85911435d672d</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9446abbf0a9e21d5</t>
+          <t>https://www.indeed.com/viewjob?jk=d9b1c071eb4265fc</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cf9f394fc466cab</t>
+          <t>https://www.indeed.com/viewjob?jk=16f343db215cfb2f</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53279f54b14e6849</t>
+          <t>https://www.indeed.com/viewjob?jk=c44c288bccc8a6a7</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a92d266fe841f72</t>
+          <t>https://www.indeed.com/viewjob?jk=211ece43a6639e15</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Insight Software</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f17a3a493c5baa0</t>
+          <t>https://www.indeed.com/viewjob?jk=117b69fc0cf106cd</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spokane Valley, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b11f37b58c06df</t>
+          <t>https://www.indeed.com/viewjob?jk=3a31df839c27886a</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e166dda8b8fb2c2</t>
+          <t>https://www.indeed.com/viewjob?jk=c2e202fe647fc8c9</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Richland, WA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38d66edddd66e10c</t>
+          <t>https://www.indeed.com/viewjob?jk=7c1275067df0fefc</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Shared Services</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>HeroDevs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6847e3d78dab687e</t>
+          <t>https://www.indeed.com/viewjob?jk=0b046a816c53c475</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc42c2a4e5140f69</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0dcc0f31186adf</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66e65258ac69fefd</t>
+          <t>https://www.indeed.com/viewjob?jk=26a73c1c18e4feb1</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b8c309e1dd4b82</t>
+          <t>https://www.indeed.com/viewjob?jk=c162c04d00001e41</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f98038822e26dd8</t>
+          <t>https://www.indeed.com/viewjob?jk=d72aa3d302823165</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a55ba7ce9c7c4713</t>
+          <t>https://www.indeed.com/viewjob?jk=437542252a94a7bd</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85557e4da3ee4405</t>
+          <t>https://www.indeed.com/viewjob?jk=1db9b5fd4ad91c79</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c9edfc26a261dd</t>
+          <t>https://www.indeed.com/viewjob?jk=c338c18f5cc8b343</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc933305859d57b2</t>
+          <t>https://www.indeed.com/viewjob?jk=9b85cee4884732fd</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18e6b1969d6c7210</t>
+          <t>https://www.indeed.com/viewjob?jk=87011ec9083a8b23</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e1d701408b5626</t>
+          <t>https://www.indeed.com/viewjob?jk=c1d4cefa45bd4112</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=288dfb7ead95495d</t>
+          <t>https://www.indeed.com/viewjob?jk=66e3413d7b223f3a</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fa85911435d672d</t>
+          <t>https://www.indeed.com/viewjob?jk=5f780ced93a3bc16</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9b1c071eb4265fc</t>
+          <t>https://www.indeed.com/viewjob?jk=5a4ad2ff105c8b83</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f343db215cfb2f</t>
+          <t>https://www.indeed.com/viewjob?jk=430e2adbc8757712</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44c288bccc8a6a7</t>
+          <t>https://www.indeed.com/viewjob?jk=43daf093c3246e39</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211ece43a6639e15</t>
+          <t>https://www.indeed.com/viewjob?jk=90d2c0b1b77db71f</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117b69fc0cf106cd</t>
+          <t>https://www.indeed.com/viewjob?jk=db8c787399aa7569</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a31df839c27886a</t>
+          <t>https://www.indeed.com/viewjob?jk=afd791e19de5a0fe</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2e202fe647fc8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=1e23b8b93066067d</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c1275067df0fefc</t>
+          <t>https://www.indeed.com/viewjob?jk=aa821c9250f94164</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b046a816c53c475</t>
+          <t>https://www.indeed.com/viewjob?jk=8f15f76b6c67bbdd</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>DevOps Engineer - Mid</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nalley Consulting</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,24 +6131,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0dcc0f31186adf</t>
+          <t>https://www.indeed.com/viewjob?jk=35023775c057de52</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,857 +6156,17 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26a73c1c18e4feb1</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c162c04d00001e41</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d72aa3d302823165</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=437542252a94a7bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1db9b5fd4ad91c79</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c338c18f5cc8b343</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Stamford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9b85cee4884732fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=87011ec9083a8b23</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c1d4cefa45bd4112</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=66e3413d7b223f3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f780ced93a3bc16</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a4ad2ff105c8b83</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=430e2adbc8757712</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=43daf093c3246e39</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90d2c0b1b77db71f</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db8c787399aa7569</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=afd791e19de5a0fe</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Costa Mesa, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1e23b8b93066067d</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>New Orleans, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa821c9250f94164</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f15f76b6c67bbdd</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>DevOps Engineer - Mid</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Nalley Consulting</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Doral, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35023775c057de52</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Senior Applied AI Engineer</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=c3ac436669ece2e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Application Traffic team</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Mountain View, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLflow</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc893f4e11c92275</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Ai Architect</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Five Below</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=45b842ee858dea9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Sr. Solutions Engineer - AI Natives Business</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d884fcaeec353d16</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-30.xlsx
+++ b/results/job_matches_2026-05-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G164"/>
+  <dimension ref="A1:G156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,60 +748,60 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Engineer with AI/ML</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0769674b72ae58f</t>
+          <t>https://www.indeed.com/viewjob?jk=836bfed93aa23557</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>Aptean</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aef1c5cf0ee00174</t>
+          <t>https://www.indeed.com/viewjob?jk=13c44a8aef4fd0a0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer with AI/ML</t>
+          <t>Senior Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Decagon</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=836bfed93aa23557</t>
+          <t>https://www.indeed.com/viewjob?jk=d3d218109f5a2e7c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Decagon</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c250c7540d478f32</t>
+          <t>https://www.indeed.com/viewjob?jk=cb96afd07bcd39f3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Aptean</t>
+          <t>Happy Returns, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13c44a8aef4fd0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa757e1e92cc3c3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Infrastructure</t>
+          <t>Cloud &amp; Digital Platform Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Decagon</t>
+          <t>Diality</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,102 +951,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3d218109f5a2e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=7fe3f1dbc64665df</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Infrastructure</t>
+          <t>Data Engineer Remote - w2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Decagon</t>
+          <t>itheroes inc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb96afd07bcd39f3</t>
+          <t>https://www.indeed.com/viewjob?jk=22ba56caa4808317</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Platform Software Engineer (Remote)</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Happy Returns, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Data Modeling</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa757e1e92cc3c3</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab00f608359b4fd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud &amp; Digital Platform Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Diality</t>
+          <t>MAGNETO &amp; DIESEL INJECTOR SERVICE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Humble, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hive, Sqoop, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fe3f1dbc64665df</t>
+          <t>https://www.indeed.com/viewjob?jk=d19cafe12d10dcef</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer Remote - w2</t>
+          <t>Sr. Systems Engineer- Cloud Infrastructure Engineering</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>itheroes inc</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22ba56caa4808317</t>
+          <t>https://www.indeed.com/viewjob?jk=4de6e8c6244caa58</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Sr. Product Mgr. &amp; Enterprise App Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Vomela Companies</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Elk Grove Village, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Scala, Kafka, SQL Server, MongoDB, Power BI, Tableau, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab00f608359b4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=f0c1cd41ea8edf5b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MAGNETO &amp; DIESEL INJECTOR SERVICE</t>
+          <t>First Command Financial Services</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Humble, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hive, Sqoop, Spark, Scala, ETL, ELT</t>
+          <t>RDS, Data Factory, Scala, Oracle, SQL Server, NoSQL, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d19cafe12d10dcef</t>
+          <t>https://www.indeed.com/viewjob?jk=5a2bba3746f32469</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer- Cloud Infrastructure Engineering</t>
+          <t>Senior Sales Engineer, Commercial</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de6e8c6244caa58</t>
+          <t>https://www.indeed.com/viewjob?jk=0487f884b026bec9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Product Mgr. &amp; Enterprise App Developer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Vomela Companies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Elk Grove Village, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, SQL Server, MongoDB, Power BI, Tableau, CI/CD, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0c1cd41ea8edf5b</t>
+          <t>https://www.indeed.com/viewjob?jk=8f9b9650d1bc3a54</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>First Command Financial Services</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Scala, Oracle, SQL Server, NoSQL, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a2bba3746f32469</t>
+          <t>https://www.indeed.com/viewjob?jk=efb82b07adb9feba</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0487f884b026bec9</t>
+          <t>https://www.indeed.com/viewjob?jk=65195644bb1b9e0b</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f9b9650d1bc3a54</t>
+          <t>https://www.indeed.com/viewjob?jk=75e8ade515a41a57</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb82b07adb9feba</t>
+          <t>https://www.indeed.com/viewjob?jk=859e82cabfb17666</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65195644bb1b9e0b</t>
+          <t>https://www.indeed.com/viewjob?jk=f143b13efb8ce9b6</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e8ade515a41a57</t>
+          <t>https://www.indeed.com/viewjob?jk=5a031b4964c2a255</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859e82cabfb17666</t>
+          <t>https://www.indeed.com/viewjob?jk=c4349cc4f94a5d87</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f143b13efb8ce9b6</t>
+          <t>https://www.indeed.com/viewjob?jk=e66448573f4489d1</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a031b4964c2a255</t>
+          <t>https://www.indeed.com/viewjob?jk=ddbf7440ad773888</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4349cc4f94a5d87</t>
+          <t>https://www.indeed.com/viewjob?jk=b72f3a18139b7e54</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66448573f4489d1</t>
+          <t>https://www.indeed.com/viewjob?jk=7467917f2474b2e9</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddbf7440ad773888</t>
+          <t>https://www.indeed.com/viewjob?jk=741f313dfe0a4767</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b72f3a18139b7e54</t>
+          <t>https://www.indeed.com/viewjob?jk=fb549dda19deb4df</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7467917f2474b2e9</t>
+          <t>https://www.indeed.com/viewjob?jk=ad53455736c94aa1</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=741f313dfe0a4767</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf96d3e5672d2dd</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb549dda19deb4df</t>
+          <t>https://www.indeed.com/viewjob?jk=a2abd6bece93c89e</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad53455736c94aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7b4a6316115547</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf96d3e5672d2dd</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef2a2c6485dc8ce</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2abd6bece93c89e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8777195f0640326</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7b4a6316115547</t>
+          <t>https://www.indeed.com/viewjob?jk=8b251c80469648dc</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef2a2c6485dc8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad5e6a6c6033f66</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8777195f0640326</t>
+          <t>https://www.indeed.com/viewjob?jk=4439501b54b34a7a</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b251c80469648dc</t>
+          <t>https://www.indeed.com/viewjob?jk=1151c815185cd79e</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad5e6a6c6033f66</t>
+          <t>https://www.indeed.com/viewjob?jk=d6614c39234b9da2</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4439501b54b34a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7e23c7f438f8c8</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1151c815185cd79e</t>
+          <t>https://www.indeed.com/viewjob?jk=e8663ead75611c2e</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6614c39234b9da2</t>
+          <t>https://www.indeed.com/viewjob?jk=51de78e580811e18</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7e23c7f438f8c8</t>
+          <t>https://www.indeed.com/viewjob?jk=548feeaa37b8c916</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8663ead75611c2e</t>
+          <t>https://www.indeed.com/viewjob?jk=9cf7d70224611ecc</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51de78e580811e18</t>
+          <t>https://www.indeed.com/viewjob?jk=08e283453e85139f</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=548feeaa37b8c916</t>
+          <t>https://www.indeed.com/viewjob?jk=ecaa2a1fd433f4a4</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cf7d70224611ecc</t>
+          <t>https://www.indeed.com/viewjob?jk=dd01c10e73409cc8</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e283453e85139f</t>
+          <t>https://www.indeed.com/viewjob?jk=3166241cc8c62f5d</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecaa2a1fd433f4a4</t>
+          <t>https://www.indeed.com/viewjob?jk=1572589542133e74</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd01c10e73409cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=a2ec3f9f81325aa0</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3166241cc8c62f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=492f0c5d5b1026f4</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1572589542133e74</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5a1bf124fcc939</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2ec3f9f81325aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=e7780a9fb7958201</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=492f0c5d5b1026f4</t>
+          <t>https://www.indeed.com/viewjob?jk=fd18a128a4672b91</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5a1bf124fcc939</t>
+          <t>https://www.indeed.com/viewjob?jk=ea676aaaba70e2d7</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7780a9fb7958201</t>
+          <t>https://www.indeed.com/viewjob?jk=cab3ba747ce4a550</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd18a128a4672b91</t>
+          <t>https://www.indeed.com/viewjob?jk=d65e39a595440fab</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea676aaaba70e2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=55cb9c48e2f72a54</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab3ba747ce4a550</t>
+          <t>https://www.indeed.com/viewjob?jk=b3a01b8449781d9b</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65e39a595440fab</t>
+          <t>https://www.indeed.com/viewjob?jk=5fa7561c868d2097</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55cb9c48e2f72a54</t>
+          <t>https://www.indeed.com/viewjob?jk=3a729d7eaa711e20</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3a01b8449781d9b</t>
+          <t>https://www.indeed.com/viewjob?jk=1f022796cfb8fbcc</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fa7561c868d2097</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c33b5572cf45fa</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a729d7eaa711e20</t>
+          <t>https://www.indeed.com/viewjob?jk=8762f88f61ad7223</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f022796cfb8fbcc</t>
+          <t>https://www.indeed.com/viewjob?jk=efdfb03d10f7ec00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Senior Associate, Data Analytics Engineering</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Options Clearing Corporation</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,67 +3016,67 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c33b5572cf45fa</t>
+          <t>https://www.indeed.com/viewjob?jk=1ad61eb5cd2a5633</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Uber Freight</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Scala, Kafka, Oracle, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8762f88f61ad7223</t>
+          <t>https://www.indeed.com/viewjob?jk=1b1465e42f01feff</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Consultant</t>
+          <t>Sr. Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdfb03d10f7ec00</t>
+          <t>https://www.indeed.com/viewjob?jk=ae7ce0b79b127907</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Analytics Engineering</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Options Clearing Corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, dbt, Tableau, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ad61eb5cd2a5633</t>
+          <t>https://www.indeed.com/viewjob?jk=b7994c3eb46bae42</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Fabletics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,59 +3156,59 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac7bdb141d55008</t>
+          <t>https://www.indeed.com/viewjob?jk=649242ee28a33ae5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Uber Freight</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Scala, Kafka, Oracle, CI/CD, Maven</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b1465e42f01feff</t>
+          <t>https://www.indeed.com/viewjob?jk=4b46b87f1359f8f5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae7ce0b79b127907</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a7b9a70e68cf9f</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7994c3eb46bae42</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a148e3a41849d9</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=649242ee28a33ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=fa4b4fcc410a503a</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b46b87f1359f8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=6147a561d729a0dd</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a7b9a70e68cf9f</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab5bc5f32a7b9a0</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a148e3a41849d9</t>
+          <t>https://www.indeed.com/viewjob?jk=29f309b16d064eae</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa4b4fcc410a503a</t>
+          <t>https://www.indeed.com/viewjob?jk=f0b6e4cc0b843bf8</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6147a561d729a0dd</t>
+          <t>https://www.indeed.com/viewjob?jk=9d739c3bc7cf38d1</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab5bc5f32a7b9a0</t>
+          <t>https://www.indeed.com/viewjob?jk=70aa889c4c9efda8</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29f309b16d064eae</t>
+          <t>https://www.indeed.com/viewjob?jk=97557fcc3403a036</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0b6e4cc0b843bf8</t>
+          <t>https://www.indeed.com/viewjob?jk=01009226e788120d</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d739c3bc7cf38d1</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b0eb4fb08e6514</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70aa889c4c9efda8</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7b1778e389048a</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97557fcc3403a036</t>
+          <t>https://www.indeed.com/viewjob?jk=a5c63e693a3dd615</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01009226e788120d</t>
+          <t>https://www.indeed.com/viewjob?jk=91abed51133c7c23</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b0eb4fb08e6514</t>
+          <t>https://www.indeed.com/viewjob?jk=432b655803995623</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7b1778e389048a</t>
+          <t>https://www.indeed.com/viewjob?jk=04006a1fe4e66850</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5c63e693a3dd615</t>
+          <t>https://www.indeed.com/viewjob?jk=4786e7810dfbd42c</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91abed51133c7c23</t>
+          <t>https://www.indeed.com/viewjob?jk=a73d9c78e32edfcb</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432b655803995623</t>
+          <t>https://www.indeed.com/viewjob?jk=f6e14d6ec4b8aeb0</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04006a1fe4e66850</t>
+          <t>https://www.indeed.com/viewjob?jk=f49fd486a1470d4a</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4786e7810dfbd42c</t>
+          <t>https://www.indeed.com/viewjob?jk=bb0d75494367b7de</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a73d9c78e32edfcb</t>
+          <t>https://www.indeed.com/viewjob?jk=3194fbbe9c9c6915</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6e14d6ec4b8aeb0</t>
+          <t>https://www.indeed.com/viewjob?jk=28e73925baaee988</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f49fd486a1470d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=fd07d9e8d85d17ee</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb0d75494367b7de</t>
+          <t>https://www.indeed.com/viewjob?jk=518960648e6b46f0</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3194fbbe9c9c6915</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5b4030fed54c3d</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e73925baaee988</t>
+          <t>https://www.indeed.com/viewjob?jk=25174fd8817164ea</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd07d9e8d85d17ee</t>
+          <t>https://www.indeed.com/viewjob?jk=69b7427915d34288</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,102 +4241,102 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518960648e6b46f0</t>
+          <t>https://www.indeed.com/viewjob?jk=4964a3b46fec8c52</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5b4030fed54c3d</t>
+          <t>https://www.indeed.com/viewjob?jk=53279f54b14e6849</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25174fd8817164ea</t>
+          <t>https://www.indeed.com/viewjob?jk=0a92d266fe841f72</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Sr. Software Engineer - Shared Services</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HeroDevs</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,14 +4346,14 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b7427915d34288</t>
+          <t>https://www.indeed.com/viewjob?jk=6847e3d78dab687e</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4363,15 +4363,15 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4964a3b46fec8c52</t>
+          <t>https://www.indeed.com/viewjob?jk=cc42c2a4e5140f69</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aad1cd4d5b8e2</t>
+          <t>https://www.indeed.com/viewjob?jk=66e65258ac69fefd</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4edb47917f0e6215</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b8c309e1dd4b82</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e84f993a048191bd</t>
+          <t>https://www.indeed.com/viewjob?jk=3f98038822e26dd8</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53279f54b14e6849</t>
+          <t>https://www.indeed.com/viewjob?jk=a55ba7ce9c7c4713</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a92d266fe841f72</t>
+          <t>https://www.indeed.com/viewjob?jk=85557e4da3ee4405</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Insight Software</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f17a3a493c5baa0</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c9edfc26a261dd</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Shared Services</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>HeroDevs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6847e3d78dab687e</t>
+          <t>https://www.indeed.com/viewjob?jk=bc933305859d57b2</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc42c2a4e5140f69</t>
+          <t>https://www.indeed.com/viewjob?jk=18e6b1969d6c7210</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66e65258ac69fefd</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e1d701408b5626</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b8c309e1dd4b82</t>
+          <t>https://www.indeed.com/viewjob?jk=288dfb7ead95495d</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f98038822e26dd8</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa85911435d672d</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a55ba7ce9c7c4713</t>
+          <t>https://www.indeed.com/viewjob?jk=d9b1c071eb4265fc</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85557e4da3ee4405</t>
+          <t>https://www.indeed.com/viewjob?jk=16f343db215cfb2f</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c9edfc26a261dd</t>
+          <t>https://www.indeed.com/viewjob?jk=c44c288bccc8a6a7</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc933305859d57b2</t>
+          <t>https://www.indeed.com/viewjob?jk=211ece43a6639e15</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18e6b1969d6c7210</t>
+          <t>https://www.indeed.com/viewjob?jk=117b69fc0cf106cd</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e1d701408b5626</t>
+          <t>https://www.indeed.com/viewjob?jk=3a31df839c27886a</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=288dfb7ead95495d</t>
+          <t>https://www.indeed.com/viewjob?jk=c2e202fe647fc8c9</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fa85911435d672d</t>
+          <t>https://www.indeed.com/viewjob?jk=7c1275067df0fefc</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9b1c071eb4265fc</t>
+          <t>https://www.indeed.com/viewjob?jk=0b046a816c53c475</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f343db215cfb2f</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0dcc0f31186adf</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44c288bccc8a6a7</t>
+          <t>https://www.indeed.com/viewjob?jk=26a73c1c18e4feb1</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211ece43a6639e15</t>
+          <t>https://www.indeed.com/viewjob?jk=c162c04d00001e41</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117b69fc0cf106cd</t>
+          <t>https://www.indeed.com/viewjob?jk=d72aa3d302823165</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a31df839c27886a</t>
+          <t>https://www.indeed.com/viewjob?jk=437542252a94a7bd</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2e202fe647fc8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=1db9b5fd4ad91c79</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c1275067df0fefc</t>
+          <t>https://www.indeed.com/viewjob?jk=c338c18f5cc8b343</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b046a816c53c475</t>
+          <t>https://www.indeed.com/viewjob?jk=9b85cee4884732fd</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0dcc0f31186adf</t>
+          <t>https://www.indeed.com/viewjob?jk=87011ec9083a8b23</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26a73c1c18e4feb1</t>
+          <t>https://www.indeed.com/viewjob?jk=c1d4cefa45bd4112</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c162c04d00001e41</t>
+          <t>https://www.indeed.com/viewjob?jk=66e3413d7b223f3a</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72aa3d302823165</t>
+          <t>https://www.indeed.com/viewjob?jk=5f780ced93a3bc16</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=437542252a94a7bd</t>
+          <t>https://www.indeed.com/viewjob?jk=5a4ad2ff105c8b83</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1db9b5fd4ad91c79</t>
+          <t>https://www.indeed.com/viewjob?jk=430e2adbc8757712</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c338c18f5cc8b343</t>
+          <t>https://www.indeed.com/viewjob?jk=43daf093c3246e39</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b85cee4884732fd</t>
+          <t>https://www.indeed.com/viewjob?jk=90d2c0b1b77db71f</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87011ec9083a8b23</t>
+          <t>https://www.indeed.com/viewjob?jk=db8c787399aa7569</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1d4cefa45bd4112</t>
+          <t>https://www.indeed.com/viewjob?jk=afd791e19de5a0fe</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66e3413d7b223f3a</t>
+          <t>https://www.indeed.com/viewjob?jk=1e23b8b93066067d</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f780ced93a3bc16</t>
+          <t>https://www.indeed.com/viewjob?jk=aa821c9250f94164</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a4ad2ff105c8b83</t>
+          <t>https://www.indeed.com/viewjob?jk=8f15f76b6c67bbdd</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>DevOps Engineer - Mid</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nalley Consulting</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=430e2adbc8757712</t>
+          <t>https://www.indeed.com/viewjob?jk=35023775c057de52</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,295 +5876,15 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=43daf093c3246e39</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90d2c0b1b77db71f</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db8c787399aa7569</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=afd791e19de5a0fe</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Costa Mesa, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1e23b8b93066067d</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>New Orleans, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa821c9250f94164</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>AI Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f15f76b6c67bbdd</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>DevOps Engineer - Mid</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Nalley Consulting</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Doral, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35023775c057de52</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Senior Applied AI Engineer</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c3ac436669ece2e5</t>
         </is>
